--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,6 +727,5244 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tijuana</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pachuca</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K2" t="n">
+        <v>950</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Necaxa</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBV</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KR Reykjavik</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Serbian Super League</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Radnicki Nis</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FK Javor Ivanjica</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>870</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>660</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Al Mokawloon</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Al Ittihad (EGY)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Danish Superliga</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FC Nordsjaelland</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Danish Superliga</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Randers</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fredericia</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Serbian Super League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FK Napredak</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FK IMT Novi Beograd</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dutch Eredivisie</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Malmo FF</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mjallby</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AaB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>B93 Copenhagen</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>IFK Goteborg</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Danish Superliga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SonderjyskE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Zamalek</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pyramids</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Petrojet</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Serbian Super League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mladost Lucani</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FK Radnicki 1923</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K20" t="n">
+        <v>950</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Serbian Super League</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FK Spartak</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FK Backa Topola</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>950</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CDT Real Oruro</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K23" t="n">
+        <v>950</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dutch Eredivisie</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PEC Zwolle</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Hafnarfjordur</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I2" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -805,7 +805,7 @@
         <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W2" t="n">
         <v>1.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -969,16 +969,16 @@
         <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>2.32</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
         <v>2.32</v>
@@ -987,16 +987,16 @@
         <v>1.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="T3" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="V3" t="n">
         <v>2.16</v>
@@ -1005,116 +1005,116 @@
         <v>1.23</v>
       </c>
       <c r="X3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI3" t="n">
         <v>30</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>40</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.04</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.14</v>
+        <v>16</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.18</v>
+        <v>18</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.24</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.14</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.14</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.22</v>
+        <v>6.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.28</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.26</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.28</v>
+        <v>7.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.34</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.34</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>1.84</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
         <v>2.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.92</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>1.76</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>2.92</v>
       </c>
       <c r="G10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
         <v>2.24</v>
       </c>
       <c r="I10" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.95</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="I11" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.9</v>
@@ -3181,7 +3181,7 @@
         <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM14" t="n">
         <v>140</v>
@@ -3202,7 +3202,7 @@
         <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT14" t="n">
         <v>9</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G15" t="n">
         <v>1.88</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
         <v>2.48</v>
@@ -3485,7 +3485,7 @@
         <v>2.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
         <v>3.6</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>4.8</v>
       </c>
       <c r="G17" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="I17" t="n">
         <v>1.76</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="H18" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="H19" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="I19" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J19" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4670,13 +4670,13 @@
         <v>1.77</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R22" t="n">
         <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
         <v>1.94</v>
@@ -4718,7 +4718,7 @@
         <v>13</v>
       </c>
       <c r="AG22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
         <v>21</v>
@@ -4748,7 +4748,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR22" t="n">
         <v>23</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
         <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
         <v>1.82</v>
@@ -5661,7 +5661,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y27" t="n">
         <v>9.6</v>
@@ -5688,13 +5688,13 @@
         <v>32</v>
       </c>
       <c r="AG27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH27" t="n">
         <v>18.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ27" t="n">
         <v>95</v>
@@ -5739,13 +5739,13 @@
         <v>20</v>
       </c>
       <c r="AX27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY27" t="n">
         <v>15</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA27" t="n">
         <v>32</v>
@@ -5757,20 +5757,20 @@
         <v>27</v>
       </c>
       <c r="BD27" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BE27" t="n">
         <v>44</v>
       </c>
       <c r="BF27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BG27" t="n">
         <v>14.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5801,23 +5801,23 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.55</v>
       </c>
-      <c r="I28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4.9</v>
-      </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -793,7 +793,7 @@
         <v>1.86</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
         <v>2.52</v>
@@ -811,52 +811,52 @@
         <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="H3" t="n">
         <v>1.71</v>
       </c>
       <c r="I3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
@@ -993,128 +993,128 @@
         <v>2.58</v>
       </c>
       <c r="T3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="AE3" t="n">
         <v>20</v>
       </c>
-      <c r="AB3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>18</v>
-      </c>
       <c r="AF3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AG3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH3" t="n">
         <v>20</v>
       </c>
-      <c r="AH3" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AI3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL3" t="n">
         <v>60</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN3" t="n">
         <v>55</v>
       </c>
-      <c r="AM3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR3" t="n">
         <v>9.6</v>
       </c>
-      <c r="AR3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AS3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT3" t="n">
         <v>16</v>
       </c>
-      <c r="AT3" t="n">
-        <v>18</v>
-      </c>
       <c r="AU3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY3" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>16</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>3.45</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H4" t="n">
         <v>1.84</v>
       </c>
       <c r="I4" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
         <v>5.3</v>
@@ -1178,7 +1178,7 @@
         <v>3.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
         <v>3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
         <v>4.7</v>
@@ -1548,7 +1548,7 @@
         <v>2.42</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G7" t="n">
         <v>3.2</v>
@@ -1736,7 +1736,7 @@
         <v>2.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
@@ -1760,7 +1760,7 @@
         <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
         <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J10" t="n">
         <v>3.95</v>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q10" t="n">
         <v>1.52</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
@@ -2730,7 +2730,7 @@
         <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G14" t="n">
         <v>2.62</v>
@@ -3094,7 +3094,7 @@
         <v>3.1</v>
       </c>
       <c r="I14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
@@ -3190,13 +3190,13 @@
         <v>30</v>
       </c>
       <c r="AO14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP14" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
         <v>18</v>
@@ -3217,7 +3217,7 @@
         <v>23</v>
       </c>
       <c r="AX14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
         <v>11</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G15" t="n">
         <v>1.86</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.88</v>
-      </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>4.8</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="I17" t="n">
         <v>1.76</v>
@@ -3682,7 +3682,7 @@
         <v>4.3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I18" t="n">
         <v>2.88</v>
@@ -3876,7 +3876,7 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>1.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H19" t="n">
         <v>2.9</v>
       </c>
-      <c r="G19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.64</v>
-      </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.18</v>
       </c>
       <c r="H22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>4.1</v>
@@ -4652,7 +4652,7 @@
         <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4706,7 +4706,7 @@
         <v>8.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
         <v>17</v>
@@ -4754,13 +4754,13 @@
         <v>23</v>
       </c>
       <c r="AS22" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AT22" t="n">
         <v>7.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV22" t="n">
         <v>14.5</v>
@@ -4775,10 +4775,10 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB22" t="n">
         <v>25</v>
@@ -4796,11 +4796,11 @@
         <v>18</v>
       </c>
       <c r="BG22" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>1.22</v>
       </c>
       <c r="G24" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="H24" t="n">
         <v>11.5</v>
       </c>
       <c r="I24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="J24" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
         <v>9.199999999999999</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>4.1</v>
       </c>
       <c r="H27" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I27" t="n">
         <v>2.18</v>
@@ -5646,7 +5646,7 @@
         <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T27" t="n">
         <v>1.82</v>
@@ -5688,7 +5688,7 @@
         <v>32</v>
       </c>
       <c r="AG27" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AH27" t="n">
         <v>18.5</v>
@@ -5724,13 +5724,13 @@
         <v>12</v>
       </c>
       <c r="AS27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
         <v>13</v>
       </c>
       <c r="AU27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
         <v>10</v>
@@ -5754,13 +5754,13 @@
         <v>40</v>
       </c>
       <c r="BC27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD27" t="n">
         <v>34</v>
       </c>
       <c r="BE27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF27" t="n">
         <v>29</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5810,13 +5810,13 @@
         <v>3.95</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q28" t="n">
         <v>2.38</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -787,7 +787,7 @@
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.86</v>
@@ -799,16 +799,16 @@
         <v>2.52</v>
       </c>
       <c r="T2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
         <v>1.48</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="H3" t="n">
         <v>1.71</v>
       </c>
       <c r="I3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
@@ -993,52 +993,52 @@
         <v>2.58</v>
       </c>
       <c r="T3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="W3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
       </c>
       <c r="Y3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z3" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z3" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AA3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB3" t="n">
         <v>25</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG3" t="n">
         <v>20</v>
       </c>
-      <c r="AF3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>22</v>
-      </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
@@ -1047,34 +1047,34 @@
         <v>65</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="n">
         <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
         <v>9.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
         <v>8</v>
@@ -1083,38 +1083,38 @@
         <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AY3" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
         <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>3.45</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="H4" t="n">
         <v>1.84</v>
       </c>
       <c r="I4" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="J4" t="n">
         <v>4.6</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H6" t="n">
         <v>3.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G7" t="n">
         <v>3.2</v>
@@ -1742,7 +1742,7 @@
         <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
         <v>1.58</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I10" t="n">
         <v>2.36</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
         <v>2.02</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H12" t="n">
         <v>3.2</v>
@@ -2709,7 +2709,7 @@
         <v>3.55</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
@@ -2730,7 +2730,7 @@
         <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I13" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
         <v>3.7</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>3.1</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
@@ -3145,7 +3145,7 @@
         <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
         <v>60</v>
@@ -3205,7 +3205,7 @@
         <v>28</v>
       </c>
       <c r="AT14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU14" t="n">
         <v>6.8</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H15" t="n">
-        <v>2.16</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>2.98</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H16" t="n">
         <v>2.48</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J16" t="n">
         <v>3.2</v>
@@ -3506,7 +3506,7 @@
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>4.8</v>
       </c>
       <c r="G17" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
         <v>1.69</v>
@@ -3700,7 +3700,7 @@
         <v>2.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G18" t="n">
         <v>3.75</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I18" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
         <v>3.35</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="G19" t="n">
         <v>3.4</v>
@@ -4064,7 +4064,7 @@
         <v>2.9</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>2.78</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -4649,10 +4649,10 @@
         <v>4.1</v>
       </c>
       <c r="J22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.45</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.5</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
         <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4694,7 +4694,7 @@
         <v>12</v>
       </c>
       <c r="Y22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
         <v>28</v>
@@ -4772,7 +4772,7 @@
         <v>11.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
         <v>17</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5028,19 +5028,19 @@
         <v>1.22</v>
       </c>
       <c r="G24" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="H24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="I24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J24" t="n">
         <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5640,16 +5640,16 @@
         <v>1.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
         <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U27" t="n">
         <v>2.14</v>
@@ -5667,7 +5667,7 @@
         <v>9.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA27" t="n">
         <v>27</v>
@@ -5724,13 +5724,13 @@
         <v>12</v>
       </c>
       <c r="AS27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="n">
         <v>13</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
         <v>10</v>
@@ -5760,7 +5760,7 @@
         <v>34</v>
       </c>
       <c r="BE27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF27" t="n">
         <v>29</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5807,16 +5807,16 @@
         <v>2.3</v>
       </c>
       <c r="H28" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>1.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH28"/>
+  <dimension ref="A1:BH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.48</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.44</v>
-      </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="H3" t="n">
         <v>1.71</v>
@@ -963,13 +963,13 @@
         <v>1.85</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -981,16 +981,16 @@
         <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
         <v>1.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.66</v>
@@ -1065,7 +1065,7 @@
         <v>9.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
         <v>16</v>
@@ -1077,22 +1077,22 @@
         <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
         <v>6.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
         <v>7.2</v>
@@ -1110,18 +1110,18 @@
         <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IBV</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1.99</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>3.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Radnicki Nis</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Javor Ivanjica</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="G5" t="n">
-        <v>870</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="I5" t="n">
-        <v>660</v>
+        <v>2.16</v>
       </c>
       <c r="J5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L5" t="n">
         <v>1.01</v>
       </c>
-      <c r="K5" t="n">
-        <v>950</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="P5" t="n">
-        <v>1.07</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.01</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Radnicki Nis</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>FK Javor Ivanjica</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>3.25</v>
+        <v>870</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>660</v>
       </c>
       <c r="J6" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.92</v>
+        <v>2.54</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>1.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>2.78</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.76</v>
+        <v>2.94</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="I8" t="n">
-        <v>5.3</v>
+        <v>2.36</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FK Napredak</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK IMT Novi Beograd</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>FK Napredak</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>FK IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.66</v>
+        <v>1.07</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>2.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>2.92</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I13" t="n">
         <v>2.66</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,61 +3076,61 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="G14" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="I14" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>2.64</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3139,123 +3139,123 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B93 Copenhagen</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="G15" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>AaB</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>B93 Copenhagen</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.8</v>
+        <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="H17" t="n">
-        <v>1.69</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.76</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,66 +3847,66 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="G18" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
         <v>3.35</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3915,123 +3915,123 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.92</v>
+        <v>4.7</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9</v>
+        <v>1.69</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>1.77</v>
       </c>
       <c r="J19" t="n">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.98</v>
+        <v>1.59</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,31 +4240,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="H20" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.07</v>
+        <v>1.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,31 +4434,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Backa Topola</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,61 +4628,61 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="G22" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="K22" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.77</v>
+        <v>1.07</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,17 +4817,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>FK Backa Topola</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q23" t="n">
         <v>1.01</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.22</v>
+        <v>2.16</v>
       </c>
       <c r="G24" t="n">
-        <v>1.26</v>
+        <v>2.2</v>
       </c>
       <c r="H24" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV24" t="n">
         <v>14.5</v>
       </c>
-      <c r="J24" t="n">
-        <v>8</v>
-      </c>
-      <c r="K24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,36 +5399,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>4.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,66 +5593,66 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -5661,310 +5661,698 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 09:02:28</t>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Hafnarfjordur</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-21 11:17:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-21 11:17:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Santa Fe</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F30" t="n">
         <v>2.06</v>
       </c>
-      <c r="G28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="G30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H30" t="n">
         <v>3.9</v>
       </c>
-      <c r="I28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="I30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.55</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2026-04-21 09:02:28</t>
+      <c r="Q30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-21 11:17:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH30"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>2.74</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -790,7 +790,7 @@
         <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
         <v>1.47</v>
@@ -805,10 +805,10 @@
         <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -823,10 +823,10 @@
         <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
@@ -847,7 +847,7 @@
         <v>40</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK2" t="n">
         <v>34</v>
@@ -859,7 +859,7 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -874,7 +874,7 @@
         <v>15.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
@@ -898,19 +898,19 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
         <v>16</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G3" t="n">
         <v>5.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -981,7 +981,7 @@
         <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
         <v>1.67</v>
@@ -996,49 +996,49 @@
         <v>1.66</v>
       </c>
       <c r="U3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB3" t="n">
         <v>25</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
@@ -1047,74 +1047,74 @@
         <v>65</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
         <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY3" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>16</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BC3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG3" t="n">
         <v>6.8</v>
       </c>
-      <c r="BD3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="I5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J5" t="n">
         <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,7 +1363,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="O5" t="n">
         <v>1.06</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="G6" t="n">
-        <v>870</v>
+        <v>2.16</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>660</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L6" t="n">
         <v>1.01</v>
       </c>
-      <c r="K6" t="n">
-        <v>950</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.07</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.01</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="H7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS7" t="n">
         <v>2.42</v>
       </c>
-      <c r="K7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.94</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I8" t="n">
         <v>2.36</v>
@@ -1939,152 +1939,152 @@
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
         <v>1.48</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2327,159 +2327,159 @@
         <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.07</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.01</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="G11" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BC11" t="n">
         <v>2.2</v>
       </c>
-      <c r="I11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="I12" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>2.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.06</v>
+        <v>1.52</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="H13" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="I13" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="J14" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="I15" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B93 Copenhagen</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,61 +3852,61 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>AaB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>B93 Copenhagen</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.58</v>
+        <v>1.75</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3915,123 +3915,123 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,66 +4041,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.7</v>
+        <v>2.58</v>
       </c>
       <c r="G19" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.69</v>
+        <v>3.15</v>
       </c>
       <c r="I19" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,31 +4240,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="G20" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="H20" t="n">
-        <v>2.52</v>
+        <v>1.69</v>
       </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>1.77</v>
       </c>
       <c r="J20" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6</v>
+        <v>2.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.34</v>
+        <v>1.58</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
@@ -4434,31 +4434,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="I21" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="J21" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,31 +4628,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H22" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,31 +4822,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Backa Topola</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="H23" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,61 +5016,61 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="K24" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.78</v>
+        <v>1.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5079,123 +5079,123 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,27 +5205,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>FK Backa Topola</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q25" t="n">
         <v>1.01</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,66 +5399,66 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.22</v>
+        <v>2.16</v>
       </c>
       <c r="G26" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="H26" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>9.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P26" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5467,123 +5467,123 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,36 +5593,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,36 +5787,36 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>4.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,66 +5981,66 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.93</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6049,310 +6049,698 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 11:17:25</t>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Hafnarfjordur</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-21 13:33:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-21 13:33:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Santa Fe</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F32" t="n">
         <v>2.06</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G32" t="n">
         <v>2.32</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H32" t="n">
         <v>3.9</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I32" t="n">
         <v>4.6</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J32" t="n">
         <v>3.05</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K32" t="n">
         <v>3.55</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q30" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2026-04-21 11:17:25</t>
+      <c r="Q32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-21 13:33:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,46 +757,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="G2" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="H2" t="n">
         <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
       </c>
       <c r="K2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
         <v>4.2</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="T2" t="n">
         <v>1.62</v>
@@ -808,7 +808,7 @@
         <v>1.57</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -954,16 +954,16 @@
         <v>4.4</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I3" t="n">
         <v>1.84</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
         <v>4.7</v>
@@ -978,7 +978,7 @@
         <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
         <v>2.32</v>
@@ -999,46 +999,46 @@
         <v>2.26</v>
       </c>
       <c r="V3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
       </c>
       <c r="AE3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG3" t="n">
         <v>20</v>
       </c>
-      <c r="AF3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>22</v>
-      </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
@@ -1047,58 +1047,58 @@
         <v>65</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT3" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
         <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BD3" t="n">
         <v>38</v>
@@ -1107,14 +1107,14 @@
         <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>1.71</v>
       </c>
       <c r="I5" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
         <v>4.2</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G6" t="n">
         <v>2.16</v>
       </c>
       <c r="H6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I6" t="n">
         <v>6.2</v>
@@ -1548,7 +1548,7 @@
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1560,7 +1560,7 @@
         <v>1.54</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
         <v>1.54</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
         <v>3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="J7" t="n">
         <v>2.74</v>
@@ -1751,40 +1751,40 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O7" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="S7" t="n">
         <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
         <v>8.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>30</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
         <v>20</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G8" t="n">
         <v>3.2</v>
@@ -1939,13 +1939,13 @@
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
@@ -1966,7 +1966,7 @@
         <v>1.54</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="V8" t="n">
         <v>1.73</v>
@@ -1975,25 +1975,25 @@
         <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AA8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB8" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>330</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
         <v>22</v>
@@ -2002,19 +2002,19 @@
         <v>25</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AI8" t="n">
         <v>29</v>
       </c>
       <c r="AJ8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
         <v>34</v>
@@ -2023,68 +2023,68 @@
         <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AO8" t="n">
-        <v>85</v>
+        <v>970</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AV8" t="n">
         <v>10</v>
       </c>
       <c r="AW8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="BD8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BF8" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7</v>
-      </c>
       <c r="BG8" t="n">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2133,16 @@
         <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
@@ -2151,16 +2151,16 @@
         <v>1.66</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
         <v>1.27</v>
@@ -2178,7 +2178,7 @@
         <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB9" t="n">
         <v>12</v>
@@ -2220,7 +2220,7 @@
         <v>9.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AP9" t="n">
         <v>18</v>
@@ -2229,10 +2229,10 @@
         <v>17</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
         <v>9.800000000000001</v>
@@ -2244,7 +2244,7 @@
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2256,7 +2256,7 @@
         <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
         <v>17.5</v>
@@ -2265,20 +2265,20 @@
         <v>15</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
         <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>1.71</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,35 +2333,35 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.07</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X10" t="n">
         <v>1000</v>
       </c>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -2503,37 +2503,37 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="I11" t="n">
         <v>2.02</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="O11" t="n">
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q11" t="n">
         <v>1.58</v>
@@ -2542,19 +2542,19 @@
         <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V11" t="n">
         <v>1.98</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -2608,65 +2608,65 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.97</v>
+        <v>2.36</v>
       </c>
       <c r="AR11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.16</v>
+        <v>2.66</v>
       </c>
       <c r="AY11" t="n">
         <v>14</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.26</v>
+        <v>5.9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I12" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="J12" t="n">
         <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P12" t="n">
         <v>2.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H13" t="n">
         <v>2.38</v>
       </c>
       <c r="I13" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
@@ -2909,152 +2909,152 @@
         <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS13" t="n">
         <v>2.08</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="G14" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I14" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AR15" t="n">
         <v>2.46</v>
       </c>
-      <c r="G15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="AS15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT15" t="n">
         <v>2.28</v>
       </c>
-      <c r="I15" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.14</v>
+        <v>2.96</v>
       </c>
       <c r="G16" t="n">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>2.64</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -3685,152 +3685,152 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -3879,152 +3879,152 @@
         <v>4.7</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P18" t="n">
         <v>2.5</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.5</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>2.58</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H19" t="n">
         <v>3.15</v>
@@ -4073,7 +4073,7 @@
         <v>3.35</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -4094,7 +4094,7 @@
         <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
         <v>1.9</v>
@@ -4103,19 +4103,19 @@
         <v>2.04</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="n">
         <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA19" t="n">
         <v>55</v>
@@ -4127,37 +4127,37 @@
         <v>7.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE19" t="n">
         <v>40</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
         <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL19" t="n">
         <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO19" t="n">
         <v>40</v>
@@ -4166,43 +4166,43 @@
         <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
         <v>18.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AT19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
         <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AX19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY19" t="n">
         <v>11</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BC19" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="BD19" t="n">
         <v>27</v>
@@ -4214,18 +4214,18 @@
         <v>25</v>
       </c>
       <c r="BG19" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.7</v>
+        <v>2.14</v>
       </c>
       <c r="G20" t="n">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="H20" t="n">
-        <v>1.69</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.77</v>
+        <v>4.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P20" t="n">
-        <v>2.46</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.58</v>
+        <v>2.18</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>FK Backa Topola</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>2.52</v>
+        <v>1.35</v>
       </c>
       <c r="I21" t="n">
-        <v>2.96</v>
+        <v>2.22</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
         <v>1.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9</v>
+        <v>1.28</v>
       </c>
       <c r="I22" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="J22" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.98</v>
+        <v>1.87</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.68</v>
+        <v>5.6</v>
       </c>
       <c r="G23" t="n">
-        <v>1.84</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>4.9</v>
+        <v>1.65</v>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>1.69</v>
       </c>
       <c r="J23" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P24" t="n">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Backa Topola</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>3.05</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P25" t="n">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="J26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.35</v>
       </c>
-      <c r="K26" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>1.62</v>
       </c>
       <c r="O26" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>1.77</v>
       </c>
       <c r="J27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="G28" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="H28" t="n">
-        <v>13</v>
+        <v>1.95</v>
       </c>
       <c r="I28" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>8</v>
+        <v>3.75</v>
       </c>
       <c r="K28" t="n">
-        <v>9.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P28" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,36 +5981,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,36 +6175,36 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,11 +6219,11 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,66 +6369,66 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.93</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6437,310 +6437,698 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 13:33:08</t>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Hafnarfjordur</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-21 15:48:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-21 15:48:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Santa Fe</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F34" t="n">
         <v>2.06</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G34" t="n">
         <v>2.32</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H34" t="n">
         <v>3.9</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I34" t="n">
         <v>4.6</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J34" t="n">
         <v>3.05</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K34" t="n">
         <v>3.55</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q34" t="n">
         <v>2.38</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-04-21 13:33:08</t>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-21 15:48:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -793,7 +793,7 @@
         <v>1.63</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
         <v>2.52</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.27</v>
@@ -987,22 +987,22 @@
         <v>1.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S3" t="n">
         <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
         <v>2.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
@@ -1011,7 +1011,7 @@
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
         <v>20</v>
@@ -1056,16 +1056,16 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AP3" t="n">
         <v>18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
         <v>16</v>
@@ -1074,19 +1074,19 @@
         <v>17.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
@@ -1095,10 +1095,10 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
         <v>38</v>
@@ -1107,14 +1107,14 @@
         <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H7" t="n">
         <v>3.05</v>
       </c>
-      <c r="H7" t="n">
-        <v>3.2</v>
-      </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.74</v>
+        <v>2.12</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.63</v>
@@ -1751,16 +1751,16 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.39</v>
+        <v>2.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="P7" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="R7" t="n">
         <v>1.12</v>
@@ -1769,16 +1769,16 @@
         <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
         <v>1.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
         <v>8.6</v>
@@ -1793,7 +1793,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>9.6</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
         <v>20</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AT7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU7" t="n">
         <v>2.16</v>
       </c>
-      <c r="AU7" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AV7" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.96</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H8" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I8" t="n">
         <v>2.36</v>
@@ -1954,7 +1954,7 @@
         <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
         <v>1.59</v>
@@ -1972,7 +1972,7 @@
         <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X8" t="n">
         <v>29</v>
@@ -1987,7 +1987,7 @@
         <v>38</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC8" t="n">
         <v>970</v>
@@ -2029,62 +2029,62 @@
         <v>970</v>
       </c>
       <c r="AP8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS8" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>3.7</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AV8" t="n">
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA8" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8</v>
-      </c>
       <c r="BB8" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H9" t="n">
         <v>4.3</v>
@@ -2166,7 +2166,7 @@
         <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X9" t="n">
         <v>23</v>
@@ -2271,14 +2271,14 @@
         <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG9" t="n">
         <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="I10" t="n">
         <v>1.71</v>
@@ -2324,13 +2324,13 @@
         <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
         <v>3.4</v>
@@ -2339,10 +2339,10 @@
         <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
         <v>1.09</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G11" t="n">
         <v>6.4</v>
@@ -2512,10 +2512,10 @@
         <v>1.63</v>
       </c>
       <c r="I11" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="J11" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -2548,10 +2548,10 @@
         <v>1.53</v>
       </c>
       <c r="U11" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="W11" t="n">
         <v>1.18</v>
@@ -2584,7 +2584,7 @@
         <v>55</v>
       </c>
       <c r="AG11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AH11" t="n">
         <v>25</v>
@@ -2596,7 +2596,7 @@
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL11" t="n">
         <v>75</v>
@@ -2611,62 +2611,62 @@
         <v>12.5</v>
       </c>
       <c r="AP11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS11" t="n">
         <v>2.54</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AT11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV11" t="n">
         <v>2.36</v>
       </c>
-      <c r="AR11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS11" t="n">
+      <c r="AW11" t="n">
         <v>2.52</v>
       </c>
-      <c r="AT11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AX11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AY11" t="n">
         <v>14</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BG11" t="n">
         <v>5.9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
         <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I12" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J12" t="n">
         <v>3.95</v>
@@ -2727,7 +2727,7 @@
         <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q12" t="n">
         <v>1.51</v>
@@ -2745,7 +2745,7 @@
         <v>2.66</v>
       </c>
       <c r="V12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W12" t="n">
         <v>1.44</v>
@@ -2757,7 +2757,7 @@
         <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA12" t="n">
         <v>32</v>
@@ -2844,13 +2844,13 @@
         <v>7.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF12" t="n">
         <v>13</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>2.54</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
         <v>3.6</v>
@@ -2915,16 +2915,16 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O13" t="n">
         <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R13" t="n">
         <v>1.29</v>
@@ -2933,16 +2933,16 @@
         <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U13" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
         <v>1.66</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2978,13 +2978,13 @@
         <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
         <v>90</v>
       </c>
       <c r="AK13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL13" t="n">
         <v>70</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AS13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AW13" t="n">
         <v>2.08</v>
       </c>
-      <c r="AT13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>2.06</v>
       </c>
-      <c r="AX13" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AY13" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BB13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BC13" t="n">
         <v>2.12</v>
       </c>
-      <c r="BC13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BD13" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="G14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J14" t="n">
         <v>3.4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>3.85</v>
@@ -3106,34 +3106,34 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W14" t="n">
         <v>1.43</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="AQ14" t="n">
         <v>2.14</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AX14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.28</v>
       </c>
       <c r="BA14" t="n">
         <v>2.42</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H15" t="n">
         <v>3.2</v>
@@ -3291,7 +3291,7 @@
         <v>3.55</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -3303,7 +3303,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="O15" t="n">
         <v>1.25</v>
@@ -3315,10 +3315,10 @@
         <v>1.79</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="T15" t="n">
         <v>1.58</v>
@@ -3330,7 +3330,7 @@
         <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
         <v>21</v>
@@ -3390,49 +3390,49 @@
         <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AV15" t="n">
         <v>2.32</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AX15" t="n">
         <v>10.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BB15" t="n">
         <v>2.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BD15" t="n">
         <v>2.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BF15" t="n">
         <v>2.66</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G16" t="n">
         <v>3.15</v>
       </c>
       <c r="H16" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I16" t="n">
         <v>2.64</v>
@@ -3488,7 +3488,7 @@
         <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,7 +3497,7 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
         <v>1.3</v>
@@ -3506,13 +3506,13 @@
         <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="R16" t="n">
         <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.76</v>
@@ -3539,7 +3539,7 @@
         <v>50</v>
       </c>
       <c r="AB16" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
         <v>11</v>
@@ -3566,7 +3566,7 @@
         <v>70</v>
       </c>
       <c r="AK16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
         <v>65</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="AR16" t="n">
         <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="AT16" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AW16" t="n">
         <v>19.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AY16" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -3882,31 +3882,31 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
         <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P18" t="n">
         <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>1.58</v>
+        <v>2.28</v>
       </c>
       <c r="T18" t="n">
         <v>1.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
         <v>1.23</v>
@@ -3963,22 +3963,22 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
         <v>14</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AT18" t="n">
         <v>8</v>
@@ -3990,7 +3990,7 @@
         <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AX18" t="n">
         <v>8.4</v>
@@ -4002,7 +4002,7 @@
         <v>10.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
@@ -4014,17 +4014,17 @@
         <v>16.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -4058,28 +4058,28 @@
         <v>2.58</v>
       </c>
       <c r="G19" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I19" t="n">
         <v>3.15</v>
       </c>
-      <c r="I19" t="n">
-        <v>3.2</v>
-      </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.4</v>
@@ -4088,7 +4088,7 @@
         <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R19" t="n">
         <v>1.29</v>
@@ -4103,13 +4103,13 @@
         <v>2.04</v>
       </c>
       <c r="V19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y19" t="n">
         <v>11</v>
@@ -4151,10 +4151,10 @@
         <v>30</v>
       </c>
       <c r="AL19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN19" t="n">
         <v>28</v>
@@ -4196,7 +4196,7 @@
         <v>17.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB19" t="n">
         <v>34</v>
@@ -4205,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="BD19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE19" t="n">
         <v>40</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -4261,13 +4261,13 @@
         <v>4.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
         <v>3.45</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
@@ -4282,16 +4282,16 @@
         <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R20" t="n">
         <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
         <v>2</v>
@@ -4372,7 +4372,7 @@
         <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
         <v>15</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.85</v>
+        <v>4.5</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="I21" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>950</v>
@@ -4467,7 +4467,7 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="O21" t="n">
         <v>1.36</v>
@@ -4479,10 +4479,10 @@
         <v>2.04</v>
       </c>
       <c r="R21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S21" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4491,7 +4491,7 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -4643,16 +4643,16 @@
         <v>4.8</v>
       </c>
       <c r="H22" t="n">
-        <v>1.28</v>
+        <v>1.96</v>
       </c>
       <c r="I22" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="J22" t="n">
         <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4685,7 +4685,7 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="W22" t="n">
         <v>1.26</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v>4.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -4861,7 +4861,7 @@
         <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q23" t="n">
         <v>2.02</v>
@@ -4870,7 +4870,7 @@
         <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
         <v>2</v>
@@ -4882,7 +4882,7 @@
         <v>2.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X23" t="n">
         <v>14</v>
@@ -4975,7 +4975,7 @@
         <v>28</v>
       </c>
       <c r="BB23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC23" t="n">
         <v>13.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G24" t="n">
         <v>1.84</v>
@@ -5034,7 +5034,7 @@
         <v>4.9</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J24" t="n">
         <v>3.8</v>
@@ -5043,7 +5043,7 @@
         <v>4.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -5067,10 +5067,10 @@
         <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V24" t="n">
         <v>1.2</v>
@@ -5115,7 +5115,7 @@
         <v>75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AK24" t="n">
         <v>21</v>
@@ -5139,10 +5139,10 @@
         <v>15</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT24" t="n">
         <v>7.8</v>
@@ -5154,7 +5154,7 @@
         <v>17.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX24" t="n">
         <v>9</v>
@@ -5163,10 +5163,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB24" t="n">
         <v>15</v>
@@ -5175,20 +5175,20 @@
         <v>14.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF24" t="n">
         <v>7.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5222,13 @@
         <v>2.94</v>
       </c>
       <c r="G25" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H25" t="n">
         <v>2.9</v>
       </c>
       <c r="I25" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
         <v>2.78</v>
@@ -5240,10 +5240,10 @@
         <v>1.6</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>1.43</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
         <v>1.6</v>
@@ -5255,134 +5255,134 @@
         <v>2.98</v>
       </c>
       <c r="R25" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA25" t="n">
         <v>9</v>
       </c>
-      <c r="Y25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="BB25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE25" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>2.92</v>
-      </c>
       <c r="BF25" t="n">
-        <v>2.92</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.92</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -5416,37 +5416,37 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="H26" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="I26" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="J26" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>3.35</v>
       </c>
       <c r="L26" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O26" t="n">
         <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
@@ -5458,13 +5458,13 @@
         <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V26" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5521,52 +5521,52 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -5625,10 +5625,10 @@
         <v>4.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N27" t="n">
         <v>2.46</v>
@@ -5640,19 +5640,19 @@
         <v>2.46</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R27" t="n">
         <v>1.51</v>
       </c>
       <c r="S27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U27" t="n">
         <v>2.18</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.16</v>
       </c>
       <c r="V27" t="n">
         <v>2.28</v>
@@ -5661,7 +5661,7 @@
         <v>1.23</v>
       </c>
       <c r="X27" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y27" t="n">
         <v>18</v>
@@ -5712,65 +5712,65 @@
         <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.99</v>
+        <v>2.48</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.88</v>
+        <v>2.32</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AX27" t="n">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.96</v>
+        <v>2.44</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.04</v>
+        <v>2.58</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.04</v>
+        <v>2.58</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -5807,16 +5807,16 @@
         <v>2.1</v>
       </c>
       <c r="H28" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="J28" t="n">
         <v>3.75</v>
       </c>
       <c r="K28" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5837,7 +5837,7 @@
         <v>1.57</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
         <v>2.36</v>
@@ -5849,7 +5849,7 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W28" t="n">
         <v>1.9</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="H29" t="n">
         <v>1.04</v>
@@ -6013,152 +6013,152 @@
         <v>950</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>1.22</v>
       </c>
       <c r="G30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H30" t="n">
         <v>13</v>
@@ -6201,158 +6201,158 @@
         <v>14</v>
       </c>
       <c r="J30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="K30" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -6401,16 +6401,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P31" t="n">
         <v>1.24</v>
@@ -6419,134 +6419,134 @@
         <v>1.01</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -6595,152 +6595,152 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -6786,10 +6786,10 @@
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
@@ -6801,10 +6801,10 @@
         <v>1.33</v>
       </c>
       <c r="P33" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
         <v>1.36</v>
@@ -6819,19 +6819,19 @@
         <v>2.14</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y33" t="n">
         <v>9.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
         <v>26</v>
@@ -6843,16 +6843,16 @@
         <v>7.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE33" t="n">
         <v>23</v>
       </c>
       <c r="AF33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG33" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH33" t="n">
         <v>17.5</v>
@@ -6861,19 +6861,19 @@
         <v>38</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL33" t="n">
         <v>60</v>
       </c>
       <c r="AM33" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO33" t="n">
         <v>16.5</v>
@@ -6882,19 +6882,19 @@
         <v>12</v>
       </c>
       <c r="AQ33" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR33" t="n">
         <v>12</v>
       </c>
       <c r="AS33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT33" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV33" t="n">
         <v>10</v>
@@ -6903,25 +6903,25 @@
         <v>20</v>
       </c>
       <c r="AX33" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AY33" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BB33" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BC33" t="n">
         <v>26</v>
       </c>
       <c r="BD33" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BE33" t="n">
         <v>38</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>2.06</v>
       </c>
       <c r="G34" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H34" t="n">
         <v>3.9</v>
@@ -6995,10 +6995,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-21 15:48:56</t>
+          <t>2026-04-21 18:03:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,16 +760,16 @@
         <v>2.68</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H2" t="n">
         <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
@@ -799,13 +799,13 @@
         <v>2.52</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
         <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W2" t="n">
         <v>1.52</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -957,13 +957,13 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I3" t="n">
         <v>1.83</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
@@ -978,13 +978,13 @@
         <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R3" t="n">
         <v>1.54</v>
@@ -993,7 +993,7 @@
         <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
         <v>2.3</v>
@@ -1008,7 +1008,7 @@
         <v>26</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z3" t="n">
         <v>13</v>
@@ -1017,7 +1017,7 @@
         <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
@@ -1056,7 +1056,7 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP3" t="n">
         <v>18</v>
@@ -1083,7 +1083,7 @@
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY3" t="n">
         <v>16</v>
@@ -1095,10 +1095,10 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC3" t="n">
         <v>8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
         <v>38</v>
@@ -1107,14 +1107,14 @@
         <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
         <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="G6" t="n">
         <v>2.16</v>
       </c>
       <c r="H6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
         <v>6.2</v>
@@ -1548,7 +1548,7 @@
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="G7" t="n">
         <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.63</v>
@@ -1778,7 +1778,7 @@
         <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
         <v>8.6</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>3.25</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -2309,46 +2309,46 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="I10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.71</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.67</v>
       </c>
       <c r="R10" t="n">
         <v>1.09</v>
       </c>
       <c r="S10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2357,10 +2357,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G11" t="n">
         <v>6.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="I11" t="n">
         <v>1.92</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
         <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
         <v>1.77</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>2.48</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
@@ -3118,7 +3118,7 @@
         <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
         <v>1.29</v>
@@ -3133,7 +3133,7 @@
         <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W14" t="n">
         <v>1.43</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H15" t="n">
         <v>3.2</v>
@@ -3291,7 +3291,7 @@
         <v>3.55</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -3303,7 +3303,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="O15" t="n">
         <v>1.25</v>
@@ -3318,7 +3318,7 @@
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
         <v>1.58</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G16" t="n">
         <v>3.15</v>
@@ -3497,22 +3497,22 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
         <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
         <v>1.76</v>
@@ -3590,7 +3590,7 @@
         <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AT16" t="n">
         <v>1.94</v>
@@ -3599,13 +3599,13 @@
         <v>1.65</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AW16" t="n">
         <v>19.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AY16" t="n">
         <v>1.76</v>
@@ -3617,7 +3617,7 @@
         <v>1.88</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BC16" t="n">
         <v>1.94</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -3888,13 +3888,13 @@
         <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P18" t="n">
         <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="R18" t="n">
         <v>1.53</v>
@@ -3903,10 +3903,10 @@
         <v>2.28</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
         <v>1.23</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H19" t="n">
         <v>3.1</v>
@@ -4106,7 +4106,7 @@
         <v>1.46</v>
       </c>
       <c r="W19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X19" t="n">
         <v>11.5</v>
@@ -4130,7 +4130,7 @@
         <v>13.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF19" t="n">
         <v>15.5</v>
@@ -4148,7 +4148,7 @@
         <v>38</v>
       </c>
       <c r="AK19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
         <v>48</v>
@@ -4157,7 +4157,7 @@
         <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO19" t="n">
         <v>40</v>
@@ -4187,7 +4187,7 @@
         <v>34</v>
       </c>
       <c r="AX19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
         <v>11</v>
@@ -4199,13 +4199,13 @@
         <v>48</v>
       </c>
       <c r="BB19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC19" t="n">
         <v>27</v>
       </c>
       <c r="BD19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE19" t="n">
         <v>40</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G20" t="n">
         <v>2.18</v>
@@ -4258,10 +4258,10 @@
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
         <v>3.45</v>
@@ -4273,25 +4273,25 @@
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
         <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
         <v>2</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -4446,40 +4446,40 @@
         <v>4.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="I21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J21" t="n">
         <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="S21" t="n">
         <v>1.98</v>
@@ -4491,10 +4491,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="G22" t="n">
-        <v>4.8</v>
+        <v>1.84</v>
       </c>
       <c r="H22" t="n">
-        <v>1.96</v>
+        <v>4.9</v>
       </c>
       <c r="I22" t="n">
-        <v>2.64</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.05</v>
       </c>
-      <c r="K22" t="n">
+      <c r="T22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR22" t="n">
         <v>6.4</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -4855,28 +4855,28 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U23" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V23" t="n">
         <v>2.44</v>
@@ -4903,10 +4903,10 @@
         <v>9.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF23" t="n">
         <v>50</v>
@@ -4915,7 +4915,7 @@
         <v>24</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>40</v>
@@ -4930,13 +4930,13 @@
         <v>95</v>
       </c>
       <c r="AM23" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>12.5</v>
@@ -4945,10 +4945,10 @@
         <v>6.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AT23" t="n">
         <v>16</v>
@@ -4960,48 +4960,48 @@
         <v>9</v>
       </c>
       <c r="AW23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>20</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>21</v>
-      </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BB23" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BE23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BF23" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>1.84</v>
+        <v>4.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.9</v>
+        <v>1.98</v>
       </c>
       <c r="I24" t="n">
-        <v>5.9</v>
+        <v>2.66</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>1.61</v>
       </c>
       <c r="O24" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>1.93</v>
       </c>
       <c r="T24" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="W24" t="n">
-        <v>2.18</v>
+        <v>1.27</v>
       </c>
       <c r="X24" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>2.9</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J25" t="n">
         <v>2.78</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H26" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I26" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,7 +5437,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="O26" t="n">
         <v>1.44</v>
@@ -5446,7 +5446,7 @@
         <v>1.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
@@ -5458,10 +5458,10 @@
         <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.36</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
         <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="T27" t="n">
         <v>1.55</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -5807,10 +5807,10 @@
         <v>2.1</v>
       </c>
       <c r="H28" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="I28" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
         <v>3.75</v>
@@ -5834,13 +5834,13 @@
         <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="R28" t="n">
         <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5849,7 +5849,7 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
         <v>1.9</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
         <v>48</v>
@@ -6007,7 +6007,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
         <v>950</v>
@@ -6019,7 +6019,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="O29" t="n">
         <v>1.06</v>
@@ -6028,13 +6028,13 @@
         <v>1.52</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="R29" t="n">
         <v>1.52</v>
       </c>
       <c r="S29" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -6192,13 +6192,13 @@
         <v>1.22</v>
       </c>
       <c r="G30" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="H30" t="n">
         <v>13</v>
       </c>
       <c r="I30" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J30" t="n">
         <v>7.8</v>
@@ -6216,7 +6216,7 @@
         <v>10</v>
       </c>
       <c r="O30" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P30" t="n">
         <v>4.4</v>
@@ -6240,7 +6240,7 @@
         <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6261,7 +6261,7 @@
         <v>26</v>
       </c>
       <c r="AD30" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
@@ -6309,13 +6309,13 @@
         <v>4</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AU30" t="n">
         <v>17</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW30" t="n">
         <v>4</v>
@@ -6345,14 +6345,14 @@
         <v>3.95</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BG30" t="n">
         <v>4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O32" t="n">
         <v>1.09</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
         <v>2.14</v>
       </c>
       <c r="I33" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
@@ -6789,13 +6789,13 @@
         <v>3.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O33" t="n">
         <v>1.33</v>
@@ -6804,22 +6804,22 @@
         <v>1.94</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R33" t="n">
         <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U33" t="n">
         <v>2.14</v>
       </c>
       <c r="V33" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W33" t="n">
         <v>1.33</v>
@@ -6921,214 +6921,408 @@
         <v>26</v>
       </c>
       <c r="BD33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE33" t="n">
         <v>38</v>
       </c>
       <c r="BF33" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BG33" t="n">
         <v>14.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 18:03:56</t>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:18:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Santa Fe</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F35" t="n">
         <v>2.06</v>
       </c>
-      <c r="G34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="G35" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H35" t="n">
         <v>3.9</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>4.6</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>3.05</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K35" t="n">
         <v>3.55</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="L35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="O35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q35" t="n">
         <v>2.36</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-04-21 18:03:56</t>
+      <c r="R35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:18:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H2" t="n">
         <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -778,7 +778,7 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
         <v>4.2</v>
@@ -796,7 +796,7 @@
         <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T2" t="n">
         <v>1.63</v>
@@ -805,7 +805,7 @@
         <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
         <v>1.52</v>
@@ -814,7 +814,7 @@
         <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
         <v>22</v>
@@ -898,10 +898,10 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC2" t="n">
         <v>4.6</v>
@@ -910,7 +910,7 @@
         <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
         <v>16</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>4.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I3" t="n">
         <v>1.83</v>
@@ -969,7 +969,7 @@
         <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -981,7 +981,7 @@
         <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
         <v>1.65</v>
@@ -993,7 +993,7 @@
         <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
         <v>2.3</v>
@@ -1110,11 +1110,11 @@
         <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2802,10 +2802,10 @@
         <v>18.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>13.5</v>
@@ -2814,7 +2814,7 @@
         <v>16</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT12" t="n">
         <v>16</v>
@@ -2838,19 +2838,19 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
         <v>13</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2897,10 +2897,10 @@
         <v>3.45</v>
       </c>
       <c r="H13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I13" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
@@ -2915,10 +2915,10 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>1.87</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P13" t="n">
         <v>1.87</v>
@@ -2927,7 +2927,7 @@
         <v>2.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
         <v>3.35</v>
@@ -2942,7 +2942,7 @@
         <v>1.66</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -3094,13 +3094,13 @@
         <v>2.48</v>
       </c>
       <c r="I14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3139,7 +3139,7 @@
         <v>1.43</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="n">
         <v>14.5</v>
@@ -3199,13 +3199,13 @@
         <v>2.14</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
@@ -3223,7 +3223,7 @@
         <v>2.24</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BA14" t="n">
         <v>2.42</v>
@@ -3235,20 +3235,20 @@
         <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BE14" t="n">
         <v>2.52</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H15" t="n">
         <v>3.2</v>
@@ -3291,7 +3291,7 @@
         <v>3.55</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -3315,10 +3315,10 @@
         <v>1.79</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="T15" t="n">
         <v>1.58</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -3497,13 +3497,13 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
         <v>1.91</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
         <v>48</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
@@ -4214,11 +4214,11 @@
         <v>25</v>
       </c>
       <c r="BG19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
         <v>4.1</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
         <v>3.45</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4679,10 +4679,10 @@
         <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V22" t="n">
         <v>1.2</v>
@@ -4766,7 +4766,7 @@
         <v>17.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX22" t="n">
         <v>9</v>
@@ -4775,10 +4775,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB22" t="n">
         <v>15</v>
@@ -4787,10 +4787,10 @@
         <v>14.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF22" t="n">
         <v>7.6</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
         <v>1.34</v>
@@ -4960,10 +4960,10 @@
         <v>9</v>
       </c>
       <c r="AW23" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY23" t="n">
         <v>19.5</v>
@@ -4975,26 +4975,26 @@
         <v>34</v>
       </c>
       <c r="BB23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC23" t="n">
         <v>15</v>
       </c>
       <c r="BD23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF23" t="n">
         <v>15</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>15.5</v>
       </c>
       <c r="BG23" t="n">
         <v>9.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -5052,19 +5052,19 @@
         <v>1.61</v>
       </c>
       <c r="O24" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P24" t="n">
         <v>1.61</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="R24" t="n">
         <v>1.07</v>
       </c>
       <c r="S24" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -5416,10 +5416,10 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="H26" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I26" t="n">
         <v>3</v>
@@ -5437,16 +5437,16 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="O26" t="n">
         <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
@@ -5464,7 +5464,7 @@
         <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G30" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="H30" t="n">
         <v>13</v>
@@ -6213,10 +6213,10 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O30" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P30" t="n">
         <v>4.4</v>
@@ -6225,134 +6225,134 @@
         <v>1.25</v>
       </c>
       <c r="R30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U30" t="n">
         <v>2.34</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.12</v>
       </c>
       <c r="V30" t="n">
         <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Y30" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AB30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AD30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF30" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK30" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP30" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.4</v>
+        <v>17.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BB30" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE30" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="BG30" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H33" t="n">
         <v>2.14</v>
@@ -6783,7 +6783,7 @@
         <v>2.16</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
         <v>3.6</v>
@@ -6792,7 +6792,7 @@
         <v>1.43</v>
       </c>
       <c r="M33" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N33" t="n">
         <v>3.85</v>
@@ -6840,13 +6840,13 @@
         <v>14.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD33" t="n">
         <v>10.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF33" t="n">
         <v>28</v>
@@ -6864,10 +6864,10 @@
         <v>80</v>
       </c>
       <c r="AK33" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM33" t="n">
         <v>100</v>
@@ -6927,14 +6927,14 @@
         <v>38</v>
       </c>
       <c r="BF33" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BG33" t="n">
         <v>14.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6965,52 +6965,52 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H34" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I34" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
         <v>3.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N34" t="n">
-        <v>1.56</v>
+        <v>2.7</v>
       </c>
       <c r="O34" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="P34" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q34" t="n">
         <v>2.58</v>
       </c>
       <c r="R34" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>2.58</v>
+        <v>5.3</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V34" t="n">
         <v>1.71</v>
@@ -7019,116 +7019,116 @@
         <v>1.32</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
         <v>3.55</v>
       </c>
       <c r="L35" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
@@ -7192,7 +7192,7 @@
         <v>1.61</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R35" t="n">
         <v>1.17</v>
@@ -7267,52 +7267,52 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH35"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="G2" t="n">
         <v>2.92</v>
@@ -766,58 +766,58 @@
         <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
         <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="U2" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
         <v>1.52</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
         <v>42</v>
@@ -826,10 +826,10 @@
         <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>30</v>
@@ -838,7 +838,7 @@
         <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>18</v>
@@ -874,16 +874,16 @@
         <v>15.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
         <v>21</v>
@@ -895,32 +895,32 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
         <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G3" t="n">
         <v>5.1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="I3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
@@ -978,7 +978,7 @@
         <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
         <v>2.32</v>
@@ -996,7 +996,7 @@
         <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V3" t="n">
         <v>2.2</v>
@@ -1017,7 +1017,7 @@
         <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
@@ -1083,7 +1083,7 @@
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
         <v>16</v>
@@ -1095,10 +1095,10 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD3" t="n">
         <v>38</v>
@@ -1107,14 +1107,14 @@
         <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
         <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1342,19 @@
         <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1372,10 +1372,10 @@
         <v>3.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S5" t="n">
         <v>1.6</v>
@@ -1390,7 +1390,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AR7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AV7" t="n">
         <v>2.56</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.5</v>
       </c>
       <c r="AW7" t="n">
         <v>2.78</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
         <v>6.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -2721,25 +2721,25 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="Q12" t="n">
         <v>1.51</v>
       </c>
       <c r="R12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U12" t="n">
         <v>2.66</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AaB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>B93 Copenhagen</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="G13" t="n">
-        <v>3.45</v>
+        <v>1.83</v>
       </c>
       <c r="H13" t="n">
-        <v>2.36</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>2.52</v>
+        <v>5.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>2.28</v>
       </c>
       <c r="T13" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
         <v>17.5</v>
       </c>
       <c r="AC13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC13" t="n">
         <v>11</v>
       </c>
-      <c r="AD13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BD13" t="n">
-        <v>2.14</v>
+        <v>16.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,112 +3076,112 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>3.55</v>
+        <v>1.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3193,69 +3193,69 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.18</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.28</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.42</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.42</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I15" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.79</v>
+        <v>2.22</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>2.86</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW15" t="n">
         <v>34</v>
       </c>
-      <c r="AA15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AX15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE15" t="n">
         <v>40</v>
       </c>
-      <c r="AK15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BF15" t="n">
-        <v>2.66</v>
+        <v>25</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.66</v>
+        <v>36</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.94</v>
+        <v>2.16</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="H16" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.64</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>2.16</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>1.79</v>
       </c>
       <c r="T16" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
         <v>15</v>
       </c>
-      <c r="Z16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>2.48</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.94</v>
+        <v>9.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="AW16" t="n">
-        <v>19.5</v>
+        <v>2.54</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.83</v>
+        <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.76</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.88</v>
+        <v>2.54</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.94</v>
+        <v>18</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.94</v>
+        <v>2.66</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.94</v>
+        <v>2.66</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,112 +3658,112 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>1.15</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3775,69 +3775,69 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B93 Copenhagen</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.75</v>
+        <v>2.96</v>
       </c>
       <c r="G18" t="n">
-        <v>1.83</v>
+        <v>3.15</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>2.46</v>
       </c>
       <c r="I18" t="n">
-        <v>5.3</v>
+        <v>2.62</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="X18" t="n">
-        <v>34</v>
+        <v>17.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AW18" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AX18" t="n">
-        <v>8.4</v>
+        <v>2.06</v>
       </c>
       <c r="AY18" t="n">
-        <v>7</v>
+        <v>1.98</v>
       </c>
       <c r="AZ18" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="BB18" t="n">
-        <v>12.5</v>
+        <v>2.14</v>
       </c>
       <c r="BC18" t="n">
-        <v>11</v>
+        <v>2.22</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.5</v>
+        <v>2.14</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.3</v>
+        <v>2.22</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="G19" t="n">
-        <v>2.62</v>
+        <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="I19" t="n">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="J19" t="n">
         <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="W19" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="X19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC19" t="n">
         <v>11</v>
       </c>
-      <c r="Z19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AD19" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AM19" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>10.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.5</v>
+        <v>1.91</v>
       </c>
       <c r="AR19" t="n">
-        <v>18.5</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>48</v>
+        <v>2.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>1.96</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>1.84</v>
       </c>
       <c r="AV19" t="n">
-        <v>12.5</v>
+        <v>1.95</v>
       </c>
       <c r="AW19" t="n">
-        <v>34</v>
+        <v>2.08</v>
       </c>
       <c r="AX19" t="n">
-        <v>14</v>
+        <v>2.06</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>1.99</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17.5</v>
+        <v>2.02</v>
       </c>
       <c r="BA19" t="n">
-        <v>48</v>
+        <v>2.12</v>
       </c>
       <c r="BB19" t="n">
-        <v>32</v>
+        <v>2.14</v>
       </c>
       <c r="BC19" t="n">
-        <v>27</v>
+        <v>2.12</v>
       </c>
       <c r="BD19" t="n">
-        <v>27</v>
+        <v>2.14</v>
       </c>
       <c r="BE19" t="n">
-        <v>40</v>
+        <v>2.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>25</v>
+        <v>2.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>36</v>
+        <v>2.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.71</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>1.84</v>
+        <v>4.7</v>
       </c>
       <c r="H22" t="n">
-        <v>4.9</v>
+        <v>1.98</v>
       </c>
       <c r="I22" t="n">
-        <v>5.9</v>
+        <v>2.66</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>1.61</v>
       </c>
       <c r="O22" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1.97</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1.84</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>1.97</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>2.18</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.6</v>
+        <v>1.71</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2</v>
+        <v>1.84</v>
       </c>
       <c r="H23" t="n">
-        <v>1.65</v>
+        <v>4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.69</v>
+        <v>5.9</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.98</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V23" t="n">
-        <v>2.44</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.19</v>
+        <v>2.18</v>
       </c>
       <c r="X23" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="Z23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC23" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AA23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AD23" t="n">
-        <v>9.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="AE23" t="n">
-        <v>18.5</v>
+        <v>75</v>
       </c>
       <c r="AF23" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="AG23" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AJ23" t="n">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AM23" t="n">
         <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="AP23" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW23" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AX23" t="n">
         <v>9</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AY23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC23" t="n">
         <v>14.5</v>
       </c>
-      <c r="AT23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>15</v>
-      </c>
       <c r="BD23" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>15</v>
+        <v>7.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="G24" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="I24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X24" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BF24" t="n">
         <v>2.66</v>
       </c>
-      <c r="J24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.94</v>
+        <v>1.66</v>
       </c>
       <c r="G25" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="H25" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="I25" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>2.78</v>
+        <v>3.75</v>
       </c>
       <c r="K25" t="n">
-        <v>3.05</v>
+        <v>10.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.98</v>
+        <v>1.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="X25" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="G26" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="H26" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="K26" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N26" t="n">
-        <v>1.51</v>
+        <v>2.28</v>
       </c>
       <c r="O26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.44</v>
       </c>
-      <c r="P26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="G27" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="H27" t="n">
-        <v>1.69</v>
+        <v>2.56</v>
       </c>
       <c r="I27" t="n">
-        <v>1.77</v>
+        <v>2.96</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>2.46</v>
+        <v>1.52</v>
       </c>
       <c r="O27" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="P27" t="n">
-        <v>2.46</v>
+        <v>1.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="R27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.51</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2.28</v>
-      </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="X27" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
         <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
         <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.66</v>
+        <v>5.6</v>
       </c>
       <c r="G28" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="H28" t="n">
-        <v>3.35</v>
+        <v>1.65</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>1.69</v>
       </c>
       <c r="J28" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="K28" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>1.2</v>
+        <v>2.44</v>
       </c>
       <c r="W28" t="n">
-        <v>1.9</v>
+        <v>1.19</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6198,10 +6198,10 @@
         <v>13</v>
       </c>
       <c r="I30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
         <v>9</v>
@@ -6219,19 +6219,19 @@
         <v>1.08</v>
       </c>
       <c r="P30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q30" t="n">
         <v>1.25</v>
       </c>
       <c r="R30" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T30" t="n">
         <v>1.62</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.64</v>
       </c>
       <c r="U30" t="n">
         <v>2.34</v>
@@ -6240,7 +6240,7 @@
         <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="X30" t="n">
         <v>80</v>
@@ -6252,7 +6252,7 @@
         <v>180</v>
       </c>
       <c r="AA30" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AB30" t="n">
         <v>21</v>
@@ -6261,7 +6261,7 @@
         <v>23</v>
       </c>
       <c r="AD30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE30" t="n">
         <v>170</v>
@@ -6279,7 +6279,7 @@
         <v>110</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK30" t="n">
         <v>13.5</v>
@@ -6291,22 +6291,22 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AO30" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT30" t="n">
         <v>17.5</v>
@@ -6315,10 +6315,10 @@
         <v>19.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX30" t="n">
         <v>12</v>
@@ -6327,10 +6327,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BA30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB30" t="n">
         <v>11.5</v>
@@ -6342,17 +6342,17 @@
         <v>21</v>
       </c>
       <c r="BE30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF30" t="n">
         <v>2.46</v>
       </c>
       <c r="BG30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
         <v>46</v>
       </c>
       <c r="AL33" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM33" t="n">
         <v>100</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         <v>2.34</v>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J34" t="n">
         <v>3.05</v>
@@ -7007,7 +7007,7 @@
         <v>5.3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U34" t="n">
         <v>1.81</v>
@@ -7031,7 +7031,7 @@
         <v>34</v>
       </c>
       <c r="AB34" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC34" t="n">
         <v>7.2</v>
@@ -7046,16 +7046,16 @@
         <v>24</v>
       </c>
       <c r="AG34" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AH34" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI34" t="n">
         <v>65</v>
       </c>
       <c r="AJ34" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK34" t="n">
         <v>65</v>
@@ -7064,13 +7064,13 @@
         <v>95</v>
       </c>
       <c r="AM34" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AN34" t="n">
         <v>90</v>
       </c>
       <c r="AO34" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP34" t="n">
         <v>8</v>
@@ -7091,7 +7091,7 @@
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW34" t="n">
         <v>28</v>
@@ -7109,26 +7109,26 @@
         <v>46</v>
       </c>
       <c r="BB34" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BC34" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BE34" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BG34" t="n">
         <v>26</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,783 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Macara</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K36" t="n">
+        <v>950</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-22 00:49:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K37" t="n">
+        <v>950</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-22 00:49:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Deportes Concepcion</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-22 00:49:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H2" t="n">
         <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
         <v>1.52</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
         <v>21</v>
@@ -823,7 +823,7 @@
         <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
@@ -838,7 +838,7 @@
         <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>18</v>
@@ -874,7 +874,7 @@
         <v>15.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
@@ -898,19 +898,19 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC2" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC2" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
         <v>16</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="I3" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="Q3" t="n">
         <v>1.65</v>
       </c>
       <c r="R3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T3" t="n">
         <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
@@ -1011,7 +1011,7 @@
         <v>11.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA3" t="n">
         <v>20</v>
@@ -1044,7 +1044,7 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1053,7 +1053,7 @@
         <v>80</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
         <v>8.4</v>
@@ -1071,7 +1071,7 @@
         <v>16</v>
       </c>
       <c r="AT3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU3" t="n">
         <v>8.800000000000001</v>
@@ -1083,7 +1083,7 @@
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="AY3" t="n">
         <v>16</v>
@@ -1095,26 +1095,26 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD3" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>38</v>
       </c>
       <c r="BE3" t="n">
         <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1378,10 +1378,10 @@
         <v>2.04</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="U5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
         <v>3.3</v>
@@ -1772,7 +1772,7 @@
         <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
         <v>1.29</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="I8" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J8" t="n">
         <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,7 +1945,7 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
@@ -1954,13 +1954,13 @@
         <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
         <v>1.54</v>
@@ -1969,13 +1969,13 @@
         <v>2.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
@@ -1984,13 +1984,13 @@
         <v>970</v>
       </c>
       <c r="AA8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB8" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
@@ -1999,7 +1999,7 @@
         <v>22</v>
       </c>
       <c r="AF8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AG8" t="n">
         <v>970</v>
@@ -2014,7 +2014,7 @@
         <v>60</v>
       </c>
       <c r="AK8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>34</v>
@@ -2023,7 +2023,7 @@
         <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
         <v>970</v>
@@ -2032,59 +2032,59 @@
         <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="AV8" t="n">
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB8" t="n">
         <v>7.2</v>
       </c>
-      <c r="AY8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BC8" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.24</v>
+        <v>5.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2118,10 +2118,10 @@
         <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="n">
         <v>4.7</v>
@@ -2154,7 +2154,7 @@
         <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T9" t="n">
         <v>1.65</v>
@@ -2166,7 +2166,7 @@
         <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
         <v>23</v>
@@ -2178,7 +2178,7 @@
         <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB9" t="n">
         <v>12</v>
@@ -2223,7 +2223,7 @@
         <v>46</v>
       </c>
       <c r="AP9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>17</v>
@@ -2271,14 +2271,14 @@
         <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG9" t="n">
         <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2318,10 +2318,10 @@
         <v>1.39</v>
       </c>
       <c r="I10" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
         <v>10</v>
@@ -2357,10 +2357,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.65</v>
+        <v>1.09</v>
       </c>
       <c r="G11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I11" t="n">
         <v>1.92</v>
@@ -2539,13 +2539,13 @@
         <v>1.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
         <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U11" t="n">
         <v>2.08</v>
@@ -2554,10 +2554,10 @@
         <v>2.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y11" t="n">
         <v>15</v>
@@ -2620,7 +2620,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AT11" t="n">
         <v>2.58</v>
@@ -2629,13 +2629,13 @@
         <v>2.34</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AY11" t="n">
         <v>14</v>
@@ -2647,16 +2647,16 @@
         <v>2.66</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BF11" t="n">
         <v>2.8</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I12" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,40 +2721,40 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U12" t="n">
         <v>2.66</v>
       </c>
       <c r="V12" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
         <v>19.5</v>
@@ -2766,7 +2766,7 @@
         <v>20</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
         <v>12.5</v>
@@ -2805,7 +2805,7 @@
         <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>13.5</v>
@@ -2814,7 +2814,7 @@
         <v>16</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT12" t="n">
         <v>16</v>
@@ -2838,29 +2838,29 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BB12" t="n">
         <v>40</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD12" t="n">
         <v>26</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BG12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G13" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H13" t="n">
         <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
@@ -2915,16 +2915,16 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O13" t="n">
         <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R13" t="n">
         <v>1.53</v>
@@ -2939,10 +2939,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X13" t="n">
         <v>34</v>
@@ -2981,7 +2981,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -3002,25 +3002,25 @@
         <v>16</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AT13" t="n">
         <v>8</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
         <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AX13" t="n">
         <v>8.4</v>
@@ -3029,13 +3029,13 @@
         <v>7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BB13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
         <v>11</v>
@@ -3044,17 +3044,17 @@
         <v>16.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BF13" t="n">
         <v>5.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3118,13 +3118,13 @@
         <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
         <v>9</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
         <v>12.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G16" t="n">
         <v>2.28</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
@@ -3494,13 +3494,13 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.16</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P16" t="n">
         <v>2.16</v>
@@ -3509,134 +3509,134 @@
         <v>1.79</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>1.79</v>
+        <v>2.96</v>
       </c>
       <c r="T16" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
         <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR16" t="n">
         <v>21</v>
       </c>
-      <c r="Y16" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AS16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV16" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="AW16" t="n">
         <v>30</v>
       </c>
-      <c r="AL16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT16" t="n">
+      <c r="AX16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA16" t="n">
         <v>9.4</v>
       </c>
-      <c r="AU16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BB16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BF16" t="n">
-        <v>2.66</v>
+        <v>12.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>2.08</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF17" t="n">
         <v>23</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AG17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL17" t="n">
         <v>55</v>
       </c>
-      <c r="AB17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AM17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
         <v>11</v>
       </c>
-      <c r="AD17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>2.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.28</v>
+        <v>13.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.42</v>
+        <v>7.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.04</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.38</v>
+        <v>7.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.32</v>
+        <v>18.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>2.24</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.3</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.42</v>
+        <v>7.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.44</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.44</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.52</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.52</v>
+        <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.52</v>
+        <v>18.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3870,13 +3870,13 @@
         <v>2.46</v>
       </c>
       <c r="I18" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,25 +3885,25 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U18" t="n">
         <v>2.18</v>
@@ -3915,116 +3915,116 @@
         <v>1.46</v>
       </c>
       <c r="X18" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX18" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y18" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AY18" t="n">
         <v>11</v>
       </c>
-      <c r="AD18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.14</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.14</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.14</v>
+        <v>6.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.22</v>
+        <v>7.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.22</v>
+        <v>6.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.22</v>
+        <v>19</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4061,19 +4061,19 @@
         <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I19" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
         <v>3.65</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
@@ -4082,25 +4082,25 @@
         <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
         <v>3.35</v>
       </c>
       <c r="T19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V19" t="n">
         <v>1.66</v>
@@ -4112,22 +4112,22 @@
         <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA19" t="n">
         <v>50</v>
       </c>
       <c r="AB19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
         <v>40</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AW19" t="n">
         <v>2.2</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AW19" t="n">
+      <c r="AX19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY19" t="n">
         <v>2.08</v>
       </c>
-      <c r="AX19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>2.02</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="G21" t="n">
         <v>8</v>
@@ -4452,13 +4452,13 @@
         <v>1.57</v>
       </c>
       <c r="I21" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="J21" t="n">
         <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4491,7 +4491,7 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="W21" t="n">
         <v>1.14</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G23" t="n">
         <v>1.84</v>
@@ -4840,13 +4840,13 @@
         <v>4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,31 +4855,31 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
         <v>1.29</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
         <v>1.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U23" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
         <v>2.18</v>
@@ -4894,49 +4894,49 @@
         <v>44</v>
       </c>
       <c r="AA23" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG23" t="n">
         <v>11</v>
       </c>
-      <c r="AG23" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
         <v>70</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
       </c>
       <c r="AL23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM23" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN23" t="n">
         <v>11</v>
       </c>
       <c r="AO23" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP23" t="n">
         <v>13.5</v>
@@ -4945,56 +4945,56 @@
         <v>15</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU23" t="n">
         <v>8</v>
       </c>
       <c r="AV23" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX23" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AY23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
-        <v>15</v>
+        <v>5.6</v>
       </c>
       <c r="BC23" t="n">
         <v>14.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
         <v>7.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>5.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="I24" t="n">
         <v>1.77</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
         <v>1.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>2.94</v>
       </c>
       <c r="G26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H26" t="n">
         <v>2.9</v>
       </c>
       <c r="I26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>2.78</v>
@@ -5437,7 +5437,7 @@
         <v>1.16</v>
       </c>
       <c r="N26" t="n">
-        <v>2.28</v>
+        <v>1.43</v>
       </c>
       <c r="O26" t="n">
         <v>1.6</v>
@@ -5509,7 +5509,7 @@
         <v>55</v>
       </c>
       <c r="AL26" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM26" t="n">
         <v>270</v>
@@ -5539,13 +5539,13 @@
         <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.4</v>
+        <v>12.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY26" t="n">
         <v>5.7</v>
@@ -5557,10 +5557,10 @@
         <v>7.8</v>
       </c>
       <c r="BB26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC26" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>7.2</v>
       </c>
       <c r="BD26" t="n">
         <v>7.8</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>3.65</v>
@@ -5616,7 +5616,7 @@
         <v>2.56</v>
       </c>
       <c r="I27" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>3</v>
@@ -5631,16 +5631,16 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="O27" t="n">
         <v>1.43</v>
       </c>
       <c r="P27" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
@@ -5655,7 +5655,7 @@
         <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W27" t="n">
         <v>1.38</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G28" t="n">
         <v>6.2</v>
       </c>
       <c r="H28" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="I28" t="n">
         <v>1.69</v>
@@ -5828,13 +5828,13 @@
         <v>3.55</v>
       </c>
       <c r="O28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P28" t="n">
         <v>1.93</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="R28" t="n">
         <v>1.34</v>
@@ -5873,7 +5873,7 @@
         <v>9.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE28" t="n">
         <v>18.5</v>
@@ -5891,22 +5891,22 @@
         <v>40</v>
       </c>
       <c r="AJ28" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AK28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL28" t="n">
         <v>100</v>
       </c>
-      <c r="AL28" t="n">
-        <v>95</v>
-      </c>
       <c r="AM28" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN28" t="n">
         <v>120</v>
       </c>
       <c r="AO28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP28" t="n">
         <v>12.5</v>
@@ -5930,10 +5930,10 @@
         <v>9</v>
       </c>
       <c r="AW28" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
         <v>19.5</v>
@@ -5945,26 +5945,26 @@
         <v>34</v>
       </c>
       <c r="BB28" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BF28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BG28" t="n">
         <v>9.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -6198,10 +6198,10 @@
         <v>13</v>
       </c>
       <c r="I30" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="K30" t="n">
         <v>9</v>
@@ -6216,22 +6216,22 @@
         <v>11</v>
       </c>
       <c r="O30" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P30" t="n">
         <v>4.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R30" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="S30" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T30" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="U30" t="n">
         <v>2.34</v>
@@ -6240,22 +6240,22 @@
         <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="X30" t="n">
         <v>80</v>
       </c>
       <c r="Y30" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Z30" t="n">
         <v>180</v>
       </c>
       <c r="AA30" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AB30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC30" t="n">
         <v>23</v>
@@ -6264,10 +6264,10 @@
         <v>50</v>
       </c>
       <c r="AE30" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AG30" t="n">
         <v>13.5</v>
@@ -6276,10 +6276,10 @@
         <v>27</v>
       </c>
       <c r="AI30" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK30" t="n">
         <v>13.5</v>
@@ -6297,16 +6297,16 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR30" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT30" t="n">
         <v>17.5</v>
@@ -6315,10 +6315,10 @@
         <v>19.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX30" t="n">
         <v>12</v>
@@ -6327,10 +6327,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BA30" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
         <v>11.5</v>
@@ -6342,17 +6342,17 @@
         <v>21</v>
       </c>
       <c r="BE30" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BG30" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
         <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R31" t="n">
         <v>1.24</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -6610,13 +6610,13 @@
         <v>1.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="R32" t="n">
         <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
         <v>20</v>
       </c>
       <c r="BA34" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB34" t="n">
         <v>15</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -7159,19 +7159,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G35" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="H35" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I35" t="n">
         <v>4.6</v>
       </c>
       <c r="J35" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K35" t="n">
         <v>3.55</v>
@@ -7210,7 +7210,7 @@
         <v>1.27</v>
       </c>
       <c r="W35" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G36" t="n">
         <v>1.84</v>
@@ -7362,10 +7362,10 @@
         <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J36" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K36" t="n">
         <v>950</v>
@@ -7392,7 +7392,7 @@
         <v>1.22</v>
       </c>
       <c r="S36" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -7401,7 +7401,7 @@
         <v>1.74</v>
       </c>
       <c r="V36" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W36" t="n">
         <v>2.18</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -7547,19 +7547,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="I37" t="n">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="K37" t="n">
         <v>950</v>
@@ -7571,7 +7571,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="O37" t="n">
         <v>1.08</v>
@@ -7580,13 +7580,13 @@
         <v>1.46</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="R37" t="n">
         <v>1.46</v>
       </c>
       <c r="S37" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -7595,10 +7595,10 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -7959,13 +7959,13 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O39" t="n">
         <v>1.35</v>
       </c>
       <c r="P39" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q39" t="n">
         <v>2.08</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
         <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
         <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
         <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="V2" t="n">
         <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
         <v>20</v>
@@ -817,31 +817,31 @@
         <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA2" t="n">
         <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
         <v>40</v>
@@ -865,7 +865,7 @@
         <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2" t="n">
         <v>11</v>
@@ -874,7 +874,7 @@
         <v>15.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
@@ -898,29 +898,29 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BG2" t="n">
         <v>15</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>4.8</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I3" t="n">
         <v>1.77</v>
@@ -993,10 +993,10 @@
         <v>2.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V3" t="n">
         <v>2.28</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="S5" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.54</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -1727,100 +1727,100 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="R7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.63</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.52</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.62</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.86</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.22</v>
+        <v>6.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.56</v>
+        <v>5.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.78</v>
+        <v>7.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.54</v>
+        <v>5.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.68</v>
+        <v>6.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.86</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.76</v>
+        <v>7.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.76</v>
+        <v>7.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.86</v>
+        <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.86</v>
+        <v>2.18</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.82</v>
+        <v>7.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.82</v>
+        <v>7.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H9" t="n">
         <v>4.2</v>
@@ -2133,7 +2133,7 @@
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2154,7 +2154,7 @@
         <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
         <v>1.65</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -2309,94 +2309,94 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K10" t="n">
         <v>5.5</v>
       </c>
-      <c r="G10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="L10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.39</v>
       </c>
-      <c r="I10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="S10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.98</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF10" t="n">
         <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
         <v>1000</v>
@@ -2414,65 +2414,65 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.09</v>
+        <v>4.5</v>
       </c>
       <c r="G11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA11" t="n">
         <v>6.6</v>
       </c>
-      <c r="H11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BB11" t="n">
-        <v>2.84</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.74</v>
+        <v>7.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.74</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G12" t="n">
         <v>3.25</v>
@@ -2715,40 +2715,40 @@
         <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="T12" t="n">
         <v>1.52</v>
       </c>
       <c r="U12" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="V12" t="n">
         <v>1.77</v>
       </c>
       <c r="W12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
         <v>28</v>
@@ -2760,7 +2760,7 @@
         <v>19.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB12" t="n">
         <v>20</v>
@@ -2805,7 +2805,7 @@
         <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ12" t="n">
         <v>13.5</v>
@@ -2814,7 +2814,7 @@
         <v>16</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT12" t="n">
         <v>16</v>
@@ -2844,23 +2844,23 @@
         <v>40</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>26</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BF12" t="n">
         <v>15.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -2909,152 +2909,152 @@
         <v>4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>2.52</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
         <v>2.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="S13" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
         <v>2.22</v>
       </c>
       <c r="X13" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y13" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AR13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC13" t="n">
         <v>14.5</v>
       </c>
-      <c r="AD13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>11</v>
-      </c>
       <c r="BD13" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.52</v>
+        <v>4.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.52</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -3106,13 +3106,13 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
         <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
         <v>1.25</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>2.18</v>
       </c>
       <c r="G16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H16" t="n">
         <v>3.25</v>
@@ -3491,7 +3491,7 @@
         <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -3506,7 +3506,7 @@
         <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R16" t="n">
         <v>1.46</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
         <v>3.2</v>
@@ -3691,28 +3691,28 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
         <v>1.81</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
         <v>1.6</v>
@@ -3733,7 +3733,7 @@
         <v>40</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC17" t="n">
         <v>7.8</v>
@@ -3745,13 +3745,13 @@
         <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
         <v>46</v>
@@ -3772,19 +3772,19 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
@@ -3796,7 +3796,7 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX17" t="n">
         <v>18.5</v>
@@ -3805,32 +3805,32 @@
         <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG17" t="n">
         <v>18.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -3867,22 +3867,22 @@
         <v>3.15</v>
       </c>
       <c r="H18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
         <v>3.65</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
         <v>3.7</v>
@@ -3891,7 +3891,7 @@
         <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
         <v>1.98</v>
@@ -3900,7 +3900,7 @@
         <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
         <v>1.77</v>
@@ -3909,7 +3909,7 @@
         <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W18" t="n">
         <v>1.46</v>
@@ -3927,7 +3927,7 @@
         <v>40</v>
       </c>
       <c r="AB18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
         <v>8.4</v>
@@ -3972,59 +3972,59 @@
         <v>12.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR18" t="n">
         <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX18" t="n">
         <v>17.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF18" t="n">
         <v>7</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>6.8</v>
       </c>
       <c r="BG18" t="n">
         <v>19</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H19" t="n">
         <v>2.38</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J19" t="n">
         <v>3.4</v>
@@ -4076,149 +4076,149 @@
         <v>1.37</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q19" t="n">
         <v>2.04</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
         <v>1.41</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR19" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AS19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.04</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.18</v>
+        <v>7.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.08</v>
+        <v>12.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.26</v>
+        <v>9.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.3</v>
+        <v>9.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.3</v>
+        <v>16.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -4255,10 +4255,10 @@
         <v>2.18</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J20" t="n">
         <v>3.35</v>
@@ -4297,7 +4297,7 @@
         <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W20" t="n">
         <v>1.84</v>
@@ -4402,7 +4402,7 @@
         <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF20" t="n">
         <v>18.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -4443,67 +4443,67 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="I21" t="n">
         <v>1.89</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>1.98</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
         <v>2.12</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
@@ -4512,7 +4512,7 @@
         <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD21" t="n">
         <v>1000</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="H22" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,34 +4661,34 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R22" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S22" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -4846,10 +4846,10 @@
         <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
@@ -4858,7 +4858,7 @@
         <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P23" t="n">
         <v>2.02</v>
@@ -4867,10 +4867,10 @@
         <v>1.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
         <v>1.78</v>
@@ -4969,7 +4969,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA23" t="n">
         <v>7</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>1.66</v>
       </c>
       <c r="I24" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J24" t="n">
         <v>4.2</v>
@@ -5043,16 +5043,16 @@
         <v>4.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>2.46</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
         <v>2.46</v>
@@ -5061,16 +5061,16 @@
         <v>1.62</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="S24" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="T24" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="U24" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="V24" t="n">
         <v>2.28</v>
@@ -5079,116 +5079,116 @@
         <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Y24" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH24" t="n">
         <v>18</v>
       </c>
-      <c r="Z24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>25</v>
-      </c>
       <c r="AI24" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
         <v>75</v>
       </c>
-      <c r="AL24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>100</v>
-      </c>
       <c r="AN24" t="n">
         <v>1000</v>
       </c>
       <c r="AO24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>10.5</v>
       </c>
-      <c r="AP24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AR24" t="n">
-        <v>2.34</v>
+        <v>10.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.42</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.48</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.28</v>
+        <v>9</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.28</v>
+        <v>9</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.4</v>
+        <v>13.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.56</v>
+        <v>7.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>2.44</v>
+        <v>16.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.42</v>
+        <v>14.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>2.68</v>
+        <v>8.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.58</v>
+        <v>7.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.58</v>
+        <v>7.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.6</v>
+        <v>8</v>
       </c>
       <c r="BF24" t="n">
-        <v>2.66</v>
+        <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -5219,64 +5219,64 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="G25" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H25" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K25" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W25" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5285,34 +5285,34 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="n">
         <v>1000</v>
@@ -5321,68 +5321,68 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.94</v>
       </c>
       <c r="G26" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H26" t="n">
         <v>2.9</v>
@@ -5431,16 +5431,16 @@
         <v>3.05</v>
       </c>
       <c r="L26" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M26" t="n">
         <v>1.16</v>
       </c>
       <c r="N26" t="n">
-        <v>1.43</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
         <v>1.43</v>
@@ -5527,7 +5527,7 @@
         <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>13.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS26" t="n">
         <v>7.4</v>
@@ -5545,7 +5545,7 @@
         <v>7.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
         <v>5.7</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G27" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H27" t="n">
         <v>2.56</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>3</v>
@@ -5625,73 +5625,73 @@
         <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>2.82</v>
       </c>
       <c r="O27" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P27" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="V27" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W27" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -5700,7 +5700,7 @@
         <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL27" t="n">
         <v>1000</v>
@@ -5715,62 +5715,62 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -5807,19 +5807,19 @@
         <v>6.2</v>
       </c>
       <c r="H28" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="I28" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K28" t="n">
         <v>4.3</v>
       </c>
-      <c r="K28" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
@@ -5831,25 +5831,25 @@
         <v>1.35</v>
       </c>
       <c r="P28" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
         <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V28" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="W28" t="n">
         <v>1.19</v>
@@ -5861,13 +5861,13 @@
         <v>7.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA28" t="n">
         <v>16.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
         <v>9.4</v>
@@ -5879,10 +5879,10 @@
         <v>18.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH28" t="n">
         <v>23</v>
@@ -5891,22 +5891,22 @@
         <v>40</v>
       </c>
       <c r="AJ28" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AK28" t="n">
         <v>95</v>
       </c>
       <c r="AL28" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AM28" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AN28" t="n">
         <v>120</v>
       </c>
       <c r="AO28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP28" t="n">
         <v>12.5</v>
@@ -5915,7 +5915,7 @@
         <v>6.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS28" t="n">
         <v>14.5</v>
@@ -5933,10 +5933,10 @@
         <v>16.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AZ28" t="n">
         <v>20</v>
@@ -5945,26 +5945,26 @@
         <v>34</v>
       </c>
       <c r="BB28" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BD28" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -5995,58 +5995,58 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="G29" t="n">
-        <v>48</v>
+        <v>1.59</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="O29" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="P29" t="n">
-        <v>1.52</v>
+        <v>3.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="R29" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="S29" t="n">
-        <v>1.06</v>
+        <v>1.73</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6097,68 +6097,68 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -6192,28 +6192,28 @@
         <v>1.23</v>
       </c>
       <c r="G30" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="H30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" t="n">
         <v>14.5</v>
       </c>
       <c r="J30" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="K30" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O30" t="n">
         <v>1.07</v>
@@ -6231,19 +6231,19 @@
         <v>1.62</v>
       </c>
       <c r="T30" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="U30" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V30" t="n">
         <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="X30" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Y30" t="n">
         <v>90</v>
@@ -6255,7 +6255,7 @@
         <v>440</v>
       </c>
       <c r="AB30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="n">
         <v>23</v>
@@ -6267,25 +6267,25 @@
         <v>160</v>
       </c>
       <c r="AF30" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
         <v>27</v>
       </c>
       <c r="AI30" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AK30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
@@ -6294,31 +6294,31 @@
         <v>2.66</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP30" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>19.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AX30" t="n">
         <v>12</v>
@@ -6327,10 +6327,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BA30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BB30" t="n">
         <v>11.5</v>
@@ -6342,17 +6342,17 @@
         <v>21</v>
       </c>
       <c r="BE30" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BG30" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
         <v>38</v>
       </c>
       <c r="AJ33" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK33" t="n">
         <v>46</v>
@@ -6873,7 +6873,7 @@
         <v>100</v>
       </c>
       <c r="AN33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO33" t="n">
         <v>16.5</v>
@@ -6927,14 +6927,14 @@
         <v>38</v>
       </c>
       <c r="BF33" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BG33" t="n">
         <v>14.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
         <v>3.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M34" t="n">
         <v>1.12</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>2.1</v>
       </c>
       <c r="G35" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H35" t="n">
         <v>3.95</v>
@@ -7174,19 +7174,19 @@
         <v>3.1</v>
       </c>
       <c r="K35" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.61</v>
+        <v>2.86</v>
       </c>
       <c r="O35" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P35" t="n">
         <v>1.61</v>
@@ -7195,134 +7195,134 @@
         <v>2.38</v>
       </c>
       <c r="R35" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V35" t="n">
         <v>1.27</v>
       </c>
       <c r="W35" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA35" t="n">
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -7353,19 +7353,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.53</v>
+        <v>1.09</v>
       </c>
       <c r="G36" t="n">
         <v>1.84</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I36" t="n">
         <v>7.6</v>
       </c>
       <c r="J36" t="n">
-        <v>3.05</v>
+        <v>1.09</v>
       </c>
       <c r="K36" t="n">
         <v>950</v>
@@ -7377,16 +7377,16 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O36" t="n">
         <v>1.36</v>
       </c>
       <c r="P36" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R36" t="n">
         <v>1.22</v>
@@ -7401,7 +7401,7 @@
         <v>1.74</v>
       </c>
       <c r="V36" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W36" t="n">
         <v>2.18</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G37" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="J37" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K37" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7571,34 +7571,34 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="O37" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P37" t="n">
-        <v>1.46</v>
+        <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="R37" t="n">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="S37" t="n">
-        <v>1.08</v>
+        <v>1.78</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
         <v>5.1</v>
       </c>
       <c r="I38" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J38" t="n">
         <v>3.75</v>
@@ -7762,13 +7762,13 @@
         <v>1.34</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="O38" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P38" t="n">
         <v>1.93</v>
@@ -7777,134 +7777,134 @@
         <v>1.95</v>
       </c>
       <c r="R38" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W38" t="n">
         <v>2.18</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA38" t="n">
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH38" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM38" t="n">
         <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -7938,55 +7938,55 @@
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="H39" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="I39" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J39" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="K39" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N39" t="n">
-        <v>1.64</v>
+        <v>3.2</v>
       </c>
       <c r="O39" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P39" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="Q39" t="n">
         <v>2.08</v>
       </c>
       <c r="R39" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V39" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="W39" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8043,62 +8043,62 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="H2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
@@ -805,10 +805,10 @@
         <v>2.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X2" t="n">
         <v>20</v>
@@ -844,7 +844,7 @@
         <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>48</v>
@@ -859,13 +859,13 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
         <v>11</v>
@@ -874,7 +874,7 @@
         <v>15.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
@@ -895,22 +895,22 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
         <v>7.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BF2" t="n">
         <v>18.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>5.1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I3" t="n">
         <v>1.77</v>
@@ -1014,10 +1014,10 @@
         <v>12.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
@@ -1026,16 +1026,16 @@
         <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AF3" t="n">
         <v>42</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>30</v>
@@ -1053,13 +1053,13 @@
         <v>80</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>8.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AT3" t="n">
         <v>18.5</v>
@@ -1080,41 +1080,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>55</v>
+        <v>7.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BG3" t="n">
         <v>7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -1145,67 +1145,67 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M4" t="n">
         <v>1.04</v>
       </c>
-      <c r="G4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>1.23</v>
+        <v>2.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1250,65 +1250,65 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G5" t="n">
         <v>4.1</v>
@@ -1348,7 +1348,7 @@
         <v>1.86</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J5" t="n">
         <v>4.6</v>
@@ -1366,7 +1366,7 @@
         <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P5" t="n">
         <v>3.8</v>
@@ -1378,7 +1378,7 @@
         <v>2.14</v>
       </c>
       <c r="S5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="T5" t="n">
         <v>1.4</v>
@@ -1387,7 +1387,7 @@
         <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="W5" t="n">
         <v>1.35</v>
@@ -1396,13 +1396,13 @@
         <v>65</v>
       </c>
       <c r="Y5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB5" t="n">
         <v>42</v>
@@ -1447,19 +1447,19 @@
         <v>6.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AU5" t="n">
         <v>10.5</v>
@@ -1480,19 +1480,19 @@
         <v>10.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BF5" t="n">
         <v>10.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,114 +1713,114 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>1.07</v>
       </c>
       <c r="O7" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1.36</v>
       </c>
       <c r="R7" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="S7" t="n">
-        <v>6.4</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1835,69 +1835,69 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,184 +1907,184 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H8" t="n">
         <v>3.05</v>
       </c>
-      <c r="G8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.18</v>
-      </c>
       <c r="I8" t="n">
-        <v>2.32</v>
+        <v>3.45</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="N8" t="n">
-        <v>5.4</v>
+        <v>2.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>1.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.54</v>
+        <v>2.26</v>
       </c>
       <c r="U8" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="V8" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
         <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
         <v>60</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.4</v>
+        <v>1.96</v>
       </c>
       <c r="BF8" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>2.94</v>
       </c>
       <c r="G9" t="n">
-        <v>1.89</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.2</v>
       </c>
-      <c r="I9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE9" t="n">
         <v>22</v>
       </c>
-      <c r="Z9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AF9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FK Napredak</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK IMT Novi Beograd</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>1.82</v>
       </c>
       <c r="G10" t="n">
-        <v>10.5</v>
+        <v>1.89</v>
       </c>
       <c r="H10" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.51</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>2.92</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="X10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y10" t="n">
         <v>22</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT10" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Z10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AU10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV10" t="n">
         <v>15</v>
       </c>
-      <c r="AB10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AW10" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>21</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE10" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>FK Napredak</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>FK IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="I11" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="J11" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="T11" t="n">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="V11" t="n">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="W11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT11" t="n">
         <v>21</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>17</v>
       </c>
       <c r="AU11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>16.5</v>
+        <v>3.95</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="H12" t="n">
-        <v>2.24</v>
+        <v>1.7</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="J12" t="n">
         <v>3.95</v>
       </c>
       <c r="K12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N12" t="n">
         <v>4.4</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.9</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.68</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.34</v>
-      </c>
       <c r="T12" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="U12" t="n">
-        <v>2.76</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Y12" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="AA12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX12" t="n">
         <v>30</v>
       </c>
-      <c r="AB12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ12" t="n">
+      <c r="AY12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA12" t="n">
-        <v>22</v>
+        <v>4.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>40</v>
+        <v>4.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>26</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>42</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>15.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B93 Copenhagen</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.73</v>
+        <v>2.94</v>
       </c>
       <c r="G13" t="n">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>2.28</v>
       </c>
       <c r="I13" t="n">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R13" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="S13" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="T13" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
       <c r="W13" t="n">
-        <v>2.22</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI13" t="n">
         <v>27</v>
       </c>
-      <c r="Z13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>60</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AK13" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
         <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.8</v>
+        <v>26</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="AX13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB13" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BC13" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF13" t="n">
         <v>14.5</v>
       </c>
-      <c r="BD13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>AaB</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>B93 Copenhagen</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="S14" t="n">
-        <v>1.41</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.22</v>
+        <v>1.41</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2</v>
+        <v>1.41</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,88 +3464,88 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="R16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.46</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.4</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="X16" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE16" t="n">
         <v>38</v>
@@ -3554,89 +3554,89 @@
         <v>15.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN16" t="n">
         <v>29</v>
       </c>
-      <c r="AK16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AO16" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP16" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV16" t="n">
         <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.4</v>
+        <v>48</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BC16" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="BD16" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BE16" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="BF16" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="I17" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>2.76</v>
       </c>
       <c r="T17" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="X17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>13</v>
       </c>
-      <c r="Y17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>9</v>
-      </c>
       <c r="AR17" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BC17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE17" t="n">
         <v>8.6</v>
       </c>
-      <c r="BD17" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>10</v>
-      </c>
       <c r="BF17" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -3852,91 +3852,91 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G18" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="I18" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
         <v>3.65</v>
       </c>
       <c r="L18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="O18" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
         <v>40</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD18" t="n">
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
         <v>22</v>
@@ -3945,86 +3945,86 @@
         <v>14</v>
       </c>
       <c r="AH18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX18" t="n">
         <v>18</v>
       </c>
-      <c r="AI18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BG18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -4046,103 +4046,103 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="H19" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="I19" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
         <v>3.65</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P19" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="U19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W19" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="X19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AB19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ19" t="n">
         <v>60</v>
@@ -4151,81 +4151,81 @@
         <v>40</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB19" t="n">
         <v>7</v>
       </c>
-      <c r="BA19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BC19" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BE19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="W20" t="n">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z20" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AA20" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AF20" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AH20" t="n">
         <v>19.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
         <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AO20" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AP20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT20" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8</v>
       </c>
       <c r="AU20" t="n">
         <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AX20" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE20" t="n">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>50</v>
+        <v>16.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Backa Topola</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="G21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC21" t="n">
         <v>7.4</v>
       </c>
-      <c r="H21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z21" t="n">
+      <c r="AD21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AR21" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.1</v>
+        <v>34</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.2</v>
+        <v>46</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="BB21" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.9</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.9</v>
+        <v>38</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="BF21" t="n">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.9</v>
+        <v>50</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -4628,76 +4628,76 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>FK Backa Topola</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K22" t="n">
         <v>4.2</v>
       </c>
-      <c r="H22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N22" t="n">
         <v>3.1</v>
       </c>
-      <c r="K22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.76</v>
-      </c>
       <c r="O22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
         <v>1.99</v>
       </c>
       <c r="R22" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>1.99</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="W22" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
@@ -4706,7 +4706,7 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4745,69 +4745,69 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.73</v>
+        <v>3.35</v>
       </c>
       <c r="G23" t="n">
-        <v>1.84</v>
+        <v>3.95</v>
       </c>
       <c r="H23" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="I23" t="n">
-        <v>5.7</v>
+        <v>2.48</v>
       </c>
       <c r="J23" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.38</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB23" t="n">
         <v>4</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BC23" t="n">
-        <v>14.5</v>
+        <v>3.95</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>55</v>
+        <v>3.65</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.7</v>
+        <v>1.71</v>
       </c>
       <c r="G24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW24" t="n">
         <v>5.2</v>
       </c>
-      <c r="H24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="AX24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD24" t="n">
         <v>4.8</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X24" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK24" t="n">
+      <c r="BE24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG24" t="n">
         <v>55</v>
       </c>
-      <c r="AL24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.76</v>
+        <v>4.7</v>
       </c>
       <c r="G25" t="n">
-        <v>2.04</v>
+        <v>5.2</v>
       </c>
       <c r="H25" t="n">
-        <v>3.75</v>
+        <v>1.66</v>
       </c>
       <c r="I25" t="n">
-        <v>5.3</v>
+        <v>1.78</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P25" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="S25" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="T25" t="n">
         <v>1.6</v>
       </c>
       <c r="U25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.23</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.96</v>
-      </c>
       <c r="X25" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Y25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB25" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="AC25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW25" t="n">
         <v>12</v>
       </c>
-      <c r="AD25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AZ25" t="n">
         <v>12.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="BD25" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,179 +5404,179 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.94</v>
+        <v>1.8</v>
       </c>
       <c r="G26" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
-        <v>2.78</v>
+        <v>3.95</v>
       </c>
       <c r="K26" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="M26" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>2.32</v>
+        <v>4.9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="P26" t="n">
-        <v>1.43</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.98</v>
+        <v>1.59</v>
       </c>
       <c r="R26" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="S26" t="n">
-        <v>6.4</v>
+        <v>2.46</v>
       </c>
       <c r="T26" t="n">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.68</v>
+        <v>2.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="W26" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY26" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y26" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV26" t="n">
+      <c r="AZ26" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX26" t="n">
+      <c r="BA26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB26" t="n">
         <v>16</v>
       </c>
-      <c r="AY26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BC26" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.05</v>
       </c>
-      <c r="G27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L27" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="N27" t="n">
-        <v>2.82</v>
+        <v>2.32</v>
       </c>
       <c r="O27" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="P27" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="S27" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="U27" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="V27" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W27" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y27" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="Z27" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB27" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AG27" t="n">
         <v>17.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK27" t="n">
         <v>55</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="AT27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW27" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>26</v>
-      </c>
       <c r="AX27" t="n">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.7</v>
+        <v>3.05</v>
       </c>
       <c r="G28" t="n">
-        <v>6.2</v>
+        <v>3.55</v>
       </c>
       <c r="H28" t="n">
-        <v>1.66</v>
+        <v>2.56</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="K28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE28" t="n">
         <v>4.3</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X28" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BF28" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.47</v>
+        <v>5.8</v>
       </c>
       <c r="G29" t="n">
-        <v>1.59</v>
+        <v>6.4</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>1.66</v>
       </c>
       <c r="I29" t="n">
-        <v>7.4</v>
+        <v>1.69</v>
       </c>
       <c r="J29" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="K29" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>1.54</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="P29" t="n">
-        <v>3.15</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.92</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>1.73</v>
+        <v>3.7</v>
       </c>
       <c r="T29" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>2.74</v>
+        <v>1.9</v>
       </c>
       <c r="V29" t="n">
-        <v>1.15</v>
+        <v>2.44</v>
       </c>
       <c r="W29" t="n">
-        <v>2.64</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN29" t="n">
-        <v>4.7</v>
+        <v>120</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.8</v>
+        <v>16</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.95</v>
+        <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.7</v>
+        <v>12.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.45</v>
+        <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3.75</v>
+        <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.1</v>
+        <v>34</v>
       </c>
       <c r="BB29" t="n">
-        <v>3.75</v>
+        <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.3</v>
+        <v>14.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="G30" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="H30" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="J30" t="n">
-        <v>8.6</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="L30" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="O30" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P30" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R30" t="n">
-        <v>2.46</v>
+        <v>1.92</v>
       </c>
       <c r="S30" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="T30" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="U30" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="V30" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="W30" t="n">
-        <v>5.1</v>
+        <v>2.64</v>
       </c>
       <c r="X30" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.66</v>
+        <v>4.7</v>
       </c>
       <c r="AO30" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="AR30" t="n">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS30" t="n">
-        <v>14.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>18</v>
+        <v>3.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>19.5</v>
+        <v>3.65</v>
       </c>
       <c r="AV30" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="AW30" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX30" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="AY30" t="n">
-        <v>11.5</v>
+        <v>3.45</v>
       </c>
       <c r="AZ30" t="n">
-        <v>23</v>
+        <v>3.75</v>
       </c>
       <c r="BA30" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="BB30" t="n">
-        <v>11.5</v>
+        <v>3.75</v>
       </c>
       <c r="BC30" t="n">
-        <v>11.5</v>
+        <v>3.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="BE30" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="BG30" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,184 +6369,184 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M31" t="n">
         <v>1.01</v>
       </c>
-      <c r="M31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="N31" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="P31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1.5</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.24</v>
+        <v>2.48</v>
       </c>
       <c r="S31" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -6604,19 +6604,19 @@
         <v>1.01</v>
       </c>
       <c r="O32" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N33" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="O33" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="P33" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.02</v>
+        <v>1.35</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>1.35</v>
       </c>
       <c r="T33" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR33" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AS33" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV33" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW33" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX33" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AY33" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA33" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB33" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="BC33" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BD33" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="BE33" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BF33" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G34" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H34" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="I34" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="K34" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="L34" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N34" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="O34" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="P34" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="T34" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="U34" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="V34" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="W34" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X34" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="Z34" t="n">
         <v>13</v>
       </c>
       <c r="AA34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA34" t="n">
         <v>34</v>
       </c>
-      <c r="AB34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI34" t="n">
+      <c r="BB34" t="n">
         <v>65</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>15</v>
-      </c>
       <c r="BC34" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="BD34" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="BE34" t="n">
-        <v>16.5</v>
+        <v>38</v>
       </c>
       <c r="BF34" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="BG34" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7150,186 +7150,186 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="G35" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="H35" t="n">
-        <v>3.95</v>
+        <v>2.34</v>
       </c>
       <c r="I35" t="n">
-        <v>4.6</v>
+        <v>2.42</v>
       </c>
       <c r="J35" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K35" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N35" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="O35" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="P35" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="U35" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V35" t="n">
-        <v>1.27</v>
+        <v>1.71</v>
       </c>
       <c r="W35" t="n">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="X35" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY35" t="n">
         <v>15</v>
       </c>
-      <c r="Z35" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH35" t="n">
+      <c r="AZ35" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG35" t="n">
         <v>26</v>
       </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,191 +7339,191 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="G36" t="n">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="H36" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I36" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="J36" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>1.67</v>
+        <v>2.86</v>
       </c>
       <c r="O36" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="P36" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="R36" t="n">
         <v>1.22</v>
       </c>
       <c r="S36" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U36" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="V36" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="W36" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA36" t="n">
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE36" t="n">
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7538,67 +7538,67 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.09</v>
+        <v>1.75</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="H37" t="n">
-        <v>1.75</v>
+        <v>4.9</v>
       </c>
       <c r="I37" t="n">
-        <v>1.98</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K37" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N37" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>1.79</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.78</v>
+        <v>3.55</v>
       </c>
       <c r="T37" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="U37" t="n">
-        <v>2.8</v>
+        <v>1.89</v>
       </c>
       <c r="V37" t="n">
-        <v>2.02</v>
+        <v>1.21</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7613,10 +7613,10 @@
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD37" t="n">
         <v>1000</v>
@@ -7655,69 +7655,69 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="AQ37" t="n">
         <v>3.55</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AS37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV37" t="n">
         <v>3.7</v>
       </c>
-      <c r="AT37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AW37" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="AX37" t="n">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="AZ37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF37" t="n">
         <v>3.4</v>
       </c>
-      <c r="BA37" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BG37" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,373 +7732,567 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportes Concepcion</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
         <v>1.75</v>
       </c>
-      <c r="G38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="H38" t="n">
-        <v>5.1</v>
-      </c>
       <c r="I38" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT38" t="n">
         <v>3.75</v>
       </c>
-      <c r="K38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N38" t="n">
+      <c r="AU38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA38" t="n">
         <v>3.7</v>
       </c>
-      <c r="O38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="X38" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>5</v>
-      </c>
       <c r="BB38" t="n">
-        <v>16.5</v>
+        <v>4</v>
       </c>
       <c r="BC38" t="n">
-        <v>17</v>
+        <v>3.85</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="BF38" t="n">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Deportes Concepcion</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-22 07:36:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Millonarios</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Tolima</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="F40" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G40" t="n">
         <v>2.24</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H40" t="n">
         <v>3.85</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD40" t="n">
         <v>4.6</v>
       </c>
-      <c r="J39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP39" t="n">
+      <c r="BE40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG40" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>2026-04-22 05:21:00</t>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH40"/>
+  <dimension ref="A1:BH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="I2" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY2" t="n">
         <v>13</v>
       </c>
-      <c r="Z2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BE2" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="BG2" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -951,91 +951,91 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="I3" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="W3" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AF3" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
         <v>30</v>
@@ -1044,10 +1044,10 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
         <v>80</v>
@@ -1056,7 +1056,7 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP3" t="n">
         <v>18.5</v>
@@ -1065,16 +1065,16 @@
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
         <v>18.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
         <v>9.199999999999999</v>
@@ -1089,32 +1089,32 @@
         <v>16.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BG3" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -1151,43 +1151,43 @@
         <v>16.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I4" t="n">
         <v>1.36</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
         <v>2.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
         <v>1.69</v>
@@ -1202,7 +1202,7 @@
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>8.800000000000001</v>
@@ -1250,65 +1250,65 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.1</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BD4" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>3.4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>4.6</v>
@@ -1363,22 +1363,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="T5" t="n">
         <v>1.4</v>
@@ -1387,7 +1387,7 @@
         <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
         <v>1.35</v>
@@ -1396,16 +1396,16 @@
         <v>65</v>
       </c>
       <c r="Y5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z5" t="n">
         <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AC5" t="n">
         <v>17.5</v>
@@ -1417,7 +1417,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG5" t="n">
         <v>22</v>
@@ -1441,13 +1441,13 @@
         <v>44</v>
       </c>
       <c r="AN5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>6.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>17.5</v>
@@ -1459,19 +1459,19 @@
         <v>19.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU5" t="n">
         <v>10.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW5" t="n">
         <v>12.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY5" t="n">
         <v>13</v>
@@ -1483,16 +1483,16 @@
         <v>14.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF5" t="n">
         <v>10.5</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,64 +1524,64 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Radnicki Nis</t>
+          <t>FC Pyunik</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Javor Ivanjica</t>
+          <t>FC Urartu</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.09</v>
       </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.25</v>
-      </c>
       <c r="S6" t="n">
-        <v>3.85</v>
+        <v>1.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="W6" t="n">
         <v>1.9</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,69 +1641,69 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,72 +1713,72 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11:15:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bihor Oradea</t>
+          <t>Radnicki Nis</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>FK Javor Ivanjica</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.07</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.07</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.36</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1835,69 +1835,69 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,114 +1907,114 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.24</v>
+        <v>1.09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>1.35</v>
       </c>
       <c r="R8" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="S8" t="n">
-        <v>6.4</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2029,69 +2029,69 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.96</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,184 +2101,184 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.36</v>
+        <v>3.35</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="N9" t="n">
-        <v>5.4</v>
+        <v>2.24</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>1.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.56</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>6.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
         <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="AD9" t="n">
         <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK9" t="n">
         <v>55</v>
       </c>
-      <c r="AK9" t="n">
-        <v>30</v>
-      </c>
       <c r="AL9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR9" t="n">
         <v>5.9</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AS9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY9" t="n">
         <v>5.4</v>
       </c>
-      <c r="AR9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.82</v>
+        <v>2.96</v>
       </c>
       <c r="G10" t="n">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>2.24</v>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>2.32</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="T10" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="W10" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF10" t="n">
         <v>25</v>
       </c>
-      <c r="Y10" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>14</v>
-      </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
         <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AN10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FK Napredak</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FK IMT Novi Beograd</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF11" t="n">
         <v>7</v>
       </c>
-      <c r="G11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG11" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>FK Napredak</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>FK IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="G12" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA12" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
         <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AR12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS12" t="n">
-        <v>14</v>
-      </c>
       <c r="AT12" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BG12" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="I13" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
         <v>4.4</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="R13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.69</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.51</v>
-      </c>
       <c r="U13" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AP13" t="n">
         <v>17</v>
       </c>
-      <c r="Z13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AQ13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR13" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AS13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>15</v>
       </c>
-      <c r="AI13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
-      </c>
       <c r="BA13" t="n">
-        <v>23</v>
+        <v>6.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
-        <v>24</v>
+        <v>7.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>26</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B93 Copenhagen</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>1.81</v>
+        <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>2.28</v>
       </c>
       <c r="I14" t="n">
-        <v>5.5</v>
+        <v>2.32</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R14" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="T14" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="W14" t="n">
-        <v>2.22</v>
+        <v>1.46</v>
       </c>
       <c r="X14" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK14" t="n">
         <v>29</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>19.5</v>
       </c>
       <c r="AL14" t="n">
         <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.8</v>
+        <v>26</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF14" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>6</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,112 +3270,112 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>1.41</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK15" t="n">
         <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
@@ -3384,72 +3384,72 @@
         <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I16" t="n">
         <v>2.6</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3.15</v>
-      </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="W16" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
         <v>11</v>
       </c>
-      <c r="Z16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AQ16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR16" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AS16" t="n">
-        <v>48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="BB16" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD16" t="n">
-        <v>42</v>
+        <v>9.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="BG16" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="H17" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J17" t="n">
         <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.31</v>
@@ -3691,61 +3691,61 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="T17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X17" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
         <v>15.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC17" t="n">
         <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
@@ -3754,22 +3754,22 @@
         <v>17</v>
       </c>
       <c r="AI17" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL17" t="n">
         <v>34</v>
       </c>
-      <c r="AK17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>38</v>
-      </c>
       <c r="AM17" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO17" t="n">
         <v>32</v>
@@ -3781,10 +3781,10 @@
         <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
         <v>9.800000000000001</v>
@@ -3808,29 +3808,29 @@
         <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
-        <v>21</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -3852,25 +3852,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
         <v>3.4</v>
@@ -3879,88 +3879,88 @@
         <v>3.65</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
         <v>2.06</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="W18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AA18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB18" t="n">
         <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AJ18" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK18" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN18" t="n">
         <v>1000</v>
@@ -3969,7 +3969,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>8.800000000000001</v>
@@ -3978,60 +3978,60 @@
         <v>13.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
         <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BF18" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="O19" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.98</v>
+        <v>1.41</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>1.41</v>
       </c>
       <c r="T19" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AaB</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>B93 Copenhagen</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4</v>
+        <v>1.81</v>
       </c>
       <c r="H20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.38</v>
       </c>
-      <c r="I20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="X20" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="Z20" t="n">
-        <v>970</v>
+        <v>46</v>
       </c>
       <c r="AA20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AF20" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
         <v>19.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ20" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="AK20" t="n">
-        <v>50</v>
+        <v>19.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AM20" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>50</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO20" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AP20" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT20" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX20" t="n">
         <v>10</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AY20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD20" t="n">
         <v>20</v>
       </c>
-      <c r="AX20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>36</v>
-      </c>
       <c r="BE20" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BG20" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -4429,39 +4429,39 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="J21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
@@ -4473,140 +4473,140 @@
         <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R21" t="n">
         <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="W21" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="X21" t="n">
         <v>11.5</v>
       </c>
       <c r="Y21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD21" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AE21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI21" t="n">
         <v>55</v>
       </c>
-      <c r="AF21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>70</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL21" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AO21" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AP21" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AS21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW21" t="n">
         <v>34</v>
       </c>
-      <c r="AT21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>46</v>
-      </c>
       <c r="AX21" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AY21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BE21" t="n">
         <v>40</v>
       </c>
       <c r="BF21" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BG21" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -4637,67 +4637,67 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G22" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="H22" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="I22" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
         <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="W22" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
@@ -4706,7 +4706,7 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4745,13 +4745,13 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS22" t="n">
         <v>4.2</v>
@@ -4763,7 +4763,7 @@
         <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW22" t="n">
         <v>4.3</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -4834,22 +4834,22 @@
         <v>3.35</v>
       </c>
       <c r="G23" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I23" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
@@ -4861,28 +4861,28 @@
         <v>1.39</v>
       </c>
       <c r="P23" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T23" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U23" t="n">
         <v>1.96</v>
       </c>
       <c r="V23" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W23" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4900,7 +4900,7 @@
         <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD23" t="n">
         <v>1000</v>
@@ -4948,7 +4948,7 @@
         <v>10</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AT23" t="n">
         <v>8.6</v>
@@ -4960,41 +4960,41 @@
         <v>8.4</v>
       </c>
       <c r="AW23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX23" t="n">
         <v>3.8</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>3.7</v>
       </c>
       <c r="AY23" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4</v>
       </c>
-      <c r="BC23" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF23" t="n">
         <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G24" t="n">
         <v>1.84</v>
@@ -5034,7 +5034,7 @@
         <v>4.9</v>
       </c>
       <c r="I24" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>3.75</v>
@@ -5043,22 +5043,22 @@
         <v>4.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
         <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R24" t="n">
         <v>1.39</v>
@@ -5073,34 +5073,34 @@
         <v>2.04</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W24" t="n">
         <v>2.18</v>
       </c>
       <c r="X24" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y24" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y24" t="n">
-        <v>22</v>
-      </c>
       <c r="Z24" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA24" t="n">
         <v>170</v>
       </c>
       <c r="AB24" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AF24" t="n">
         <v>11.5</v>
@@ -5112,13 +5112,13 @@
         <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ24" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL24" t="n">
         <v>38</v>
@@ -5127,25 +5127,25 @@
         <v>140</v>
       </c>
       <c r="AN24" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO24" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP24" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
@@ -5154,7 +5154,7 @@
         <v>17</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX24" t="n">
         <v>9.199999999999999</v>
@@ -5166,7 +5166,7 @@
         <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB24" t="n">
         <v>15.5</v>
@@ -5175,27 +5175,27 @@
         <v>14.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BF24" t="n">
         <v>9</v>
       </c>
       <c r="BG24" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="I25" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="J25" t="n">
         <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="P25" t="n">
-        <v>2.46</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="U25" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="V25" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="W25" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AC25" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG25" t="n">
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AJ25" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AK25" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AL25" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AM25" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AN25" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AO25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR25" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AP25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AS25" t="n">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AU25" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV25" t="n">
         <v>9</v>
       </c>
       <c r="AW25" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.9</v>
+        <v>14.5</v>
       </c>
       <c r="AY25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC25" t="n">
         <v>14.5</v>
       </c>
-      <c r="AZ25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4</v>
-      </c>
       <c r="BD25" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,179 +5404,179 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.8</v>
       </c>
-      <c r="G26" t="n">
+      <c r="Q26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.34</v>
-      </c>
       <c r="V26" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="X26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z26" t="n">
         <v>27</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR26" t="n">
         <v>24</v>
       </c>
-      <c r="Z26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="AS26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX26" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY26" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.5</v>
+        <v>55</v>
       </c>
       <c r="BB26" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BC26" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.7</v>
+        <v>40</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.4</v>
+        <v>55</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -5613,13 +5613,13 @@
         <v>3.25</v>
       </c>
       <c r="H27" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I27" t="n">
         <v>3.2</v>
       </c>
       <c r="J27" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K27" t="n">
         <v>3.05</v>
@@ -5640,7 +5640,7 @@
         <v>1.43</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="R27" t="n">
         <v>1.15</v>
@@ -5652,13 +5652,13 @@
         <v>2.26</v>
       </c>
       <c r="U27" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.45</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.44</v>
       </c>
       <c r="X27" t="n">
         <v>8.199999999999999</v>
@@ -5673,13 +5673,13 @@
         <v>60</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE27" t="n">
         <v>55</v>
@@ -5688,13 +5688,13 @@
         <v>970</v>
       </c>
       <c r="AG27" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI27" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ27" t="n">
         <v>65</v>
@@ -5703,13 +5703,13 @@
         <v>55</v>
       </c>
       <c r="AL27" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM27" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AN27" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AO27" t="n">
         <v>75</v>
@@ -5718,59 +5718,59 @@
         <v>6.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
       </c>
       <c r="AU27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX27" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AY27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC27" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD27" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG27" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>3.05</v>
       </c>
       <c r="G28" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="J28" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="K28" t="n">
         <v>3.25</v>
@@ -5840,10 +5840,10 @@
         <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U28" t="n">
         <v>1.88</v>
@@ -5852,40 +5852,40 @@
         <v>1.53</v>
       </c>
       <c r="W28" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X28" t="n">
         <v>12</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z28" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
@@ -5912,66 +5912,66 @@
         <v>8.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR28" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.1</v>
+        <v>26</v>
       </c>
       <c r="AT28" t="n">
         <v>8.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="AV28" t="n">
         <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.1</v>
+        <v>38</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="BG28" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="G29" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="H29" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="I29" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="J29" t="n">
         <v>4.2</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="M29" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="S29" t="n">
-        <v>3.7</v>
+        <v>2.44</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="U29" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="V29" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="Z29" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AB29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG29" t="n">
         <v>21</v>
       </c>
-      <c r="AC29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="AH29" t="n">
         <v>18.5</v>
       </c>
-      <c r="AF29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>24</v>
-      </c>
       <c r="AI29" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AJ29" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="AK29" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AL29" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AM29" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="AN29" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AO29" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AP29" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
       </c>
       <c r="AW29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY29" t="n">
         <v>16.5</v>
       </c>
-      <c r="AX29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>20</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BC29" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD29" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="BG29" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,78 +6175,78 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="G30" t="n">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="I30" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
         <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="O30" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="P30" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="R30" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="S30" t="n">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="T30" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="U30" t="n">
-        <v>2.74</v>
+        <v>2.34</v>
       </c>
       <c r="V30" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="W30" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z30" t="n">
         <v>1000</v>
@@ -6255,34 +6255,34 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="n">
         <v>1000</v>
@@ -6291,75 +6291,75 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS30" t="n">
         <v>4.7</v>
       </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS30" t="n">
+      <c r="AT30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG30" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>4</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,186 +6374,186 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="G31" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="H31" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="I31" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="M31" t="n">
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P31" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="R31" t="n">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="S31" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="T31" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="U31" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="V31" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="W31" t="n">
-        <v>5.1</v>
+        <v>2.68</v>
       </c>
       <c r="X31" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.64</v>
+        <v>4.2</v>
       </c>
       <c r="AO31" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>2.52</v>
       </c>
       <c r="AS31" t="n">
-        <v>15</v>
+        <v>2.02</v>
       </c>
       <c r="AT31" t="n">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="AU31" t="n">
-        <v>19.5</v>
+        <v>5.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>12</v>
+        <v>2.38</v>
       </c>
       <c r="AW31" t="n">
-        <v>14</v>
+        <v>2.52</v>
       </c>
       <c r="AX31" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>11.5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>23</v>
+        <v>3.05</v>
       </c>
       <c r="BA31" t="n">
-        <v>13.5</v>
+        <v>2.92</v>
       </c>
       <c r="BB31" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="BD31" t="n">
-        <v>21</v>
+        <v>3.3</v>
       </c>
       <c r="BE31" t="n">
-        <v>13</v>
+        <v>2.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="BG31" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,184 +6563,184 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M32" t="n">
         <v>1.01</v>
       </c>
-      <c r="M32" t="n">
-        <v>1.02</v>
-      </c>
       <c r="N32" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="O32" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="P32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1.5</v>
-      </c>
       <c r="R32" t="n">
-        <v>1.24</v>
+        <v>2.48</v>
       </c>
       <c r="S32" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -6798,19 +6798,19 @@
         <v>1.01</v>
       </c>
       <c r="O33" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P33" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="R33" t="n">
         <v>1.24</v>
       </c>
       <c r="S33" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="O34" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="P34" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>3.6</v>
+        <v>1.35</v>
       </c>
       <c r="T34" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR34" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AS34" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU34" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV34" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AY34" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA34" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB34" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="BC34" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BD34" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="BE34" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BF34" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,191 +7145,191 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N35" t="n">
         <v>3.8</v>
       </c>
-      <c r="G35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J35" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O35" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="P35" t="n">
-        <v>1.56</v>
+        <v>1.94</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="U35" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="V35" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="W35" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X35" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="Z35" t="n">
         <v>13</v>
       </c>
       <c r="AA35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA35" t="n">
         <v>34</v>
       </c>
-      <c r="AB35" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI35" t="n">
+      <c r="BB35" t="n">
         <v>65</v>
       </c>
-      <c r="AJ35" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>15</v>
-      </c>
       <c r="BC35" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="BD35" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="BE35" t="n">
-        <v>16.5</v>
+        <v>38</v>
       </c>
       <c r="BF35" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="BG35" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7344,186 +7344,186 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.08</v>
+        <v>3.85</v>
       </c>
       <c r="G36" t="n">
-        <v>2.26</v>
+        <v>4.2</v>
       </c>
       <c r="H36" t="n">
-        <v>3.95</v>
+        <v>2.32</v>
       </c>
       <c r="I36" t="n">
-        <v>4.6</v>
+        <v>2.38</v>
       </c>
       <c r="J36" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K36" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N36" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="O36" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="P36" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="U36" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V36" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="W36" t="n">
-        <v>1.77</v>
+        <v>1.31</v>
       </c>
       <c r="X36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z36" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y36" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB36" t="n">
         <v>36</v>
       </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH36" t="n">
+      <c r="BC36" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG36" t="n">
         <v>26</v>
       </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,191 +7533,191 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="G37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U37" t="n">
         <v>1.84</v>
       </c>
-      <c r="H37" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I37" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K37" t="n">
+      <c r="V37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS37" t="n">
         <v>4.1</v>
       </c>
-      <c r="L37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AT37" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU37" t="n">
         <v>6.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.7</v>
+        <v>13</v>
       </c>
       <c r="AW37" t="n">
         <v>4.1</v>
       </c>
       <c r="AX37" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY37" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.7</v>
+        <v>18.5</v>
       </c>
       <c r="BA37" t="n">
         <v>4.1</v>
       </c>
       <c r="BB37" t="n">
-        <v>3.65</v>
+        <v>20</v>
       </c>
       <c r="BC37" t="n">
-        <v>3.65</v>
+        <v>20</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE37" t="n">
         <v>4.2</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.4</v>
+        <v>18</v>
       </c>
       <c r="BG37" t="n">
         <v>4.1</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,186 +7732,186 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.09</v>
+        <v>1.76</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="H38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I38" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U38" t="n">
         <v>1.75</v>
       </c>
-      <c r="I38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K38" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="V38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
         <v>1.01</v>
       </c>
-      <c r="N38" t="n">
+      <c r="AQ38" t="n">
         <v>1.01</v>
       </c>
-      <c r="O38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AR38" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7926,373 +7926,567 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportes Concepcion</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" t="n">
         <v>1.75</v>
       </c>
-      <c r="G39" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="H39" t="n">
-        <v>5.1</v>
-      </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>1.98</v>
       </c>
       <c r="J39" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="K39" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="M39" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N39" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="O39" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="P39" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.95</v>
+        <v>1.37</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="S39" t="n">
-        <v>3.4</v>
+        <v>1.78</v>
       </c>
       <c r="T39" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="V39" t="n">
-        <v>1.21</v>
+        <v>2.02</v>
       </c>
       <c r="W39" t="n">
-        <v>2.18</v>
+        <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>11</v>
+        <v>1.25</v>
       </c>
       <c r="AQ39" t="n">
-        <v>13.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.5</v>
+        <v>1.59</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.8</v>
+        <v>1.52</v>
       </c>
       <c r="AT39" t="n">
-        <v>7.4</v>
+        <v>1.53</v>
       </c>
       <c r="AU39" t="n">
-        <v>7.8</v>
+        <v>1.43</v>
       </c>
       <c r="AV39" t="n">
-        <v>15.5</v>
+        <v>1.41</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.7</v>
+        <v>1.59</v>
       </c>
       <c r="AX39" t="n">
-        <v>9.6</v>
+        <v>1.54</v>
       </c>
       <c r="AY39" t="n">
-        <v>9</v>
+        <v>1.43</v>
       </c>
       <c r="AZ39" t="n">
-        <v>15.5</v>
+        <v>1.43</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.7</v>
+        <v>1.52</v>
       </c>
       <c r="BB39" t="n">
-        <v>16.5</v>
+        <v>1.26</v>
       </c>
       <c r="BC39" t="n">
-        <v>14.5</v>
+        <v>1.54</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.5</v>
+        <v>1.54</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.8</v>
+        <v>1.39</v>
       </c>
       <c r="BF39" t="n">
-        <v>9.199999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Deportes Concepcion</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-04-22 10:44:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Millonarios</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Tolima</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F41" t="n">
         <v>2.04</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G41" t="n">
         <v>2.24</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S41" t="n">
         <v>3.85</v>
       </c>
-      <c r="I40" t="n">
+      <c r="T41" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY41" t="n">
         <v>4.7</v>
       </c>
-      <c r="J40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K40" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA40" t="n">
+      <c r="AZ41" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC41" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH40" t="inlineStr">
-        <is>
-          <t>2026-04-22 07:36:40</t>
+      <c r="BD41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.39</v>
@@ -787,7 +787,7 @@
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
         <v>1.89</v>
@@ -796,7 +796,7 @@
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.71</v>
@@ -808,7 +808,7 @@
         <v>1.65</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
         <v>16.5</v>
@@ -823,7 +823,7 @@
         <v>36</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.4</v>
@@ -835,7 +835,7 @@
         <v>26</v>
       </c>
       <c r="AF2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
         <v>13.5</v>
@@ -844,7 +844,7 @@
         <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
         <v>50</v>
@@ -853,7 +853,7 @@
         <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
         <v>80</v>
@@ -862,7 +862,7 @@
         <v>27</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
         <v>14.5</v>
@@ -877,7 +877,7 @@
         <v>29</v>
       </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -889,7 +889,7 @@
         <v>23</v>
       </c>
       <c r="AX2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>12</v>
@@ -907,7 +907,7 @@
         <v>29</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE2" t="n">
         <v>48</v>
@@ -916,11 +916,11 @@
         <v>23</v>
       </c>
       <c r="BG2" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -963,10 +963,10 @@
         <v>1.63</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.3</v>
@@ -978,22 +978,22 @@
         <v>5.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P3" t="n">
         <v>2.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R3" t="n">
         <v>1.61</v>
       </c>
       <c r="S3" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U3" t="n">
         <v>2.3</v>
@@ -1005,22 +1005,22 @@
         <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AB3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
         <v>10.5</v>
@@ -1038,19 +1038,19 @@
         <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AM3" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
@@ -1074,7 +1074,7 @@
         <v>18.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV3" t="n">
         <v>9.199999999999999</v>
@@ -1083,19 +1083,19 @@
         <v>14</v>
       </c>
       <c r="AX3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
         <v>23</v>
       </c>
       <c r="BB3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
         <v>24</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G4" t="n">
         <v>2.66</v>
@@ -1172,19 +1172,19 @@
         <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
         <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
         <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
         <v>1.75</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -1345,13 +1345,13 @@
         <v>16.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I5" t="n">
         <v>1.33</v>
       </c>
       <c r="J5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K5" t="n">
         <v>6.4</v>
@@ -1363,25 +1363,25 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
         <v>1.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
         <v>1.69</v>
@@ -1390,7 +1390,7 @@
         <v>3.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1453,56 +1453,56 @@
         <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AV5" t="n">
         <v>8.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="I6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="J6" t="n">
         <v>5.3</v>
       </c>
       <c r="K6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1560,143 +1560,143 @@
         <v>12</v>
       </c>
       <c r="O6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P6" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q6" t="n">
         <v>1.21</v>
       </c>
       <c r="R6" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="S6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="U6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="V6" t="n">
         <v>2.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
         <v>23</v>
       </c>
-      <c r="AA6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
         <v>18.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
         <v>20</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO6" t="n">
         <v>4.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.04</v>
+        <v>5.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>19.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
         <v>18.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.98</v>
+        <v>5.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.99</v>
+        <v>5.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
         <v>12</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.04</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.97</v>
+        <v>5.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.04</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.04</v>
+        <v>26</v>
       </c>
       <c r="BF6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG6" t="n">
         <v>3.15</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
         <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,22 +1793,22 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1829,68 +1829,68 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="R8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.24</v>
       </c>
-      <c r="S8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.23</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,7 +1987,7 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
         <v>9</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2139,7 +2139,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.01</v>
@@ -2148,13 +2148,13 @@
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R9" t="n">
         <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2166,7 +2166,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -2327,25 +2327,25 @@
         <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
         <v>1.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
         <v>1.35</v>
@@ -2423,31 +2423,31 @@
         <v>3.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AS10" t="n">
         <v>3.95</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AU10" t="n">
         <v>3.05</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AW10" t="n">
         <v>3.85</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AY10" t="n">
         <v>3.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BA10" t="n">
         <v>4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H11" t="n">
         <v>2.96</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
         <v>2.44</v>
@@ -2527,7 +2527,7 @@
         <v>1.16</v>
       </c>
       <c r="N11" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.56</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>3.2</v>
@@ -2706,13 +2706,13 @@
         <v>2.26</v>
       </c>
       <c r="I12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.25</v>
@@ -2745,13 +2745,13 @@
         <v>2.62</v>
       </c>
       <c r="V12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W12" t="n">
         <v>1.46</v>
       </c>
       <c r="X12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y12" t="n">
         <v>16</v>
@@ -2775,7 +2775,7 @@
         <v>22</v>
       </c>
       <c r="AF12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG12" t="n">
         <v>13.5</v>
@@ -2805,16 +2805,16 @@
         <v>13</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
         <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT12" t="n">
         <v>15.5</v>
@@ -2823,10 +2823,10 @@
         <v>8.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX12" t="n">
         <v>21</v>
@@ -2835,7 +2835,7 @@
         <v>12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
         <v>24</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.82</v>
       </c>
       <c r="G13" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H13" t="n">
         <v>4.3</v>
@@ -2903,115 +2903,115 @@
         <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="T13" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="V13" t="n">
         <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Y13" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Z13" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA13" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AJ13" t="n">
         <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL13" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN13" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AO13" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AU13" t="n">
         <v>8.4</v>
@@ -3020,19 +3020,19 @@
         <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BB13" t="n">
         <v>17.5</v>
@@ -3044,17 +3044,17 @@
         <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
         <v>7.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -3091,10 +3091,10 @@
         <v>9.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="I14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J14" t="n">
         <v>4.5</v>
@@ -3133,7 +3133,7 @@
         <v>1.84</v>
       </c>
       <c r="V14" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="W14" t="n">
         <v>1.12</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -3291,13 +3291,13 @@
         <v>1.86</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -3312,7 +3312,7 @@
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R15" t="n">
         <v>1.48</v>
@@ -3324,7 +3324,7 @@
         <v>1.69</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
         <v>2.16</v>
@@ -3420,7 +3420,7 @@
         <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
         <v>8</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
         <v>2.26</v>
@@ -3488,7 +3488,7 @@
         <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.24</v>
@@ -3503,28 +3503,28 @@
         <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q16" t="n">
         <v>1.53</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U16" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X16" t="n">
         <v>27</v>
@@ -3539,7 +3539,7 @@
         <v>32</v>
       </c>
       <c r="AB16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC16" t="n">
         <v>10</v>
@@ -3593,10 +3593,10 @@
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
@@ -3626,7 +3626,7 @@
         <v>27</v>
       </c>
       <c r="BE16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF16" t="n">
         <v>14.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -3679,13 +3679,13 @@
         <v>2.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3697,7 +3697,7 @@
         <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
         <v>1.98</v>
@@ -3730,7 +3730,7 @@
         <v>17</v>
       </c>
       <c r="AA17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB17" t="n">
         <v>13</v>
@@ -3742,7 +3742,7 @@
         <v>12.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF17" t="n">
         <v>22</v>
@@ -3796,7 +3796,7 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX17" t="n">
         <v>17.5</v>
@@ -3811,16 +3811,16 @@
         <v>7.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
         <v>7.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF17" t="n">
         <v>7.8</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -3867,40 +3867,40 @@
         <v>3.2</v>
       </c>
       <c r="H18" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="I18" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P18" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
         <v>1.86</v>
@@ -3909,10 +3909,10 @@
         <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X18" t="n">
         <v>13</v>
@@ -3921,22 +3921,22 @@
         <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF18" t="n">
         <v>22</v>
@@ -3966,10 +3966,10 @@
         <v>75</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
         <v>9</v>
@@ -3978,31 +3978,31 @@
         <v>13.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT18" t="n">
         <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX18" t="n">
         <v>18</v>
       </c>
       <c r="AY18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="G19" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.31</v>
@@ -4088,7 +4088,7 @@
         <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
         <v>1.46</v>
@@ -4100,19 +4100,19 @@
         <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="X19" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
         <v>26</v>
@@ -4121,46 +4121,46 @@
         <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF19" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
@@ -4169,13 +4169,13 @@
         <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU19" t="n">
         <v>7.8</v>
@@ -4187,38 +4187,38 @@
         <v>30</v>
       </c>
       <c r="AX19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BB19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC19" t="n">
         <v>19.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H20" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I20" t="n">
         <v>2.64</v>
@@ -4264,7 +4264,7 @@
         <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L20" t="n">
         <v>1.46</v>
@@ -4273,115 +4273,115 @@
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="U20" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V20" t="n">
         <v>1.61</v>
       </c>
       <c r="W20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AG20" t="n">
         <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AJ20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL20" t="n">
         <v>60</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>50</v>
       </c>
       <c r="AM20" t="n">
         <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR20" t="n">
         <v>14.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY20" t="n">
         <v>12</v>
@@ -4393,26 +4393,26 @@
         <v>36</v>
       </c>
       <c r="BB20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE20" t="n">
         <v>40</v>
       </c>
       <c r="BF20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG20" t="n">
         <v>22</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="G21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H21" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>2.28</v>
+        <v>5.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="S21" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="V21" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="W21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>1.8</v>
       </c>
       <c r="G22" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
         <v>5.1</v>
@@ -4661,22 +4661,22 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S22" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T22" t="n">
         <v>1.6</v>
@@ -4685,10 +4685,10 @@
         <v>2.44</v>
       </c>
       <c r="V22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="X22" t="n">
         <v>27</v>
@@ -4724,7 +4724,7 @@
         <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
         <v>21</v>
@@ -4751,10 +4751,10 @@
         <v>16.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT22" t="n">
         <v>9.800000000000001</v>
@@ -4766,7 +4766,7 @@
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX22" t="n">
         <v>12.5</v>
@@ -4784,23 +4784,23 @@
         <v>18</v>
       </c>
       <c r="BC22" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BD22" t="n">
         <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF22" t="n">
         <v>7.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G23" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
         <v>3.25</v>
       </c>
       <c r="J23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.35</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.48</v>
@@ -4876,13 +4876,13 @@
         <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V23" t="n">
         <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X23" t="n">
         <v>11.5</v>
@@ -4891,19 +4891,19 @@
         <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
         <v>55</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE23" t="n">
         <v>40</v>
@@ -4912,7 +4912,7 @@
         <v>15.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
         <v>18.5</v>
@@ -4933,7 +4933,7 @@
         <v>120</v>
       </c>
       <c r="AN23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO23" t="n">
         <v>42</v>
@@ -4951,7 +4951,7 @@
         <v>50</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU23" t="n">
         <v>6.8</v>
@@ -4966,7 +4966,7 @@
         <v>14</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
         <v>17.5</v>
@@ -4975,7 +4975,7 @@
         <v>48</v>
       </c>
       <c r="BB23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC23" t="n">
         <v>27</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -5025,31 +5025,31 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G24" t="n">
         <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="I24" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O24" t="n">
         <v>1.37</v>
@@ -5061,31 +5061,31 @@
         <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W24" t="n">
         <v>1.21</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y24" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
@@ -5142,7 +5142,7 @@
         <v>8.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
         <v>12.5</v>
@@ -5154,41 +5154,41 @@
         <v>8.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG24" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G25" t="n">
         <v>3.8</v>
       </c>
       <c r="H25" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I25" t="n">
         <v>2.36</v>
@@ -5240,7 +5240,7 @@
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
         <v>3.15</v>
@@ -5285,13 +5285,13 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC25" t="n">
         <v>9.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
@@ -5336,7 +5336,7 @@
         <v>10</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AT25" t="n">
         <v>8.6</v>
@@ -5348,25 +5348,25 @@
         <v>8.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AY25" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BA25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC25" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4</v>
       </c>
       <c r="BD25" t="n">
         <v>4.1</v>
@@ -5378,11 +5378,11 @@
         <v>4.1</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -5413,64 +5413,64 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G26" t="n">
         <v>1.83</v>
       </c>
       <c r="H26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
         <v>4.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U26" t="n">
         <v>2.02</v>
       </c>
       <c r="V26" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W26" t="n">
         <v>2.2</v>
       </c>
       <c r="X26" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z26" t="n">
         <v>44</v>
@@ -5479,7 +5479,7 @@
         <v>170</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC26" t="n">
         <v>9.199999999999999</v>
@@ -5494,7 +5494,7 @@
         <v>11.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH26" t="n">
         <v>20</v>
@@ -5506,7 +5506,7 @@
         <v>19.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>36</v>
@@ -5515,7 +5515,7 @@
         <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO26" t="n">
         <v>85</v>
@@ -5527,13 +5527,13 @@
         <v>15.5</v>
       </c>
       <c r="AR26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT26" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>8</v>
       </c>
       <c r="AU26" t="n">
         <v>7.8</v>
@@ -5542,10 +5542,10 @@
         <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY26" t="n">
         <v>8.800000000000001</v>
@@ -5554,7 +5554,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB26" t="n">
         <v>15.5</v>
@@ -5563,20 +5563,20 @@
         <v>14.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -5607,170 +5607,170 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="G27" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="I27" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
         <v>4.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O27" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AA27" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AB27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH27" t="n">
         <v>22</v>
       </c>
-      <c r="AC27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>30</v>
-      </c>
       <c r="AI27" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ27" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AK27" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AL27" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AM27" t="n">
         <v>160</v>
       </c>
       <c r="AN27" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AO27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB27" t="n">
         <v>11</v>
       </c>
-      <c r="AP27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV27" t="n">
+      <c r="BC27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG27" t="n">
         <v>9</v>
       </c>
-      <c r="AW27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>44</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>17</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G28" t="n">
         <v>2.2</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
         <v>3.4</v>
@@ -5840,16 +5840,16 @@
         <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W28" t="n">
         <v>1.83</v>
@@ -5858,19 +5858,19 @@
         <v>11.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA28" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB28" t="n">
         <v>8.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD28" t="n">
         <v>16.5</v>
@@ -5891,7 +5891,7 @@
         <v>70</v>
       </c>
       <c r="AJ28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK28" t="n">
         <v>25</v>
@@ -5903,31 +5903,31 @@
         <v>130</v>
       </c>
       <c r="AN28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO28" t="n">
         <v>65</v>
       </c>
       <c r="AP28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS28" t="n">
         <v>70</v>
       </c>
       <c r="AT28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW28" t="n">
         <v>48</v>
@@ -5945,7 +5945,7 @@
         <v>55</v>
       </c>
       <c r="BB28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC28" t="n">
         <v>22</v>
@@ -5957,14 +5957,14 @@
         <v>40</v>
       </c>
       <c r="BF28" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
         <v>27</v>
       </c>
       <c r="AI29" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ29" t="n">
         <v>65</v>
@@ -6091,7 +6091,7 @@
         <v>55</v>
       </c>
       <c r="AL29" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM29" t="n">
         <v>280</v>
@@ -6106,25 +6106,25 @@
         <v>6.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AR29" t="n">
         <v>6.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT29" t="n">
         <v>7</v>
       </c>
       <c r="AU29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
         <v>5.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX29" t="n">
         <v>6.2</v>
@@ -6133,16 +6133,16 @@
         <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA29" t="n">
         <v>8.6</v>
       </c>
       <c r="BB29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC29" t="n">
         <v>8</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>7.8</v>
       </c>
       <c r="BD29" t="n">
         <v>8.6</v>
@@ -6154,11 +6154,11 @@
         <v>8.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -6231,10 +6231,10 @@
         <v>4.5</v>
       </c>
       <c r="T30" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U30" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V30" t="n">
         <v>1.54</v>
@@ -6297,13 +6297,13 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ30" t="n">
         <v>7.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
@@ -6318,7 +6318,7 @@
         <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
         <v>17.5</v>
@@ -6327,7 +6327,7 @@
         <v>12</v>
       </c>
       <c r="AZ30" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA30" t="n">
         <v>7.2</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -6386,19 +6386,19 @@
         <v>4.7</v>
       </c>
       <c r="G31" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H31" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I31" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="J31" t="n">
         <v>4.3</v>
       </c>
       <c r="K31" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6413,7 +6413,7 @@
         <v>1.19</v>
       </c>
       <c r="P31" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q31" t="n">
         <v>1.62</v>
@@ -6431,10 +6431,10 @@
         <v>2.34</v>
       </c>
       <c r="V31" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="W31" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
         <v>26</v>
@@ -6482,7 +6482,7 @@
         <v>55</v>
       </c>
       <c r="AM31" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN31" t="n">
         <v>1000</v>
@@ -6524,16 +6524,16 @@
         <v>15.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB31" t="n">
         <v>10</v>
       </c>
       <c r="BC31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE31" t="n">
         <v>9.6</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -6580,13 +6580,13 @@
         <v>1.8</v>
       </c>
       <c r="G32" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>3.95</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
         <v>3.95</v>
@@ -6607,7 +6607,7 @@
         <v>1.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q32" t="n">
         <v>1.6</v>
@@ -6616,7 +6616,7 @@
         <v>1.55</v>
       </c>
       <c r="S32" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="T32" t="n">
         <v>1.6</v>
@@ -6628,7 +6628,7 @@
         <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X32" t="n">
         <v>27</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G33" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H33" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I33" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J33" t="n">
         <v>4.6</v>
       </c>
       <c r="K33" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L33" t="n">
         <v>1.15</v>
@@ -6801,10 +6801,10 @@
         <v>1.09</v>
       </c>
       <c r="P33" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="R33" t="n">
         <v>2.12</v>
@@ -6813,7 +6813,7 @@
         <v>1.73</v>
       </c>
       <c r="T33" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="U33" t="n">
         <v>2.72</v>
@@ -6822,7 +6822,7 @@
         <v>1.15</v>
       </c>
       <c r="W33" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6873,19 +6873,19 @@
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AO33" t="n">
         <v>42</v>
       </c>
       <c r="AP33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR33" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>4.3</v>
       </c>
       <c r="AS33" t="n">
         <v>4.4</v>
@@ -6900,7 +6900,7 @@
         <v>18.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX33" t="n">
         <v>11.5</v>
@@ -6918,23 +6918,23 @@
         <v>12.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD33" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF33" t="n">
         <v>3.1</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G34" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="H34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I34" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J34" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>1.13</v>
@@ -6989,7 +6989,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O34" t="n">
         <v>1.07</v>
@@ -6998,37 +6998,37 @@
         <v>4.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S34" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="T34" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U34" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="V34" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W34" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="X34" t="n">
         <v>75</v>
       </c>
       <c r="Y34" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="Z34" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AA34" t="n">
-        <v>600</v>
+        <v>440</v>
       </c>
       <c r="AB34" t="n">
         <v>22</v>
@@ -7037,7 +7037,7 @@
         <v>23</v>
       </c>
       <c r="AD34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE34" t="n">
         <v>150</v>
@@ -7046,13 +7046,13 @@
         <v>14.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI34" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ34" t="n">
         <v>13.5</v>
@@ -7067,22 +7067,22 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AO34" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR34" t="n">
         <v>16</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AS34" t="n">
         <v>17</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>19.5</v>
       </c>
       <c r="AT34" t="n">
         <v>19</v>
@@ -7091,10 +7091,10 @@
         <v>20</v>
       </c>
       <c r="AV34" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AW34" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AX34" t="n">
         <v>12.5</v>
@@ -7103,32 +7103,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA34" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB34" t="n">
         <v>11.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD34" t="n">
         <v>20</v>
       </c>
       <c r="BE34" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BG34" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,22 +7183,22 @@
         <v>1.02</v>
       </c>
       <c r="N35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O35" t="n">
         <v>1.12</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>2.92</v>
       </c>
       <c r="Q35" t="n">
         <v>1.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="S35" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7377,7 +7377,7 @@
         <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O36" t="n">
         <v>1.09</v>
@@ -7404,7 +7404,7 @@
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -7547,28 +7547,28 @@
         </is>
       </c>
       <c r="F37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G37" t="n">
         <v>3.75</v>
       </c>
-      <c r="G37" t="n">
-        <v>3.8</v>
-      </c>
       <c r="H37" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I37" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J37" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K37" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L37" t="n">
         <v>1.43</v>
       </c>
       <c r="M37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N37" t="n">
         <v>3.85</v>
@@ -7580,7 +7580,7 @@
         <v>1.94</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
         <v>1.36</v>
@@ -7595,22 +7595,22 @@
         <v>2.14</v>
       </c>
       <c r="V37" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W37" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y37" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z37" t="n">
         <v>13.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB37" t="n">
         <v>14</v>
@@ -7619,7 +7619,7 @@
         <v>7.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE37" t="n">
         <v>23</v>
@@ -7631,7 +7631,7 @@
         <v>15</v>
       </c>
       <c r="AH37" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI37" t="n">
         <v>38</v>
@@ -7646,7 +7646,7 @@
         <v>55</v>
       </c>
       <c r="AM37" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
         <v>46</v>
@@ -7658,16 +7658,16 @@
         <v>12.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR37" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS37" t="n">
         <v>24</v>
       </c>
       <c r="AT37" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU37" t="n">
         <v>7.4</v>
@@ -7679,13 +7679,13 @@
         <v>20</v>
       </c>
       <c r="AX37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY37" t="n">
         <v>14</v>
       </c>
       <c r="AZ37" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA37" t="n">
         <v>34</v>
@@ -7700,7 +7700,7 @@
         <v>46</v>
       </c>
       <c r="BE37" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BF37" t="n">
         <v>38</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>3.7</v>
       </c>
       <c r="G38" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H38" t="n">
         <v>2.4</v>
@@ -7762,28 +7762,28 @@
         <v>1.49</v>
       </c>
       <c r="M38" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N38" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O38" t="n">
         <v>1.54</v>
       </c>
       <c r="P38" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q38" t="n">
         <v>2.62</v>
       </c>
       <c r="R38" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="T38" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U38" t="n">
         <v>1.81</v>
@@ -7792,10 +7792,10 @@
         <v>1.68</v>
       </c>
       <c r="W38" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X38" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y38" t="n">
         <v>7.8</v>
@@ -7810,7 +7810,7 @@
         <v>10.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD38" t="n">
         <v>12.5</v>
@@ -7825,7 +7825,7 @@
         <v>16</v>
       </c>
       <c r="AH38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI38" t="n">
         <v>65</v>
@@ -7858,7 +7858,7 @@
         <v>12.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AT38" t="n">
         <v>9.199999999999999</v>
@@ -7879,22 +7879,22 @@
         <v>14.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA38" t="n">
         <v>50</v>
       </c>
       <c r="BB38" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC38" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD38" t="n">
         <v>36</v>
       </c>
       <c r="BE38" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF38" t="n">
         <v>36</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -7938,13 +7938,13 @@
         <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H39" t="n">
         <v>3.9</v>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
         <v>3.1</v>
@@ -7986,7 +7986,7 @@
         <v>1.27</v>
       </c>
       <c r="W39" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X39" t="n">
         <v>12.5</v>
@@ -8043,10 +8043,10 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR39" t="n">
         <v>21</v>
@@ -8061,22 +8061,22 @@
         <v>6.4</v>
       </c>
       <c r="AV39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX39" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ39" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB39" t="n">
         <v>20</v>
@@ -8085,20 +8085,20 @@
         <v>20</v>
       </c>
       <c r="BD39" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE39" t="n">
         <v>4.2</v>
       </c>
       <c r="BF39" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -8129,79 +8129,79 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G40" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H40" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="I40" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J40" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K40" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L40" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M40" t="n">
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P40" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="Q40" t="n">
         <v>1.31</v>
       </c>
       <c r="R40" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="T40" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="U40" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
         <v>2.12</v>
       </c>
       <c r="W40" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Z40" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA40" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB40" t="n">
         <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE40" t="n">
         <v>20</v>
@@ -8210,7 +8210,7 @@
         <v>1000</v>
       </c>
       <c r="AG40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH40" t="n">
         <v>18</v>
@@ -8237,62 +8237,62 @@
         <v>6.4</v>
       </c>
       <c r="AP40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ40" t="n">
         <v>4</v>
       </c>
-      <c r="AQ40" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AR40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU40" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AV40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ40" t="n">
         <v>3.8</v>
       </c>
-      <c r="AT40" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AX40" t="n">
+      <c r="BA40" t="n">
         <v>4</v>
       </c>
-      <c r="AY40" t="n">
+      <c r="BB40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF40" t="n">
         <v>3.85</v>
       </c>
-      <c r="AZ40" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>12</v>
-      </c>
       <c r="BG40" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H41" t="n">
         <v>5</v>
@@ -8353,7 +8353,7 @@
         <v>1.32</v>
       </c>
       <c r="P41" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q41" t="n">
         <v>1.95</v>
@@ -8374,7 +8374,7 @@
         <v>1.21</v>
       </c>
       <c r="W41" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X41" t="n">
         <v>17</v>
@@ -8443,10 +8443,10 @@
         <v>4.8</v>
       </c>
       <c r="AT41" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU41" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV41" t="n">
         <v>15.5</v>
@@ -8455,10 +8455,10 @@
         <v>4.7</v>
       </c>
       <c r="AX41" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY41" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ41" t="n">
         <v>15.5</v>
@@ -8467,7 +8467,7 @@
         <v>4.7</v>
       </c>
       <c r="BB41" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC41" t="n">
         <v>14.5</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="G42" t="n">
         <v>1.84</v>
       </c>
       <c r="H42" t="n">
-        <v>1.09</v>
+        <v>5.1</v>
       </c>
       <c r="I42" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="J42" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8562,7 +8562,7 @@
         <v>1.01</v>
       </c>
       <c r="U42" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V42" t="n">
         <v>1.2</v>
@@ -8637,10 +8637,10 @@
         <v>1.01</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV42" t="n">
         <v>1.01</v>
@@ -8673,14 +8673,14 @@
         <v>1.01</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG42" t="n">
         <v>1.01</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -8711,61 +8711,61 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="G43" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="H43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K43" t="n">
         <v>3.85</v>
       </c>
-      <c r="I43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L43" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O43" t="n">
         <v>1.37</v>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R43" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T43" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="U43" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="V43" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y43" t="n">
         <v>1000</v>
@@ -8777,34 +8777,34 @@
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE43" t="n">
         <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG43" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH43" t="n">
         <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL43" t="n">
         <v>1000</v>
@@ -8816,65 +8816,65 @@
         <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP43" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.44</v>
+        <v>10</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT43" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU43" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.36</v>
+        <v>12</v>
       </c>
       <c r="AX43" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AY43" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.38</v>
+        <v>12</v>
       </c>
       <c r="BB43" t="n">
-        <v>2.66</v>
+        <v>8.6</v>
       </c>
       <c r="BC43" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD43" t="n">
-        <v>2.52</v>
+        <v>10.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.79</v>
+        <v>13</v>
       </c>
       <c r="BF43" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG43" t="n">
-        <v>2.56</v>
+        <v>12</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-22 15:17:28</t>
+          <t>2026-04-22 17:35:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -763,7 +763,7 @@
         <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
         <v>2.54</v>
@@ -781,25 +781,25 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
         <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
         <v>12</v>
@@ -862,7 +862,7 @@
         <v>27</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AP2" t="n">
         <v>14.5</v>
@@ -877,7 +877,7 @@
         <v>29</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="I3" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>1.3</v>
@@ -981,7 +981,7 @@
         <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q3" t="n">
         <v>1.62</v>
@@ -993,128 +993,128 @@
         <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V3" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X3" t="n">
         <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT3" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AZ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB3" t="n">
         <v>16.5</v>
       </c>
-      <c r="BA3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BC3" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="BD3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE3" t="n">
-        <v>60</v>
+        <v>15.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BG3" t="n">
         <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="G4" t="n">
         <v>2.66</v>
@@ -1154,10 +1154,10 @@
         <v>2.96</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1169,7 +1169,7 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
@@ -1184,16 +1184,16 @@
         <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
         <v>1.6</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="G5" t="n">
         <v>16.5</v>
@@ -1348,52 +1348,52 @@
         <v>1.28</v>
       </c>
       <c r="I5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1411,7 +1411,7 @@
         <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1444,65 +1444,65 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT5" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
         <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>6</v>
       </c>
-      <c r="AX5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.62</v>
+        <v>6.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.62</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.62</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
         <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -1536,10 +1536,10 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I6" t="n">
         <v>1.77</v>
@@ -1548,7 +1548,7 @@
         <v>5.3</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1563,10 +1563,10 @@
         <v>1.07</v>
       </c>
       <c r="P6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R6" t="n">
         <v>2.56</v>
@@ -1575,19 +1575,19 @@
         <v>1.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="U6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="V6" t="n">
         <v>2.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Y6" t="n">
         <v>34</v>
@@ -1617,7 +1617,7 @@
         <v>30</v>
       </c>
       <c r="AH6" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
         <v>20</v>
@@ -1632,7 +1632,7 @@
         <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN6" t="n">
         <v>17.5</v>
@@ -1641,19 +1641,19 @@
         <v>4.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ6" t="n">
         <v>19.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
         <v>18.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU6" t="n">
         <v>14.5</v>
@@ -1665,7 +1665,7 @@
         <v>13.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY6" t="n">
         <v>20</v>
@@ -1680,23 +1680,23 @@
         <v>5.7</v>
       </c>
       <c r="BC6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD6" t="n">
         <v>5.2</v>
       </c>
-      <c r="BD6" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE6" t="n">
-        <v>26</v>
+        <v>5.3</v>
       </c>
       <c r="BF6" t="n">
         <v>12.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G7" t="n">
         <v>1.94</v>
@@ -1811,13 +1811,13 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
         <v>24</v>
@@ -1841,10 +1841,10 @@
         <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
         <v>7.4</v>
@@ -1859,16 +1859,16 @@
         <v>4.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AZ7" t="n">
         <v>4.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB7" t="n">
         <v>15.5</v>
@@ -1877,7 +1877,7 @@
         <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
         <v>5</v>
@@ -1886,11 +1886,11 @@
         <v>10.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.48</v>
@@ -1945,34 +1945,34 @@
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="X8" t="n">
         <v>11</v>
@@ -1990,7 +1990,7 @@
         <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2011,10 +2011,10 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2023,22 +2023,22 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ8" t="n">
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT8" t="n">
         <v>5.1</v>
@@ -2047,44 +2047,44 @@
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.3</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.35</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>1.39</v>
       </c>
       <c r="G10" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.28</v>
+        <v>1.39</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,34 +2333,34 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
         <v>1.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S10" t="n">
         <v>1.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
@@ -2384,7 +2384,7 @@
         <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
         <v>27</v>
@@ -2417,46 +2417,46 @@
         <v>28</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AQ10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV10" t="n">
         <v>3.3</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.4</v>
       </c>
       <c r="AW10" t="n">
         <v>3.85</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BA10" t="n">
         <v>4</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BD10" t="n">
         <v>4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="G11" t="n">
         <v>3.45</v>
@@ -2512,19 +2512,19 @@
         <v>2.96</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>2.44</v>
       </c>
       <c r="K11" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.57</v>
       </c>
       <c r="M11" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
         <v>2.1</v>
@@ -2536,7 +2536,7 @@
         <v>1.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
         <v>1.12</v>
@@ -2545,13 +2545,13 @@
         <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
         <v>1.41</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
         <v>3.2</v>
@@ -2706,7 +2706,7 @@
         <v>2.26</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -2730,7 +2730,7 @@
         <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
         <v>1.61</v>
@@ -2745,7 +2745,7 @@
         <v>2.62</v>
       </c>
       <c r="V12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W12" t="n">
         <v>1.46</v>
@@ -2799,22 +2799,22 @@
         <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>13</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AT12" t="n">
         <v>15.5</v>
@@ -2823,10 +2823,10 @@
         <v>8.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>21</v>
@@ -2841,7 +2841,7 @@
         <v>24</v>
       </c>
       <c r="BB12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
         <v>25</v>
@@ -2850,7 +2850,7 @@
         <v>28</v>
       </c>
       <c r="BE12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF12" t="n">
         <v>15</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.82</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H13" t="n">
         <v>4.3</v>
@@ -2903,10 +2903,10 @@
         <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.26</v>
@@ -2915,19 +2915,19 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
         <v>1.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S13" t="n">
         <v>2.44</v>
@@ -2942,7 +2942,7 @@
         <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X13" t="n">
         <v>29</v>
@@ -2951,13 +2951,13 @@
         <v>25</v>
       </c>
       <c r="Z13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA13" t="n">
         <v>85</v>
       </c>
       <c r="AB13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC13" t="n">
         <v>11.5</v>
@@ -2969,7 +2969,7 @@
         <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
@@ -2999,16 +2999,16 @@
         <v>38</v>
       </c>
       <c r="AP13" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13" t="n">
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT13" t="n">
         <v>11.5</v>
@@ -3020,7 +3020,7 @@
         <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
         <v>12.5</v>
@@ -3041,20 +3041,20 @@
         <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF13" t="n">
         <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         <v>2.98</v>
       </c>
       <c r="T14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
         <v>1.84</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3297,28 +3297,28 @@
         <v>4.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
         <v>1.69</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I16" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J16" t="n">
         <v>4.1</v>
@@ -3503,34 +3503,34 @@
         <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V16" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X16" t="n">
         <v>27</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Z16" t="n">
         <v>19.5</v>
@@ -3539,7 +3539,7 @@
         <v>32</v>
       </c>
       <c r="AB16" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AC16" t="n">
         <v>10</v>
@@ -3551,22 +3551,22 @@
         <v>21</v>
       </c>
       <c r="AF16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH16" t="n">
         <v>15</v>
       </c>
       <c r="AI16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
         <v>50</v>
       </c>
       <c r="AK16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL16" t="n">
         <v>32</v>
@@ -3575,34 +3575,34 @@
         <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AO16" t="n">
         <v>11</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS16" t="n">
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX16" t="n">
         <v>22</v>
@@ -3614,10 +3614,10 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC16" t="n">
         <v>25</v>
@@ -3626,17 +3626,17 @@
         <v>27</v>
       </c>
       <c r="BE16" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
         <v>14.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="G17" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="H17" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>3.55</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3694,61 +3694,61 @@
         <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
         <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
         <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U17" t="n">
         <v>2.18</v>
       </c>
       <c r="V17" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="W17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
         <v>13</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH17" t="n">
         <v>18</v>
@@ -3757,10 +3757,10 @@
         <v>42</v>
       </c>
       <c r="AJ17" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL17" t="n">
         <v>48</v>
@@ -3769,25 +3769,25 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU17" t="n">
         <v>7.2</v>
@@ -3796,41 +3796,41 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.8</v>
+        <v>27</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BG17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3861,88 +3861,88 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G18" t="n">
         <v>3.05</v>
       </c>
-      <c r="G18" t="n">
-        <v>3.2</v>
-      </c>
       <c r="H18" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="I18" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W18" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
         <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD18" t="n">
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AF18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
         <v>18.5</v>
@@ -3954,34 +3954,34 @@
         <v>60</v>
       </c>
       <c r="AK18" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AL18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM18" t="n">
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS18" t="n">
         <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3990,41 +3990,41 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BB18" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BC18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF18" t="n">
         <v>22</v>
       </c>
       <c r="BG18" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
         <v>2.32</v>
@@ -4067,7 +4067,7 @@
         <v>3.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
         <v>3.85</v>
@@ -4082,40 +4082,40 @@
         <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
         <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
         <v>2.96</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U19" t="n">
         <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X19" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y19" t="n">
         <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA19" t="n">
         <v>60</v>
@@ -4124,7 +4124,7 @@
         <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
         <v>14.5</v>
@@ -4133,34 +4133,34 @@
         <v>36</v>
       </c>
       <c r="AF19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI19" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ19" t="n">
         <v>30</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
         <v>15.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
@@ -4169,16 +4169,16 @@
         <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV19" t="n">
         <v>12.5</v>
@@ -4187,16 +4187,16 @@
         <v>30</v>
       </c>
       <c r="AX19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB19" t="n">
         <v>24</v>
@@ -4205,20 +4205,20 @@
         <v>19.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE19" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BF19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H20" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I20" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J20" t="n">
         <v>3.35</v>
@@ -4267,82 +4267,82 @@
         <v>3.45</v>
       </c>
       <c r="L20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O20" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>1.61</v>
       </c>
       <c r="W20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD20" t="n">
         <v>13</v>
       </c>
-      <c r="Y20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>12</v>
-      </c>
       <c r="AE20" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>60</v>
       </c>
       <c r="AJ20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL20" t="n">
         <v>60</v>
@@ -4360,37 +4360,37 @@
         <v>10.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
         <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY20" t="n">
         <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB20" t="n">
         <v>29</v>
@@ -4399,20 +4399,20 @@
         <v>24</v>
       </c>
       <c r="BD20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE20" t="n">
         <v>40</v>
       </c>
       <c r="BF20" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BG20" t="n">
         <v>22</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="H21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I21" t="n">
         <v>1.98</v>
       </c>
-      <c r="I21" t="n">
-        <v>2.08</v>
-      </c>
       <c r="J21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O21" t="n">
         <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S21" t="n">
         <v>2.22</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U21" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V21" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="X21" t="n">
         <v>30</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC21" t="n">
         <v>11.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF21" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AG21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK21" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
         <v>60</v>
       </c>
       <c r="AN21" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU21" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>9.4</v>
       </c>
       <c r="AV21" t="n">
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AY21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ21" t="n">
         <v>13.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC21" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BD21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF21" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="G22" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.25</v>
@@ -4664,31 +4664,31 @@
         <v>5.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R22" t="n">
         <v>1.61</v>
       </c>
       <c r="S22" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="X22" t="n">
         <v>27</v>
@@ -4715,7 +4715,7 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
@@ -4745,13 +4745,13 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>16.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS22" t="n">
         <v>7.8</v>
@@ -4760,28 +4760,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV22" t="n">
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
         <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BC22" t="n">
         <v>14.5</v>
@@ -4793,14 +4793,14 @@
         <v>7.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG22" t="n">
         <v>7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I23" t="n">
         <v>3.2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>3.25</v>
       </c>
       <c r="J23" t="n">
         <v>3.3</v>
@@ -4873,16 +4873,16 @@
         <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U23" t="n">
         <v>2.06</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X23" t="n">
         <v>11.5</v>
@@ -4891,7 +4891,7 @@
         <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA23" t="n">
         <v>55</v>
@@ -4906,7 +4906,7 @@
         <v>13.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
         <v>15.5</v>
@@ -4936,7 +4936,7 @@
         <v>28</v>
       </c>
       <c r="AO23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP23" t="n">
         <v>10.5</v>
@@ -4948,7 +4948,7 @@
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AT23" t="n">
         <v>8.800000000000001</v>
@@ -4960,7 +4960,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX23" t="n">
         <v>14</v>
@@ -4975,16 +4975,16 @@
         <v>48</v>
       </c>
       <c r="BB23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC23" t="n">
         <v>27</v>
       </c>
       <c r="BD23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BF23" t="n">
         <v>25</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
         <v>3.15</v>
       </c>
       <c r="O24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P24" t="n">
         <v>1.81</v>
@@ -5061,7 +5061,7 @@
         <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
         <v>3.6</v>
@@ -5073,7 +5073,7 @@
         <v>1.86</v>
       </c>
       <c r="V24" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="W24" t="n">
         <v>1.21</v>
@@ -5184,11 +5184,11 @@
         <v>4.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G25" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I25" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="J25" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="K25" t="n">
         <v>3.7</v>
@@ -5243,43 +5243,43 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U25" t="n">
         <v>1.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W25" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
@@ -5288,7 +5288,7 @@
         <v>14</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
         <v>14</v>
@@ -5336,7 +5336,7 @@
         <v>10</v>
       </c>
       <c r="AS25" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT25" t="n">
         <v>8.6</v>
@@ -5348,41 +5348,41 @@
         <v>8.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX25" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AY25" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I26" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K26" t="n">
         <v>4.3</v>
@@ -5443,52 +5443,52 @@
         <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
         <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U26" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V26" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X26" t="n">
         <v>18.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z26" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA26" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD26" t="n">
         <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF26" t="n">
         <v>11.5</v>
@@ -5497,10 +5497,10 @@
         <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ26" t="n">
         <v>19.5</v>
@@ -5509,16 +5509,16 @@
         <v>19</v>
       </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM26" t="n">
         <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO26" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP26" t="n">
         <v>13.5</v>
@@ -5527,10 +5527,10 @@
         <v>15.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
@@ -5542,10 +5542,10 @@
         <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY26" t="n">
         <v>8.800000000000001</v>
@@ -5554,29 +5554,29 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BB26" t="n">
         <v>15.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD26" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
         <v>6.6</v>
       </c>
       <c r="H27" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="I27" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
         <v>4.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -5634,40 +5634,40 @@
         <v>3.95</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T27" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V27" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W27" t="n">
         <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z27" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA27" t="n">
         <v>16</v>
@@ -5676,10 +5676,10 @@
         <v>20</v>
       </c>
       <c r="AC27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE27" t="n">
         <v>17</v>
@@ -5700,28 +5700,28 @@
         <v>180</v>
       </c>
       <c r="AK27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM27" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN27" t="n">
         <v>110</v>
       </c>
       <c r="AO27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AS27" t="n">
         <v>14.5</v>
@@ -5730,19 +5730,19 @@
         <v>17.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ27" t="n">
         <v>19.5</v>
@@ -5751,26 +5751,26 @@
         <v>30</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BD27" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG27" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G28" t="n">
         <v>2.2</v>
@@ -5816,16 +5816,16 @@
         <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
         <v>1.4</v>
@@ -5834,16 +5834,16 @@
         <v>1.79</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R28" t="n">
         <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -5861,10 +5861,10 @@
         <v>13.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA28" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB28" t="n">
         <v>8.4</v>
@@ -5885,16 +5885,16 @@
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI28" t="n">
         <v>70</v>
       </c>
       <c r="AJ28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL28" t="n">
         <v>44</v>
@@ -5903,13 +5903,13 @@
         <v>130</v>
       </c>
       <c r="AN28" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO28" t="n">
         <v>65</v>
       </c>
       <c r="AP28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>12.5</v>
@@ -5921,7 +5921,7 @@
         <v>70</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5939,7 +5939,7 @@
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA28" t="n">
         <v>55</v>
@@ -5951,20 +5951,20 @@
         <v>22</v>
       </c>
       <c r="BD28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE28" t="n">
         <v>40</v>
       </c>
       <c r="BF28" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG28" t="n">
         <v>60</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H29" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
         <v>2.76</v>
@@ -6025,7 +6025,7 @@
         <v>1.65</v>
       </c>
       <c r="P29" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q29" t="n">
         <v>3</v>
@@ -6043,10 +6043,10 @@
         <v>1.69</v>
       </c>
       <c r="V29" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W29" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X29" t="n">
         <v>8.199999999999999</v>
@@ -6061,13 +6061,13 @@
         <v>60</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD29" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE29" t="n">
         <v>55</v>
@@ -6079,7 +6079,7 @@
         <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="n">
         <v>100</v>
@@ -6097,7 +6097,7 @@
         <v>280</v>
       </c>
       <c r="AN29" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO29" t="n">
         <v>75</v>
@@ -6109,10 +6109,10 @@
         <v>6.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT29" t="n">
         <v>7</v>
@@ -6121,44 +6121,44 @@
         <v>6</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX29" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY29" t="n">
         <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BE29" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>3.05</v>
       </c>
       <c r="G30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H30" t="n">
         <v>2.6</v>
@@ -6213,7 +6213,7 @@
         <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
         <v>1.46</v>
@@ -6222,7 +6222,7 @@
         <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="R30" t="n">
         <v>1.22</v>
@@ -6231,16 +6231,16 @@
         <v>4.5</v>
       </c>
       <c r="T30" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U30" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V30" t="n">
         <v>1.54</v>
       </c>
       <c r="W30" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X30" t="n">
         <v>12</v>
@@ -6270,7 +6270,7 @@
         <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH30" t="n">
         <v>1000</v>
@@ -6312,7 +6312,7 @@
         <v>8.6</v>
       </c>
       <c r="AU30" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV30" t="n">
         <v>10.5</v>
@@ -6327,7 +6327,7 @@
         <v>12</v>
       </c>
       <c r="AZ30" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA30" t="n">
         <v>7.2</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G31" t="n">
         <v>5.6</v>
@@ -6392,13 +6392,13 @@
         <v>1.69</v>
       </c>
       <c r="I31" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="J31" t="n">
         <v>4.3</v>
       </c>
       <c r="K31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6413,13 +6413,13 @@
         <v>1.19</v>
       </c>
       <c r="P31" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R31" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S31" t="n">
         <v>2.44</v>
@@ -6428,10 +6428,10 @@
         <v>1.62</v>
       </c>
       <c r="U31" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V31" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="W31" t="n">
         <v>1.22</v>
@@ -6467,7 +6467,7 @@
         <v>21</v>
       </c>
       <c r="AH31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI31" t="n">
         <v>27</v>
@@ -6476,7 +6476,7 @@
         <v>120</v>
       </c>
       <c r="AK31" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AL31" t="n">
         <v>55</v>
@@ -6485,13 +6485,13 @@
         <v>75</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO31" t="n">
         <v>7.4</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AQ31" t="n">
         <v>10.5</v>
@@ -6500,13 +6500,13 @@
         <v>10.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT31" t="n">
         <v>19.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
@@ -6524,19 +6524,19 @@
         <v>15.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE31" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>9.6</v>
       </c>
       <c r="BF31" t="n">
         <v>8.800000000000001</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H32" t="n">
         <v>3.95</v>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
         <v>3.95</v>
@@ -6628,10 +6628,10 @@
         <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y32" t="n">
         <v>24</v>
@@ -6685,13 +6685,13 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ32" t="n">
         <v>15.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS32" t="n">
         <v>4.7</v>
@@ -6700,31 +6700,31 @@
         <v>9.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
         <v>12.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB32" t="n">
         <v>16</v>
       </c>
       <c r="BC32" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD32" t="n">
         <v>21</v>
@@ -6733,14 +6733,14 @@
         <v>4.7</v>
       </c>
       <c r="BF32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -6774,16 +6774,16 @@
         <v>1.47</v>
       </c>
       <c r="G33" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="H33" t="n">
         <v>5.7</v>
       </c>
       <c r="I33" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J33" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="K33" t="n">
         <v>6.8</v>
@@ -6804,7 +6804,7 @@
         <v>3.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="R33" t="n">
         <v>2.12</v>
@@ -6813,16 +6813,16 @@
         <v>1.73</v>
       </c>
       <c r="T33" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U33" t="n">
         <v>2.72</v>
       </c>
       <c r="V33" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W33" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6879,10 +6879,10 @@
         <v>42</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AR33" t="n">
         <v>4.2</v>
@@ -6903,28 +6903,28 @@
         <v>4.2</v>
       </c>
       <c r="AX33" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY33" t="n">
         <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA33" t="n">
         <v>4.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC33" t="n">
         <v>12</v>
       </c>
       <c r="BD33" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF33" t="n">
         <v>3.1</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="G34" t="n">
         <v>1.25</v>
       </c>
       <c r="H34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I34" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="J34" t="n">
         <v>8</v>
@@ -6995,25 +6995,25 @@
         <v>1.07</v>
       </c>
       <c r="P34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q34" t="n">
         <v>1.23</v>
       </c>
       <c r="R34" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="S34" t="n">
         <v>1.6</v>
       </c>
       <c r="T34" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U34" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V34" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W34" t="n">
         <v>5</v>
@@ -7022,13 +7022,13 @@
         <v>75</v>
       </c>
       <c r="Y34" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Z34" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AA34" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="AB34" t="n">
         <v>22</v>
@@ -7037,22 +7037,22 @@
         <v>23</v>
       </c>
       <c r="AD34" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AE34" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF34" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI34" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ34" t="n">
         <v>13.5</v>
@@ -7067,25 +7067,25 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="AO34" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ34" t="n">
         <v>14</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS34" t="n">
         <v>15</v>
       </c>
-      <c r="AR34" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>17</v>
-      </c>
       <c r="AT34" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU34" t="n">
         <v>20</v>
@@ -7094,7 +7094,7 @@
         <v>13</v>
       </c>
       <c r="AW34" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX34" t="n">
         <v>12.5</v>
@@ -7103,32 +7103,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB34" t="n">
         <v>11.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD34" t="n">
         <v>20</v>
       </c>
       <c r="BE34" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BG34" t="n">
-        <v>14.5</v>
+        <v>60</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="G35" t="n">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="H35" t="n">
-        <v>2.32</v>
+        <v>1.16</v>
       </c>
       <c r="I35" t="n">
-        <v>15.5</v>
+        <v>48</v>
       </c>
       <c r="J35" t="n">
         <v>4.1</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G36" t="n">
-        <v>200</v>
+        <v>970</v>
       </c>
       <c r="H36" t="n">
-        <v>2.12</v>
+        <v>2.68</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J36" t="n">
         <v>1.03</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7395,16 +7395,16 @@
         <v>1.35</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U36" t="n">
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -7562,16 +7562,16 @@
         <v>3.45</v>
       </c>
       <c r="K37" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L37" t="n">
         <v>1.43</v>
       </c>
       <c r="M37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N37" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O37" t="n">
         <v>1.34</v>
@@ -7580,37 +7580,37 @@
         <v>1.94</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R37" t="n">
         <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T37" t="n">
         <v>1.82</v>
       </c>
       <c r="U37" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V37" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W37" t="n">
         <v>1.36</v>
       </c>
       <c r="X37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z37" t="n">
         <v>13.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB37" t="n">
         <v>14</v>
@@ -7622,37 +7622,37 @@
         <v>11</v>
       </c>
       <c r="AE37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF37" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG37" t="n">
         <v>15</v>
       </c>
       <c r="AH37" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI37" t="n">
         <v>38</v>
       </c>
       <c r="AJ37" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK37" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL37" t="n">
         <v>55</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN37" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO37" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP37" t="n">
         <v>12.5</v>
@@ -7703,14 +7703,14 @@
         <v>80</v>
       </c>
       <c r="BF37" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG37" t="n">
         <v>15</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -7741,16 +7741,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="G38" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="H38" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I38" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="J38" t="n">
         <v>3.05</v>
@@ -7759,7 +7759,7 @@
         <v>3.15</v>
       </c>
       <c r="L38" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="M38" t="n">
         <v>1.12</v>
@@ -7768,13 +7768,13 @@
         <v>2.74</v>
       </c>
       <c r="O38" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P38" t="n">
         <v>1.58</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R38" t="n">
         <v>1.21</v>
@@ -7783,46 +7783,46 @@
         <v>5.2</v>
       </c>
       <c r="T38" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V38" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="W38" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="X38" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z38" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA38" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB38" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD38" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE38" t="n">
         <v>34</v>
       </c>
       <c r="AF38" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG38" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH38" t="n">
         <v>23</v>
@@ -7831,61 +7831,61 @@
         <v>65</v>
       </c>
       <c r="AJ38" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK38" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL38" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AM38" t="n">
         <v>180</v>
       </c>
       <c r="AN38" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO38" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP38" t="n">
         <v>8</v>
       </c>
       <c r="AQ38" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS38" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AT38" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU38" t="n">
         <v>6.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW38" t="n">
         <v>28</v>
       </c>
       <c r="AX38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY38" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ38" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA38" t="n">
         <v>50</v>
       </c>
       <c r="BB38" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BC38" t="n">
         <v>29</v>
@@ -7897,14 +7897,14 @@
         <v>46</v>
       </c>
       <c r="BF38" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BG38" t="n">
         <v>27</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -7941,10 +7941,10 @@
         <v>2.3</v>
       </c>
       <c r="H39" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>3.1</v>
@@ -7953,7 +7953,7 @@
         <v>3.6</v>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M39" t="n">
         <v>1.1</v>
@@ -7977,10 +7977,10 @@
         <v>4.4</v>
       </c>
       <c r="T39" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U39" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V39" t="n">
         <v>1.27</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
         <v>3.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="R40" t="n">
         <v>2</v>
@@ -8246,28 +8246,28 @@
         <v>3.9</v>
       </c>
       <c r="AS40" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT40" t="n">
         <v>4.2</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AV40" t="n">
         <v>10.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AX40" t="n">
         <v>4.3</v>
       </c>
       <c r="AY40" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ40" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BA40" t="n">
         <v>4</v>
@@ -8276,7 +8276,7 @@
         <v>4.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BD40" t="n">
         <v>4.2</v>
@@ -8288,11 +8288,11 @@
         <v>3.85</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
         <v>4.1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M41" t="n">
         <v>1.07</v>
@@ -8353,7 +8353,7 @@
         <v>1.32</v>
       </c>
       <c r="P41" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q41" t="n">
         <v>1.95</v>
@@ -8443,10 +8443,10 @@
         <v>4.8</v>
       </c>
       <c r="AT41" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU41" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV41" t="n">
         <v>15.5</v>
@@ -8455,10 +8455,10 @@
         <v>4.7</v>
       </c>
       <c r="AX41" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY41" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AZ41" t="n">
         <v>15.5</v>
@@ -8467,7 +8467,7 @@
         <v>4.7</v>
       </c>
       <c r="BB41" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC41" t="n">
         <v>14.5</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="G42" t="n">
         <v>1.84</v>
@@ -8526,43 +8526,43 @@
         <v>5.1</v>
       </c>
       <c r="I42" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J42" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N42" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="O42" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P42" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="R42" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S42" t="n">
-        <v>1.97</v>
+        <v>3.9</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V42" t="n">
         <v>1.2</v>
@@ -8571,10 +8571,10 @@
         <v>2.18</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z42" t="n">
         <v>1000</v>
@@ -8583,10 +8583,10 @@
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD42" t="n">
         <v>1000</v>
@@ -8595,10 +8595,10 @@
         <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
         <v>1000</v>
@@ -8625,62 +8625,62 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF42" t="n">
         <v>10</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -8729,13 +8729,13 @@
         <v>3.85</v>
       </c>
       <c r="L43" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O43" t="n">
         <v>1.37</v>
@@ -8750,13 +8750,13 @@
         <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T43" t="n">
         <v>1.95</v>
       </c>
       <c r="U43" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V43" t="n">
         <v>1.25</v>
@@ -8777,10 +8777,10 @@
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
         <v>19.5</v>
@@ -8825,10 +8825,10 @@
         <v>14</v>
       </c>
       <c r="AR43" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT43" t="n">
         <v>7.4</v>
@@ -8837,44 +8837,44 @@
         <v>7.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>8.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="AW43" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AX43" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="AY43" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ43" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA43" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="BB43" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BC43" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BD43" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE43" t="n">
-        <v>13</v>
+        <v>4.9</v>
       </c>
       <c r="BF43" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -8929,22 +8929,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="O44" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="P44" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="R44" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S44" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I2" t="n">
         <v>2.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.54</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -790,10 +790,10 @@
         <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>3.3</v>
@@ -802,13 +802,13 @@
         <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
         <v>15.5</v>
@@ -835,13 +835,13 @@
         <v>26</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
@@ -850,7 +850,7 @@
         <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
         <v>42</v>
@@ -901,13 +901,13 @@
         <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC2" t="n">
         <v>29</v>
       </c>
       <c r="BD2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
         <v>48</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G3" t="n">
         <v>6.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
         <v>4.8</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.3</v>
@@ -975,22 +975,22 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T3" t="n">
         <v>1.76</v>
@@ -999,7 +999,7 @@
         <v>2.26</v>
       </c>
       <c r="V3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="W3" t="n">
         <v>1.19</v>
@@ -1020,7 +1020,7 @@
         <v>27</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>10</v>
@@ -1044,7 +1044,7 @@
         <v>160</v>
       </c>
       <c r="AK3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
@@ -1056,13 +1056,13 @@
         <v>65</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX3" t="n">
         <v>42</v>
@@ -1089,32 +1089,32 @@
         <v>20</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BD3" t="n">
         <v>50</v>
       </c>
       <c r="BE3" t="n">
-        <v>15.5</v>
+        <v>60</v>
       </c>
       <c r="BF3" t="n">
         <v>50</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1145,46 +1145,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.75</v>
@@ -1193,10 +1193,10 @@
         <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1348,16 +1348,16 @@
         <v>1.28</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="J5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
         <v>6.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1372,7 +1372,7 @@
         <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.45</v>
@@ -1387,22 +1387,22 @@
         <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB5" t="n">
         <v>1000</v>
@@ -1411,7 +1411,7 @@
         <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1444,10 +1444,10 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
@@ -1459,7 +1459,7 @@
         <v>7.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.6</v>
+        <v>26</v>
       </c>
       <c r="AU5" t="n">
         <v>11</v>
@@ -1468,41 +1468,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG5" t="n">
         <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1536,22 +1536,22 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="I6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J6" t="n">
         <v>5.3</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
@@ -1563,7 +1563,7 @@
         <v>1.07</v>
       </c>
       <c r="P6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Q6" t="n">
         <v>1.22</v>
@@ -1572,16 +1572,16 @@
         <v>2.56</v>
       </c>
       <c r="S6" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="T6" t="n">
         <v>1.33</v>
       </c>
       <c r="U6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="V6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W6" t="n">
         <v>1.27</v>
@@ -1611,7 +1611,7 @@
         <v>18.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
         <v>30</v>
@@ -1650,13 +1650,13 @@
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
         <v>5.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AV6" t="n">
         <v>9.800000000000001</v>
@@ -1674,19 +1674,19 @@
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="BF6" t="n">
         <v>12.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>5.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -1754,22 +1754,22 @@
         <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
         <v>1.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
         <v>1.98</v>
@@ -1799,16 +1799,16 @@
         <v>9.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
         <v>24</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1841,10 +1841,10 @@
         <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
         <v>7.4</v>
@@ -1853,44 +1853,44 @@
         <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>14.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AX7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY7" t="n">
         <v>4</v>
       </c>
-      <c r="AY7" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AZ7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.3</v>
       </c>
-      <c r="BA7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG7" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
         <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ8" t="n">
         <v>17.5</v>
@@ -2077,14 +2077,14 @@
         <v>6.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG8" t="n">
         <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2142,19 +2142,19 @@
         <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="R9" t="n">
         <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
         <v>1.35</v>
@@ -2417,52 +2417,52 @@
         <v>28</v>
       </c>
       <c r="AP10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT10" t="n">
         <v>3.45</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AU10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AW10" t="n">
         <v>3.85</v>
       </c>
       <c r="AX10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>3.7</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.6</v>
       </c>
       <c r="BA10" t="n">
         <v>4</v>
       </c>
       <c r="BB10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC10" t="n">
         <v>4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.95</v>
       </c>
       <c r="BD10" t="n">
         <v>4</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
         <v>3.95</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
         <v>2.44</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L11" t="n">
         <v>1.57</v>
@@ -2545,10 +2545,10 @@
         <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
         <v>1.37</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
         <v>2.26</v>
@@ -2715,22 +2715,22 @@
         <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M12" t="n">
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
         <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="R12" t="n">
         <v>1.61</v>
@@ -2742,25 +2742,25 @@
         <v>1.54</v>
       </c>
       <c r="U12" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
         <v>26</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB12" t="n">
         <v>970</v>
@@ -2772,13 +2772,13 @@
         <v>11.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
         <v>16.5</v>
@@ -2793,28 +2793,28 @@
         <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
         <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>13</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT12" t="n">
         <v>15.5</v>
@@ -2823,13 +2823,13 @@
         <v>8.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY12" t="n">
         <v>12</v>
@@ -2841,16 +2841,16 @@
         <v>24</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC12" t="n">
         <v>25</v>
       </c>
       <c r="BD12" t="n">
-        <v>28</v>
+        <v>9.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF12" t="n">
         <v>15</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
@@ -2909,7 +2909,7 @@
         <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
@@ -2918,19 +2918,19 @@
         <v>5.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T13" t="n">
         <v>1.59</v>
@@ -2945,7 +2945,7 @@
         <v>2.18</v>
       </c>
       <c r="X13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y13" t="n">
         <v>25</v>
@@ -3020,13 +3020,13 @@
         <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
         <v>12.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
         <v>13.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>9.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="I14" t="n">
         <v>1.52</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I15" t="n">
         <v>1.86</v>
@@ -3360,7 +3360,7 @@
         <v>42</v>
       </c>
       <c r="AG15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
         <v>19</v>
@@ -3411,7 +3411,7 @@
         <v>14.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY15" t="n">
         <v>16.5</v>
@@ -3426,23 +3426,23 @@
         <v>8</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG15" t="n">
         <v>7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H16" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I16" t="n">
         <v>2.28</v>
@@ -3509,22 +3509,22 @@
         <v>1.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S16" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
         <v>1.5</v>
       </c>
       <c r="U16" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="V16" t="n">
         <v>1.78</v>
       </c>
       <c r="W16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
         <v>27</v>
@@ -3554,7 +3554,7 @@
         <v>27</v>
       </c>
       <c r="AG16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
         <v>15</v>
@@ -3581,7 +3581,7 @@
         <v>11</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>8.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>14.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>3.25</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H17" t="n">
         <v>2.38</v>
@@ -3682,7 +3682,7 @@
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.36</v>
@@ -3694,22 +3694,22 @@
         <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R17" t="n">
         <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U17" t="n">
         <v>2.18</v>
@@ -3727,7 +3727,7 @@
         <v>10.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
         <v>55</v>
@@ -3787,7 +3787,7 @@
         <v>20</v>
       </c>
       <c r="AT17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU17" t="n">
         <v>7.2</v>
@@ -3805,7 +3805,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
         <v>24</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>2.64</v>
       </c>
       <c r="I18" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
@@ -3885,13 +3885,13 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O18" t="n">
         <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q18" t="n">
         <v>2.12</v>
@@ -3906,7 +3906,7 @@
         <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
         <v>1.57</v>
@@ -3951,10 +3951,10 @@
         <v>44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AL18" t="n">
         <v>50</v>
@@ -3963,10 +3963,10 @@
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AO18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AX18" t="n">
         <v>16.5</v>
@@ -4002,13 +4002,13 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB18" t="n">
         <v>40</v>
       </c>
       <c r="BC18" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BD18" t="n">
         <v>27</v>
@@ -4020,11 +4020,11 @@
         <v>22</v>
       </c>
       <c r="BG18" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
         <v>3.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
         <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -4094,22 +4094,22 @@
         <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
         <v>1.68</v>
       </c>
       <c r="U19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V19" t="n">
         <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="n">
         <v>15</v>
@@ -4133,7 +4133,7 @@
         <v>36</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
@@ -4160,10 +4160,10 @@
         <v>15.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>13</v>
@@ -4175,7 +4175,7 @@
         <v>29</v>
       </c>
       <c r="AT19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
         <v>7.6</v>
@@ -4193,7 +4193,7 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>36</v>
@@ -4214,11 +4214,11 @@
         <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G20" t="n">
         <v>3.25</v>
@@ -4267,22 +4267,22 @@
         <v>3.45</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P20" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
@@ -4291,28 +4291,28 @@
         <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
         <v>9.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA20" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB20" t="n">
         <v>10.5</v>
@@ -4321,7 +4321,7 @@
         <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
         <v>55</v>
@@ -4330,10 +4330,10 @@
         <v>27</v>
       </c>
       <c r="AG20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
         <v>60</v>
@@ -4360,19 +4360,19 @@
         <v>10.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR20" t="n">
         <v>13.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
         <v>11</v>
@@ -4390,10 +4390,10 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB20" t="n">
         <v>38</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>29</v>
       </c>
       <c r="BC20" t="n">
         <v>24</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I21" t="n">
         <v>1.98</v>
@@ -4488,13 +4488,13 @@
         <v>1.52</v>
       </c>
       <c r="U21" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V21" t="n">
         <v>2.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X21" t="n">
         <v>30</v>
@@ -4536,16 +4536,16 @@
         <v>85</v>
       </c>
       <c r="AK21" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM21" t="n">
         <v>60</v>
       </c>
       <c r="AN21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO21" t="n">
         <v>8.6</v>
@@ -4587,7 +4587,7 @@
         <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC21" t="n">
         <v>30</v>
@@ -4596,7 +4596,7 @@
         <v>30</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF21" t="n">
         <v>19.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4637,67 +4637,67 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="G22" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="K22" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="S22" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="T22" t="n">
         <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W22" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="X22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
@@ -4706,13 +4706,13 @@
         <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
         <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF22" t="n">
         <v>13</v>
@@ -4727,7 +4727,7 @@
         <v>55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
@@ -4739,10 +4739,10 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP22" t="n">
         <v>18.5</v>
@@ -4751,56 +4751,56 @@
         <v>16.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV22" t="n">
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AX22" t="n">
         <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
         <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB22" t="n">
         <v>15.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD22" t="n">
         <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G23" t="n">
         <v>2.6</v>
       </c>
-      <c r="G23" t="n">
-        <v>2.62</v>
-      </c>
       <c r="H23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J23" t="n">
         <v>3.3</v>
@@ -4849,7 +4849,7 @@
         <v>3.35</v>
       </c>
       <c r="L23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
@@ -4861,7 +4861,7 @@
         <v>1.41</v>
       </c>
       <c r="P23" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
         <v>2.22</v>
@@ -4879,19 +4879,19 @@
         <v>2.06</v>
       </c>
       <c r="V23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
         <v>55</v>
@@ -4921,7 +4921,7 @@
         <v>55</v>
       </c>
       <c r="AJ23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK23" t="n">
         <v>30</v>
@@ -4933,7 +4933,7 @@
         <v>120</v>
       </c>
       <c r="AN23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO23" t="n">
         <v>44</v>
@@ -4945,13 +4945,13 @@
         <v>10</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU23" t="n">
         <v>6.8</v>
@@ -4969,10 +4969,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB23" t="n">
         <v>32</v>
@@ -4981,7 +4981,7 @@
         <v>27</v>
       </c>
       <c r="BD23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE23" t="n">
         <v>44</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>4.7</v>
       </c>
       <c r="G24" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H24" t="n">
         <v>1.81</v>
@@ -5049,7 +5049,7 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.38</v>
@@ -5067,16 +5067,16 @@
         <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U24" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V24" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
         <v>14</v>
@@ -5139,7 +5139,7 @@
         <v>6.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS24" t="n">
         <v>6</v>
@@ -5175,7 +5175,7 @@
         <v>4.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BE24" t="n">
         <v>3</v>
@@ -5184,11 +5184,11 @@
         <v>4.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G25" t="n">
         <v>4.1</v>
@@ -5228,7 +5228,7 @@
         <v>2.22</v>
       </c>
       <c r="I25" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J25" t="n">
         <v>2.98</v>
@@ -5267,7 +5267,7 @@
         <v>1.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W25" t="n">
         <v>1.32</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
         <v>1.84</v>
       </c>
       <c r="U26" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V26" t="n">
         <v>1.2</v>
@@ -5482,7 +5482,7 @@
         <v>9</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AD26" t="n">
         <v>21</v>
@@ -5494,7 +5494,7 @@
         <v>11.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
         <v>21</v>
@@ -5527,10 +5527,10 @@
         <v>15.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
@@ -5542,7 +5542,7 @@
         <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX26" t="n">
         <v>9.199999999999999</v>
@@ -5554,7 +5554,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB26" t="n">
         <v>15.5</v>
@@ -5563,20 +5563,20 @@
         <v>15</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BF26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5610,79 +5610,79 @@
         <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="I27" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q27" t="n">
-        <v>1.95</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="V27" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X27" t="n">
         <v>18</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AA27" t="n">
         <v>16</v>
       </c>
       <c r="AB27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC27" t="n">
         <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AF27" t="n">
         <v>50</v>
@@ -5691,86 +5691,86 @@
         <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ27" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AK27" t="n">
         <v>90</v>
       </c>
       <c r="AL27" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM27" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO27" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AP27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AS27" t="n">
         <v>14.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>17.5</v>
+        <v>7.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV27" t="n">
         <v>9.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY27" t="n">
         <v>20</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA27" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB27" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BE27" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5828,22 +5828,22 @@
         <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P28" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R28" t="n">
         <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -5903,7 +5903,7 @@
         <v>130</v>
       </c>
       <c r="AN28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO28" t="n">
         <v>65</v>
@@ -5939,7 +5939,7 @@
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA28" t="n">
         <v>55</v>
@@ -5948,23 +5948,23 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD28" t="n">
         <v>40</v>
       </c>
       <c r="BE28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF28" t="n">
         <v>18.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5995,25 +5995,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H29" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J29" t="n">
         <v>2.76</v>
       </c>
       <c r="K29" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
         <v>1.16</v>
@@ -6109,7 +6109,7 @@
         <v>6.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS29" t="n">
         <v>9.4</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>3.35</v>
       </c>
       <c r="H30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I30" t="n">
         <v>2.84</v>
@@ -6234,7 +6234,7 @@
         <v>1.96</v>
       </c>
       <c r="U30" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V30" t="n">
         <v>1.54</v>
@@ -6270,7 +6270,7 @@
         <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
         <v>1000</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
         <v>1.19</v>
       </c>
       <c r="P31" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
         <v>1.59</v>
@@ -6422,10 +6422,10 @@
         <v>1.64</v>
       </c>
       <c r="S31" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T31" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U31" t="n">
         <v>2.38</v>
@@ -6476,7 +6476,7 @@
         <v>120</v>
       </c>
       <c r="AK31" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL31" t="n">
         <v>55</v>
@@ -6491,7 +6491,7 @@
         <v>7.4</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ31" t="n">
         <v>10.5</v>
@@ -6500,13 +6500,13 @@
         <v>10.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT31" t="n">
         <v>19.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
@@ -6530,23 +6530,23 @@
         <v>9.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD31" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BE31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BG31" t="n">
         <v>6.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
         <v>8.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW32" t="n">
         <v>4.6</v>
@@ -6724,7 +6724,7 @@
         <v>16</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BD32" t="n">
         <v>21</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G33" t="n">
         <v>1.55</v>
@@ -6837,10 +6837,10 @@
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC33" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AD33" t="n">
         <v>32</v>
@@ -6885,7 +6885,7 @@
         <v>4.2</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS33" t="n">
         <v>4.4</v>
@@ -6894,13 +6894,13 @@
         <v>16.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AV33" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX33" t="n">
         <v>13.5</v>
@@ -6921,7 +6921,7 @@
         <v>12</v>
       </c>
       <c r="BD33" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BE33" t="n">
         <v>4.2</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="G34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H34" t="n">
         <v>13</v>
@@ -6980,7 +6980,7 @@
         <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L34" t="n">
         <v>1.13</v>
@@ -7001,31 +7001,31 @@
         <v>1.23</v>
       </c>
       <c r="R34" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="S34" t="n">
         <v>1.6</v>
       </c>
       <c r="T34" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U34" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W34" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="X34" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
         <v>110</v>
       </c>
       <c r="Z34" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AA34" t="n">
         <v>450</v>
@@ -7040,7 +7040,7 @@
         <v>55</v>
       </c>
       <c r="AE34" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF34" t="n">
         <v>15</v>
@@ -7061,28 +7061,28 @@
         <v>13</v>
       </c>
       <c r="AL34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ34" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
         <v>14</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AS34" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>15</v>
       </c>
       <c r="AT34" t="n">
         <v>19.5</v>
@@ -7091,10 +7091,10 @@
         <v>20</v>
       </c>
       <c r="AV34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW34" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX34" t="n">
         <v>12.5</v>
@@ -7103,10 +7103,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="BA34" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BB34" t="n">
         <v>11.5</v>
@@ -7118,17 +7118,17 @@
         <v>20</v>
       </c>
       <c r="BE34" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BG34" t="n">
         <v>60</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
         <v>1.16</v>
       </c>
       <c r="I35" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="J35" t="n">
         <v>4.1</v>
@@ -7195,7 +7195,7 @@
         <v>1.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G36" t="n">
         <v>970</v>
@@ -7365,7 +7365,7 @@
         <v>970</v>
       </c>
       <c r="J36" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K36" t="n">
         <v>4.7</v>
@@ -7401,10 +7401,10 @@
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H37" t="n">
         <v>2.22</v>
@@ -7589,16 +7589,16 @@
         <v>3.65</v>
       </c>
       <c r="T37" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U37" t="n">
         <v>2.16</v>
       </c>
       <c r="V37" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W37" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X37" t="n">
         <v>13.5</v>
@@ -7610,7 +7610,7 @@
         <v>13.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB37" t="n">
         <v>14</v>
@@ -7649,7 +7649,7 @@
         <v>95</v>
       </c>
       <c r="AN37" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO37" t="n">
         <v>17.5</v>
@@ -7688,7 +7688,7 @@
         <v>15.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB37" t="n">
         <v>60</v>
@@ -7700,7 +7700,7 @@
         <v>46</v>
       </c>
       <c r="BE37" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="BF37" t="n">
         <v>40</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
         <v>3.15</v>
       </c>
       <c r="L38" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M38" t="n">
         <v>1.12</v>
@@ -7780,16 +7780,16 @@
         <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T38" t="n">
         <v>2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V38" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W38" t="n">
         <v>1.38</v>
@@ -7804,10 +7804,10 @@
         <v>14</v>
       </c>
       <c r="AA38" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AB38" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC38" t="n">
         <v>7</v>
@@ -7816,7 +7816,7 @@
         <v>13</v>
       </c>
       <c r="AE38" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AF38" t="n">
         <v>23</v>
@@ -7825,7 +7825,7 @@
         <v>15.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI38" t="n">
         <v>65</v>
@@ -7840,13 +7840,13 @@
         <v>75</v>
       </c>
       <c r="AM38" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN38" t="n">
         <v>75</v>
       </c>
       <c r="AO38" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AP38" t="n">
         <v>8</v>
@@ -7864,7 +7864,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV38" t="n">
         <v>11.5</v>
@@ -7882,13 +7882,13 @@
         <v>19.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BB38" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BC38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD38" t="n">
         <v>36</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -7938,34 +7938,34 @@
         <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H39" t="n">
         <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K39" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L39" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M39" t="n">
         <v>1.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O39" t="n">
         <v>1.46</v>
       </c>
       <c r="P39" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q39" t="n">
         <v>2.36</v>
@@ -7992,7 +7992,7 @@
         <v>12.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z39" t="n">
         <v>36</v>
@@ -8001,7 +8001,7 @@
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC39" t="n">
         <v>9</v>
@@ -8025,7 +8025,7 @@
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK39" t="n">
         <v>34</v>
@@ -8037,7 +8037,7 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
@@ -8052,7 +8052,7 @@
         <v>21</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT39" t="n">
         <v>6.4</v>
@@ -8064,7 +8064,7 @@
         <v>15</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX39" t="n">
         <v>10.5</v>
@@ -8076,7 +8076,7 @@
         <v>18.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB39" t="n">
         <v>20</v>
@@ -8088,17 +8088,17 @@
         <v>4.4</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF39" t="n">
         <v>20</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>1.75</v>
       </c>
       <c r="G41" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H41" t="n">
         <v>5</v>
@@ -8353,7 +8353,7 @@
         <v>1.32</v>
       </c>
       <c r="P41" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q41" t="n">
         <v>1.95</v>
@@ -8383,7 +8383,7 @@
         <v>21</v>
       </c>
       <c r="Z41" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA41" t="n">
         <v>1000</v>
@@ -8398,7 +8398,7 @@
         <v>24</v>
       </c>
       <c r="AE41" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF41" t="n">
         <v>12.5</v>
@@ -8416,7 +8416,7 @@
         <v>22</v>
       </c>
       <c r="AK41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL41" t="n">
         <v>44</v>
@@ -8437,28 +8437,28 @@
         <v>13.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT41" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU41" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV41" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW41" t="n">
         <v>4.7</v>
       </c>
       <c r="AX41" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AY41" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ41" t="n">
         <v>15.5</v>
@@ -8467,7 +8467,7 @@
         <v>4.7</v>
       </c>
       <c r="BB41" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC41" t="n">
         <v>14.5</v>
@@ -8479,14 +8479,14 @@
         <v>4.8</v>
       </c>
       <c r="BF41" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG41" t="n">
         <v>4.8</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -8526,10 +8526,10 @@
         <v>5.1</v>
       </c>
       <c r="I42" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K42" t="n">
         <v>4.1</v>
@@ -8538,31 +8538,31 @@
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>3.15</v>
+        <v>1.66</v>
       </c>
       <c r="O42" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P42" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S42" t="n">
-        <v>3.9</v>
+        <v>1.91</v>
       </c>
       <c r="T42" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="U42" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V42" t="n">
         <v>1.2</v>
@@ -8571,10 +8571,10 @@
         <v>2.18</v>
       </c>
       <c r="X42" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z42" t="n">
         <v>1000</v>
@@ -8583,10 +8583,10 @@
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
         <v>1000</v>
@@ -8595,10 +8595,10 @@
         <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
         <v>1000</v>
@@ -8625,62 +8625,62 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>3.7</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.8</v>
+        <v>1.24</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.2</v>
+        <v>1.33</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.15</v>
+        <v>1.33</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.3</v>
+        <v>1.33</v>
       </c>
       <c r="AV42" t="n">
-        <v>3.9</v>
+        <v>1.26</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="AX42" t="n">
-        <v>3.45</v>
+        <v>1.33</v>
       </c>
       <c r="AY42" t="n">
-        <v>3.5</v>
+        <v>1.33</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.9</v>
+        <v>1.26</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="BB42" t="n">
-        <v>3.8</v>
+        <v>1.25</v>
       </c>
       <c r="BC42" t="n">
-        <v>3.85</v>
+        <v>1.26</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.1</v>
+        <v>1.29</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.4</v>
+        <v>1.33</v>
       </c>
       <c r="BF42" t="n">
-        <v>10</v>
+        <v>1.24</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.4</v>
+        <v>1.18</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G43" t="n">
         <v>1.9</v>
@@ -8720,7 +8720,7 @@
         <v>4.6</v>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>3.7</v>
@@ -8729,16 +8729,16 @@
         <v>3.85</v>
       </c>
       <c r="L43" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O43" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P43" t="n">
         <v>1.81</v>
@@ -8750,7 +8750,7 @@
         <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T43" t="n">
         <v>1.95</v>
@@ -8762,7 +8762,7 @@
         <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X43" t="n">
         <v>12.5</v>
@@ -8777,7 +8777,7 @@
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC43" t="n">
         <v>1000</v>
@@ -8825,10 +8825,10 @@
         <v>14</v>
       </c>
       <c r="AR43" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT43" t="n">
         <v>7.4</v>
@@ -8837,31 +8837,31 @@
         <v>7.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>17</v>
+        <v>7.8</v>
       </c>
       <c r="AW43" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX43" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AY43" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB43" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BA43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>8</v>
-      </c>
       <c r="BC43" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BD43" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE43" t="n">
         <v>4.9</v>
@@ -8870,11 +8870,11 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG43" t="n">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>
@@ -8929,13 +8929,13 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O44" t="n">
         <v>1.29</v>
       </c>
       <c r="P44" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q44" t="n">
         <v>1.29</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-22 19:53:12</t>
+          <t>2026-04-22 22:10:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N2" t="n">
         <v>3.1</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.1</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.89</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.76</v>
-      </c>
       <c r="U2" t="n">
-        <v>2.28</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>990</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.5</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>15</v>
+        <v>1.34</v>
       </c>
       <c r="AS2" t="n">
-        <v>29</v>
+        <v>1.34</v>
       </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>1.34</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>1.34</v>
       </c>
       <c r="AW2" t="n">
-        <v>23</v>
+        <v>1.34</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>1.34</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>1.34</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>1.34</v>
       </c>
       <c r="BA2" t="n">
-        <v>28</v>
+        <v>1.34</v>
       </c>
       <c r="BB2" t="n">
-        <v>29</v>
+        <v>1.34</v>
       </c>
       <c r="BC2" t="n">
-        <v>29</v>
+        <v>1.34</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>1.34</v>
       </c>
       <c r="BE2" t="n">
-        <v>48</v>
+        <v>1.34</v>
       </c>
       <c r="BF2" t="n">
-        <v>23</v>
+        <v>1.34</v>
       </c>
       <c r="BG2" t="n">
-        <v>17.5</v>
+        <v>1.34</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G3" t="n">
         <v>6.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.2</v>
       </c>
-      <c r="P3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.19</v>
-      </c>
       <c r="X3" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
         <v>10</v>
       </c>
       <c r="AE3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
         <v>55</v>
       </c>
       <c r="AG3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS3" t="n">
         <v>14</v>
       </c>
       <c r="AT3" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AY3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="BC3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BD3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BE3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BF3" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
         <v>3.35</v>
@@ -1157,13 +1157,13 @@
         <v>3.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1178,7 +1178,7 @@
         <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
@@ -1196,7 +1196,7 @@
         <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1256,59 +1256,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AU4" t="n">
         <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AW4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC4" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BD4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF4" t="n">
         <v>6</v>
       </c>
-      <c r="BC4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -1351,40 +1351,40 @@
         <v>1.29</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R5" t="n">
         <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
         <v>4.4</v>
@@ -1393,7 +1393,7 @@
         <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
         <v>8.4</v>
@@ -1402,16 +1402,16 @@
         <v>7.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AB5" t="n">
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1444,28 +1444,28 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT5" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>26</v>
       </c>
       <c r="AU5" t="n">
         <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW5" t="n">
         <v>6</v>
@@ -1477,13 +1477,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>25</v>
+        <v>7.6</v>
       </c>
       <c r="BA5" t="n">
         <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC5" t="n">
         <v>9.199999999999999</v>
@@ -1498,11 +1498,11 @@
         <v>9.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="I6" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.13</v>
@@ -1563,28 +1563,28 @@
         <v>1.07</v>
       </c>
       <c r="P6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R6" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="S6" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="U6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
         <v>90</v>
@@ -1593,19 +1593,19 @@
         <v>34</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
         <v>27</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
         <v>18.5</v>
@@ -1617,7 +1617,7 @@
         <v>30</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
         <v>20</v>
@@ -1638,65 +1638,65 @@
         <v>17.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>19.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>5.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>15</v>
+        <v>5.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AW6" t="n">
         <v>13.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD6" t="n">
         <v>20</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BE6" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="BF6" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1760,13 +1760,13 @@
         <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
         <v>1.87</v>
@@ -1784,19 +1784,19 @@
         <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
         <v>22</v>
@@ -1805,13 +1805,13 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1841,10 +1841,10 @@
         <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AT7" t="n">
         <v>7.4</v>
@@ -1853,44 +1853,44 @@
         <v>7.4</v>
       </c>
       <c r="AV7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY7" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
@@ -1960,7 +1960,7 @@
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T8" t="n">
         <v>2.08</v>
@@ -1972,7 +1972,7 @@
         <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X8" t="n">
         <v>11</v>
@@ -1990,7 +1990,7 @@
         <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,10 +1999,10 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
         <v>30</v>
@@ -2023,68 +2023,68 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AR8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
         <v>6</v>
       </c>
-      <c r="AS8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>14</v>
-      </c>
       <c r="AW8" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AZ8" t="n">
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -2115,61 +2115,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="G9" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>17.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.29</v>
+        <v>1.94</v>
       </c>
       <c r="R9" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,10 +2193,10 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2205,10 +2205,10 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -2309,70 +2309,70 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.39</v>
+        <v>3.25</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
         <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>1.35</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB10" t="n">
         <v>15</v>
@@ -2381,10 +2381,10 @@
         <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
         <v>27</v>
@@ -2414,65 +2414,65 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="G11" t="n">
         <v>3.45</v>
@@ -2515,7 +2515,7 @@
         <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="K11" t="n">
         <v>2.88</v>
@@ -2533,7 +2533,7 @@
         <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
         <v>3.15</v>
@@ -2545,10 +2545,10 @@
         <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
         <v>1.37</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>3.25</v>
@@ -2706,7 +2706,7 @@
         <v>2.26</v>
       </c>
       <c r="I12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -2724,13 +2724,13 @@
         <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
         <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R12" t="n">
         <v>1.61</v>
@@ -2742,10 +2742,10 @@
         <v>1.54</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V12" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W12" t="n">
         <v>1.44</v>
@@ -2781,7 +2781,7 @@
         <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI12" t="n">
         <v>28</v>
@@ -2790,28 +2790,28 @@
         <v>55</v>
       </c>
       <c r="AK12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
         <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>13</v>
       </c>
       <c r="AP12" t="n">
-        <v>19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
         <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="AS12" t="n">
         <v>28</v>
@@ -2823,10 +2823,10 @@
         <v>8.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AX12" t="n">
         <v>22</v>
@@ -2841,26 +2841,26 @@
         <v>24</v>
       </c>
       <c r="BB12" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="BC12" t="n">
         <v>25</v>
       </c>
       <c r="BD12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE12" t="n">
         <v>10.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
         <v>10.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -2915,10 +2915,10 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P13" t="n">
         <v>2.52</v>
@@ -2930,10 +2930,10 @@
         <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
         <v>2.52</v>
@@ -2945,7 +2945,7 @@
         <v>2.18</v>
       </c>
       <c r="X13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y13" t="n">
         <v>25</v>
@@ -2954,13 +2954,13 @@
         <v>42</v>
       </c>
       <c r="AA13" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="n">
         <v>14</v>
       </c>
       <c r="AC13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
         <v>18.5</v>
@@ -2969,7 +2969,7 @@
         <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
@@ -2978,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ13" t="n">
         <v>21</v>
@@ -2999,16 +2999,16 @@
         <v>38</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT13" t="n">
         <v>11.5</v>
@@ -3020,10 +3020,10 @@
         <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
         <v>9.199999999999999</v>
@@ -3032,7 +3032,7 @@
         <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB13" t="n">
         <v>17.5</v>
@@ -3044,17 +3044,17 @@
         <v>22</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>27</v>
+        <v>8.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         <v>1.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
         <v>2.44</v>
@@ -3396,10 +3396,10 @@
         <v>10</v>
       </c>
       <c r="AS15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU15" t="n">
         <v>8.199999999999999</v>
@@ -3426,23 +3426,23 @@
         <v>8</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE15" t="n">
         <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BG15" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>2.22</v>
       </c>
       <c r="I16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>4.1</v>
@@ -3503,7 +3503,7 @@
         <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q16" t="n">
         <v>1.54</v>
@@ -3515,13 +3515,13 @@
         <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U16" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W16" t="n">
         <v>1.44</v>
@@ -3533,7 +3533,7 @@
         <v>19.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA16" t="n">
         <v>32</v>
@@ -3545,7 +3545,7 @@
         <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
         <v>21</v>
@@ -3554,7 +3554,7 @@
         <v>27</v>
       </c>
       <c r="AG16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH16" t="n">
         <v>15</v>
@@ -3566,7 +3566,7 @@
         <v>50</v>
       </c>
       <c r="AK16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL16" t="n">
         <v>32</v>
@@ -3581,7 +3581,7 @@
         <v>11</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
         <v>14.5</v>
@@ -3608,7 +3608,7 @@
         <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>13</v>
@@ -3617,7 +3617,7 @@
         <v>22</v>
       </c>
       <c r="BB16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC16" t="n">
         <v>25</v>
@@ -3626,17 +3626,17 @@
         <v>27</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BG16" t="n">
         <v>9.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -3694,19 +3694,19 @@
         <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
         <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
         <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
         <v>1.77</v>
@@ -3754,7 +3754,7 @@
         <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ17" t="n">
         <v>70</v>
@@ -3763,7 +3763,7 @@
         <v>44</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I18" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,7 +3885,7 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.37</v>
@@ -3897,10 +3897,10 @@
         <v>2.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
         <v>1.84</v>
@@ -3909,7 +3909,7 @@
         <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W18" t="n">
         <v>1.5</v>
@@ -3930,7 +3930,7 @@
         <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
         <v>12.5</v>
@@ -3939,7 +3939,7 @@
         <v>34</v>
       </c>
       <c r="AF18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG18" t="n">
         <v>13.5</v>
@@ -3948,10 +3948,10 @@
         <v>18.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK18" t="n">
         <v>38</v>
@@ -3966,7 +3966,7 @@
         <v>36</v>
       </c>
       <c r="AO18" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
@@ -3975,10 +3975,10 @@
         <v>9.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H19" t="n">
         <v>3.3</v>
@@ -4073,7 +4073,7 @@
         <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -4145,7 +4145,7 @@
         <v>42</v>
       </c>
       <c r="AJ19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK19" t="n">
         <v>23</v>
@@ -4175,7 +4175,7 @@
         <v>29</v>
       </c>
       <c r="AT19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
         <v>7.6</v>
@@ -4202,7 +4202,7 @@
         <v>24</v>
       </c>
       <c r="BC19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>29</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -4252,10 +4252,10 @@
         <v>3.05</v>
       </c>
       <c r="G20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H20" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I20" t="n">
         <v>2.62</v>
@@ -4276,13 +4276,13 @@
         <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P20" t="n">
         <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
@@ -4297,7 +4297,7 @@
         <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W20" t="n">
         <v>1.45</v>
@@ -4336,10 +4336,10 @@
         <v>27</v>
       </c>
       <c r="AI20" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK20" t="n">
         <v>100</v>
@@ -4354,7 +4354,7 @@
         <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP20" t="n">
         <v>10.5</v>
@@ -4372,7 +4372,7 @@
         <v>9.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
         <v>11</v>
@@ -4381,7 +4381,7 @@
         <v>20</v>
       </c>
       <c r="AX20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY20" t="n">
         <v>12</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G21" t="n">
         <v>4.1</v>
@@ -4452,7 +4452,7 @@
         <v>1.92</v>
       </c>
       <c r="I21" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J21" t="n">
         <v>4.3</v>
@@ -4464,7 +4464,7 @@
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
         <v>5.9</v>
@@ -4578,7 +4578,7 @@
         <v>28</v>
       </c>
       <c r="AY21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ21" t="n">
         <v>13.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H22" t="n">
         <v>4.3</v>
@@ -4679,10 +4679,10 @@
         <v>2.52</v>
       </c>
       <c r="T22" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U22" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V22" t="n">
         <v>1.26</v>
@@ -4697,7 +4697,7 @@
         <v>24</v>
       </c>
       <c r="Z22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
@@ -4712,10 +4712,10 @@
         <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
@@ -4742,19 +4742,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT22" t="n">
         <v>9.800000000000001</v>
@@ -4781,16 +4781,16 @@
         <v>8</v>
       </c>
       <c r="BB22" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC22" t="n">
         <v>15.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
         <v>7.8</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -4855,28 +4855,28 @@
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>1.41</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V23" t="n">
         <v>1.44</v>
@@ -4891,13 +4891,13 @@
         <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
         <v>55</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC23" t="n">
         <v>7</v>
@@ -4906,7 +4906,7 @@
         <v>13.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
         <v>15.5</v>
@@ -4933,7 +4933,7 @@
         <v>120</v>
       </c>
       <c r="AN23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO23" t="n">
         <v>44</v>
@@ -4951,7 +4951,7 @@
         <v>50</v>
       </c>
       <c r="AT23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU23" t="n">
         <v>6.8</v>
@@ -4978,13 +4978,13 @@
         <v>32</v>
       </c>
       <c r="BC23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD23" t="n">
         <v>42</v>
       </c>
       <c r="BE23" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BF23" t="n">
         <v>25</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G24" t="n">
         <v>5.5</v>
@@ -5037,7 +5037,7 @@
         <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
         <v>3.95</v>
@@ -5151,7 +5151,7 @@
         <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW24" t="n">
         <v>5.8</v>
@@ -5178,17 +5178,17 @@
         <v>7</v>
       </c>
       <c r="BE24" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="BF24" t="n">
         <v>4.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G25" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I25" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J25" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K25" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5267,10 +5267,10 @@
         <v>1.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X25" t="n">
         <v>13.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="G26" t="n">
         <v>1.8</v>
@@ -5422,7 +5422,7 @@
         <v>5.2</v>
       </c>
       <c r="I26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
         <v>3.95</v>
@@ -5443,7 +5443,7 @@
         <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
         <v>1.86</v>
@@ -5473,25 +5473,25 @@
         <v>19</v>
       </c>
       <c r="Z26" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA26" t="n">
         <v>160</v>
       </c>
       <c r="AB26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD26" t="n">
         <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="n">
         <v>12</v>
@@ -5500,16 +5500,16 @@
         <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM26" t="n">
         <v>130</v>
@@ -5527,10 +5527,10 @@
         <v>15.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS26" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
@@ -5542,7 +5542,7 @@
         <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX26" t="n">
         <v>9.199999999999999</v>
@@ -5554,29 +5554,29 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB26" t="n">
         <v>15.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -5610,13 +5610,13 @@
         <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="I27" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="J27" t="n">
         <v>4.2</v>
@@ -5637,49 +5637,49 @@
         <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
         <v>2.02</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
         <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U27" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="V27" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="W27" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y27" t="n">
         <v>7.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA27" t="n">
         <v>16</v>
       </c>
       <c r="AB27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AC27" t="n">
         <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE27" t="n">
         <v>18.5</v>
@@ -5697,19 +5697,19 @@
         <v>40</v>
       </c>
       <c r="AJ27" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AK27" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AL27" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM27" t="n">
         <v>150</v>
       </c>
       <c r="AN27" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AO27" t="n">
         <v>11</v>
@@ -5724,13 +5724,13 @@
         <v>8.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV27" t="n">
         <v>9.4</v>
@@ -5739,38 +5739,38 @@
         <v>16.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA27" t="n">
         <v>34</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
         <v>3.35</v>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
@@ -5834,7 +5834,7 @@
         <v>1.78</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R28" t="n">
         <v>1.29</v>
@@ -5867,7 +5867,7 @@
         <v>85</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
         <v>7.2</v>
@@ -5900,10 +5900,10 @@
         <v>44</v>
       </c>
       <c r="AM28" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO28" t="n">
         <v>65</v>
@@ -5918,7 +5918,7 @@
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT28" t="n">
         <v>7.8</v>
@@ -5942,7 +5942,7 @@
         <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB28" t="n">
         <v>23</v>
@@ -5957,14 +5957,14 @@
         <v>42</v>
       </c>
       <c r="BF28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -6010,10 +6010,10 @@
         <v>2.76</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
         <v>1.16</v>
@@ -6022,10 +6022,10 @@
         <v>2.32</v>
       </c>
       <c r="O29" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="P29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q29" t="n">
         <v>3</v>
@@ -6037,10 +6037,10 @@
         <v>6.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U29" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V29" t="n">
         <v>1.47</v>
@@ -6049,13 +6049,13 @@
         <v>1.43</v>
       </c>
       <c r="X29" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
       <c r="Z29" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="n">
         <v>60</v>
@@ -6097,7 +6097,7 @@
         <v>280</v>
       </c>
       <c r="AN29" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO29" t="n">
         <v>75</v>
@@ -6109,10 +6109,10 @@
         <v>6.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AT29" t="n">
         <v>7</v>
@@ -6121,44 +6121,44 @@
         <v>6</v>
       </c>
       <c r="AV29" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY29" t="n">
         <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE29" t="n">
         <v>10</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BF29" t="n">
         <v>9.4</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BG29" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BD29" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
         <v>2.84</v>
       </c>
       <c r="J30" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
         <v>3.25</v>
@@ -6225,7 +6225,7 @@
         <v>2.56</v>
       </c>
       <c r="R30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S30" t="n">
         <v>4.5</v>
@@ -6234,7 +6234,7 @@
         <v>1.96</v>
       </c>
       <c r="U30" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V30" t="n">
         <v>1.54</v>
@@ -6264,7 +6264,7 @@
         <v>13.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF30" t="n">
         <v>1000</v>
@@ -6294,7 +6294,7 @@
         <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP30" t="n">
         <v>8.6</v>
@@ -6309,7 +6309,7 @@
         <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU30" t="n">
         <v>6.2</v>
@@ -6330,29 +6330,29 @@
         <v>6.6</v>
       </c>
       <c r="BA30" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB30" t="n">
         <v>7.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD30" t="n">
         <v>7.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG30" t="n">
         <v>24</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>5.6</v>
@@ -6392,13 +6392,13 @@
         <v>1.69</v>
       </c>
       <c r="I31" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="J31" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K31" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6407,31 +6407,31 @@
         <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
         <v>1.19</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S31" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U31" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V31" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="W31" t="n">
         <v>1.22</v>
@@ -6470,19 +6470,19 @@
         <v>18</v>
       </c>
       <c r="AI31" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AJ31" t="n">
         <v>120</v>
       </c>
       <c r="AK31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL31" t="n">
         <v>55</v>
       </c>
       <c r="AM31" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN31" t="n">
         <v>60</v>
@@ -6491,7 +6491,7 @@
         <v>7.4</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ31" t="n">
         <v>10.5</v>
@@ -6500,13 +6500,13 @@
         <v>10.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT31" t="n">
         <v>19.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
@@ -6521,22 +6521,22 @@
         <v>17.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF31" t="n">
         <v>38</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6685,7 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="AQ32" t="n">
         <v>15.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -6837,16 +6837,16 @@
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC33" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AD33" t="n">
         <v>32</v>
       </c>
       <c r="AE33" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
         <v>19.5</v>
@@ -6858,40 +6858,40 @@
         <v>22</v>
       </c>
       <c r="AI33" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK33" t="n">
         <v>17.5</v>
       </c>
       <c r="AL33" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AM33" t="n">
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AO33" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT33" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU33" t="n">
         <v>13</v>
@@ -6900,7 +6900,7 @@
         <v>21</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX33" t="n">
         <v>13.5</v>
@@ -6912,7 +6912,7 @@
         <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB33" t="n">
         <v>14.5</v>
@@ -6924,17 +6924,17 @@
         <v>18</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>1.24</v>
       </c>
       <c r="H34" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I34" t="n">
         <v>15.5</v>
@@ -6980,7 +6980,7 @@
         <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="L34" t="n">
         <v>1.13</v>
@@ -7001,7 +7001,7 @@
         <v>1.23</v>
       </c>
       <c r="R34" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="S34" t="n">
         <v>1.6</v>
@@ -7010,7 +7010,7 @@
         <v>1.63</v>
       </c>
       <c r="U34" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V34" t="n">
         <v>1.07</v>
@@ -7019,22 +7019,22 @@
         <v>5.1</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y34" t="n">
         <v>110</v>
       </c>
       <c r="Z34" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AA34" t="n">
         <v>450</v>
       </c>
       <c r="AB34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD34" t="n">
         <v>55</v>
@@ -7043,7 +7043,7 @@
         <v>150</v>
       </c>
       <c r="AF34" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG34" t="n">
         <v>13</v>
@@ -7067,43 +7067,43 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ34" t="n">
         <v>13.5</v>
       </c>
       <c r="AR34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW34" t="n">
         <v>14</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>13.5</v>
       </c>
       <c r="AX34" t="n">
         <v>12.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ34" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BA34" t="n">
         <v>13.5</v>
@@ -7118,17 +7118,17 @@
         <v>20</v>
       </c>
       <c r="BE34" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BG34" t="n">
         <v>60</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="G35" t="n">
         <v>2.14</v>
       </c>
       <c r="H35" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I35" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="J35" t="n">
         <v>4.1</v>
@@ -7189,7 +7189,7 @@
         <v>1.12</v>
       </c>
       <c r="P35" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q35" t="n">
         <v>1.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>2.22</v>
       </c>
       <c r="I37" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J37" t="n">
         <v>3.45</v>
@@ -7595,7 +7595,7 @@
         <v>2.16</v>
       </c>
       <c r="V37" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W37" t="n">
         <v>1.35</v>
@@ -7628,7 +7628,7 @@
         <v>25</v>
       </c>
       <c r="AG37" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH37" t="n">
         <v>17</v>
@@ -7688,7 +7688,7 @@
         <v>15.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB37" t="n">
         <v>60</v>
@@ -7700,17 +7700,17 @@
         <v>46</v>
       </c>
       <c r="BE37" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BF37" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BG37" t="n">
         <v>15</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G38" t="n">
         <v>3.65</v>
@@ -7780,7 +7780,7 @@
         <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T38" t="n">
         <v>2.1</v>
@@ -7804,7 +7804,7 @@
         <v>14</v>
       </c>
       <c r="AA38" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AB38" t="n">
         <v>10</v>
@@ -7813,7 +7813,7 @@
         <v>7</v>
       </c>
       <c r="AD38" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE38" t="n">
         <v>60</v>
@@ -7822,7 +7822,7 @@
         <v>23</v>
       </c>
       <c r="AG38" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH38" t="n">
         <v>22</v>
@@ -7846,7 +7846,7 @@
         <v>75</v>
       </c>
       <c r="AO38" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP38" t="n">
         <v>8</v>
@@ -7882,7 +7882,7 @@
         <v>19.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB38" t="n">
         <v>34</v>
@@ -7897,14 +7897,14 @@
         <v>46</v>
       </c>
       <c r="BF38" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BG38" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G39" t="n">
         <v>2.28</v>
@@ -7944,22 +7944,22 @@
         <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J39" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K39" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L39" t="n">
         <v>1.51</v>
       </c>
       <c r="M39" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O39" t="n">
         <v>1.46</v>
@@ -7968,13 +7968,13 @@
         <v>1.62</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R39" t="n">
         <v>1.22</v>
       </c>
       <c r="S39" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T39" t="n">
         <v>1.98</v>
@@ -7983,13 +7983,13 @@
         <v>1.84</v>
       </c>
       <c r="V39" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W39" t="n">
         <v>1.78</v>
       </c>
       <c r="X39" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y39" t="n">
         <v>13</v>
@@ -8004,7 +8004,7 @@
         <v>9</v>
       </c>
       <c r="AC39" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD39" t="n">
         <v>22</v>
@@ -8019,7 +8019,7 @@
         <v>13.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI39" t="n">
         <v>1000</v>
@@ -8043,7 +8043,7 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ39" t="n">
         <v>10</v>
@@ -8052,7 +8052,7 @@
         <v>21</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT39" t="n">
         <v>6.4</v>
@@ -8064,7 +8064,7 @@
         <v>15</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX39" t="n">
         <v>10.5</v>
@@ -8076,7 +8076,7 @@
         <v>18.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB39" t="n">
         <v>20</v>
@@ -8085,20 +8085,20 @@
         <v>20</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BF39" t="n">
         <v>20</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v>3.85</v>
       </c>
       <c r="G40" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H40" t="n">
         <v>1.76</v>
@@ -8150,7 +8150,7 @@
         <v>1.17</v>
       </c>
       <c r="M40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N40" t="n">
         <v>8.199999999999999</v>
@@ -8180,7 +8180,7 @@
         <v>2.12</v>
       </c>
       <c r="W40" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
         <v>23</v>
       </c>
       <c r="AA40" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
         <v>1000</v>
@@ -8204,7 +8204,7 @@
         <v>15</v>
       </c>
       <c r="AE40" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF40" t="n">
         <v>1000</v>
@@ -8213,10 +8213,10 @@
         <v>23</v>
       </c>
       <c r="AH40" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
         <v>1000</v>
@@ -8231,68 +8231,68 @@
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AP40" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT40" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AV40" t="n">
         <v>10.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AX40" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AY40" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AZ40" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BA40" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BB40" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BF40" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.84</v>
+        <v>4.9</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
         <v>1.82</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I41" t="n">
         <v>5.7</v>
@@ -8341,7 +8341,7 @@
         <v>4.1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M41" t="n">
         <v>1.07</v>
@@ -8383,7 +8383,7 @@
         <v>21</v>
       </c>
       <c r="Z41" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA41" t="n">
         <v>1000</v>
@@ -8452,7 +8452,7 @@
         <v>16</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX41" t="n">
         <v>9.4</v>
@@ -8464,7 +8464,7 @@
         <v>15.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB41" t="n">
         <v>16.5</v>
@@ -8476,7 +8476,7 @@
         <v>4.5</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF41" t="n">
         <v>9</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="G42" t="n">
         <v>1.84</v>
@@ -8526,7 +8526,7 @@
         <v>5.1</v>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J42" t="n">
         <v>3.55</v>
@@ -8541,40 +8541,40 @@
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>1.66</v>
+        <v>2.68</v>
       </c>
       <c r="O42" t="n">
         <v>1.36</v>
       </c>
       <c r="P42" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R42" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W42" t="n">
         <v>2.18</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="n">
         <v>1000</v>
@@ -8583,34 +8583,34 @@
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE42" t="n">
         <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI42" t="n">
         <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL42" t="n">
         <v>1000</v>
@@ -8619,68 +8619,68 @@
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.33</v>
+        <v>3.7</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.24</v>
+        <v>3.95</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.33</v>
+        <v>4</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.24</v>
+        <v>4.2</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.33</v>
+        <v>6.6</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.33</v>
+        <v>7.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.26</v>
+        <v>3.8</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.24</v>
+        <v>4.2</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.33</v>
+        <v>8.6</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.26</v>
+        <v>3.8</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.24</v>
+        <v>4.2</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.25</v>
+        <v>3.75</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.26</v>
+        <v>3.75</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.29</v>
+        <v>4</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.24</v>
+        <v>3.75</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.18</v>
+        <v>4.2</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G43" t="n">
         <v>1.9</v>
@@ -8726,16 +8726,16 @@
         <v>3.7</v>
       </c>
       <c r="K43" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L43" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O43" t="n">
         <v>1.36</v>
@@ -8753,7 +8753,7 @@
         <v>3.9</v>
       </c>
       <c r="T43" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U43" t="n">
         <v>1.93</v>
@@ -8762,31 +8762,31 @@
         <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="X43" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA43" t="n">
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD43" t="n">
         <v>19.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF43" t="n">
         <v>11</v>
@@ -8804,7 +8804,7 @@
         <v>21</v>
       </c>
       <c r="AK43" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
         <v>1000</v>
@@ -8819,62 +8819,62 @@
         <v>90</v>
       </c>
       <c r="AP43" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ43" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR43" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT43" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AX43" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY43" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ43" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="BB43" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BC43" t="n">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF43" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>
@@ -8911,13 +8911,13 @@
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-22 22:10:16</t>
+          <t>2026-04-23 00:30:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="I2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.55</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.3</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -826,7 +826,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -835,10 +835,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="AV2" t="n">
         <v>5.6</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AW2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>2.88</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.34</v>
@@ -975,146 +975,146 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
         <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3" t="n">
         <v>7.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AB3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AC3" t="n">
         <v>14</v>
       </c>
       <c r="AD3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>310</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AP3" t="n">
         <v>11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>740</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>270</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>230</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>390</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>8.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>7.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AV3" t="n">
         <v>9.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB3" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>4.7</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="I4" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="J4" t="n">
         <v>5.2</v>
@@ -1169,31 +1169,31 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="R4" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="S4" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="U4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="W4" t="n">
         <v>1.25</v>
@@ -1205,13 +1205,13 @@
         <v>27</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AB4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AC4" t="n">
         <v>16.5</v>
@@ -1220,19 +1220,19 @@
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG4" t="n">
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>130</v>
@@ -1241,34 +1241,34 @@
         <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AP4" t="n">
         <v>34</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AU4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV4" t="n">
         <v>11.5</v>
@@ -1280,7 +1280,7 @@
         <v>30</v>
       </c>
       <c r="AY4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AZ4" t="n">
         <v>14</v>
@@ -1289,7 +1289,7 @@
         <v>16.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1298,17 +1298,17 @@
         <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BF4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1366,13 +1366,13 @@
         <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
         <v>1.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>1.34</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1447,16 +1447,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT5" t="n">
         <v>7.4</v>
@@ -1465,44 +1465,44 @@
         <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
         <v>4.4</v>
       </c>
       <c r="I6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S6" t="n">
         <v>4.5</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="X6" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1602,10 +1602,10 @@
         <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1614,89 +1614,89 @@
         <v>12</v>
       </c>
       <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AS6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>19</v>
-      </c>
       <c r="BC6" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.6</v>
+        <v>17</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
         <v>7.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="G7" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="H7" t="n">
         <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="K7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V7" t="n">
         <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1808,7 +1808,7 @@
         <v>6.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1817,7 +1817,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AK7" t="n">
         <v>20</v>
@@ -1829,68 +1829,68 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AQ7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="AW7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY7" t="n">
         <v>5.4</v>
       </c>
-      <c r="AU7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
@@ -1948,7 +1948,7 @@
         <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
         <v>1.78</v>
@@ -1960,10 +1960,10 @@
         <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
         <v>2.02</v>
@@ -1993,7 +1993,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2026,10 +2026,10 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>8</v>
@@ -2041,19 +2041,19 @@
         <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU8" t="n">
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX8" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.7</v>
       </c>
       <c r="AY8" t="n">
         <v>4.3</v>
@@ -2062,29 +2062,29 @@
         <v>4.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB8" t="n">
         <v>5.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BD8" t="n">
         <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF8" t="n">
         <v>5.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="K9" t="n">
         <v>2.84</v>
       </c>
       <c r="L9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
         <v>1.19</v>
@@ -2142,7 +2142,7 @@
         <v>2.18</v>
       </c>
       <c r="O9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="P9" t="n">
         <v>1.36</v>
@@ -2157,16 +2157,16 @@
         <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
         <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
         <v>2.28</v>
@@ -2351,10 +2351,10 @@
         <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U10" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="V10" t="n">
         <v>1.74</v>
@@ -2402,7 +2402,7 @@
         <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
         <v>34</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.82</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -2518,7 +2518,7 @@
         <v>4.2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.3</v>
@@ -2527,40 +2527,40 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R11" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
         <v>38</v>
@@ -2569,16 +2569,16 @@
         <v>90</v>
       </c>
       <c r="AB11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
         <v>18</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="n">
         <v>13.5</v>
@@ -2605,28 +2605,28 @@
         <v>65</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
         <v>21</v>
       </c>
       <c r="AQ11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR11" t="n">
         <v>34</v>
       </c>
       <c r="AS11" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AT11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
         <v>16.5</v>
@@ -2641,7 +2641,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
         <v>40</v>
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG11" t="n">
         <v>30</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>6.6</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H12" t="n">
         <v>1.51</v>
@@ -2709,16 +2709,16 @@
         <v>1.56</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.37</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
         <v>4.1</v>
@@ -2727,10 +2727,10 @@
         <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R12" t="n">
         <v>1.41</v>
@@ -2739,10 +2739,10 @@
         <v>3.1</v>
       </c>
       <c r="T12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.92</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.9</v>
       </c>
       <c r="V12" t="n">
         <v>2.74</v>
@@ -2751,7 +2751,7 @@
         <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
         <v>9</v>
@@ -2763,7 +2763,7 @@
         <v>14.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AC12" t="n">
         <v>11</v>
@@ -2826,10 +2826,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
         <v>7</v>
@@ -2838,29 +2838,29 @@
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
         <v>6.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I13" t="n">
         <v>1.73</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.75</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
@@ -2921,16 +2921,16 @@
         <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
         <v>1.7</v>
@@ -2939,13 +2939,13 @@
         <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="W13" t="n">
         <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
         <v>11.5</v>
@@ -2954,10 +2954,10 @@
         <v>12.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC13" t="n">
         <v>10.5</v>
@@ -2966,13 +2966,13 @@
         <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AG13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2984,7 +2984,7 @@
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL13" t="n">
         <v>60</v>
@@ -2999,19 +2999,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AP13" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR13" t="n">
         <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT13" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU13" t="n">
         <v>8.199999999999999</v>
@@ -3023,38 +3023,38 @@
         <v>14.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD13" t="n">
         <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3091,13 @@
         <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
         <v>4.2</v>
@@ -3109,31 +3109,31 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S14" t="n">
         <v>2.36</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U14" t="n">
         <v>2.86</v>
       </c>
       <c r="V14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W14" t="n">
         <v>1.46</v>
@@ -3142,16 +3142,16 @@
         <v>27</v>
       </c>
       <c r="Y14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
         <v>32</v>
       </c>
       <c r="AB14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC14" t="n">
         <v>10</v>
@@ -3160,16 +3160,16 @@
         <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG14" t="n">
         <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI14" t="n">
         <v>26</v>
@@ -3178,13 +3178,13 @@
         <v>50</v>
       </c>
       <c r="AK14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL14" t="n">
         <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN14" t="n">
         <v>18</v>
@@ -3193,19 +3193,19 @@
         <v>11</v>
       </c>
       <c r="AP14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR14" t="n">
         <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT14" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU14" t="n">
         <v>9</v>
@@ -3217,7 +3217,7 @@
         <v>18</v>
       </c>
       <c r="AX14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY14" t="n">
         <v>12.5</v>
@@ -3226,29 +3226,29 @@
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB14" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BC14" t="n">
         <v>25</v>
       </c>
       <c r="BD14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE14" t="n">
         <v>22</v>
       </c>
       <c r="BF14" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3279,136 +3279,136 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.04</v>
-      </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.52</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.56</v>
-      </c>
       <c r="T15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U15" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH15" t="n">
         <v>15.5</v>
       </c>
-      <c r="AC15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
         <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>18.5</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AR15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT15" t="n">
         <v>12</v>
       </c>
-      <c r="AS15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>11</v>
-      </c>
       <c r="AU15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
@@ -3417,32 +3417,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="BB15" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="BE15" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J16" t="n">
         <v>4.5</v>
@@ -3503,16 +3503,16 @@
         <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
         <v>1.49</v>
@@ -3521,10 +3521,10 @@
         <v>2.72</v>
       </c>
       <c r="V16" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X16" t="n">
         <v>48</v>
@@ -3554,7 +3554,7 @@
         <v>32</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH16" t="n">
         <v>14.5</v>
@@ -3566,7 +3566,7 @@
         <v>65</v>
       </c>
       <c r="AK16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL16" t="n">
         <v>34</v>
@@ -3584,19 +3584,19 @@
         <v>26</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
         <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>19.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
@@ -3617,7 +3617,7 @@
         <v>21</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.6</v>
+        <v>50</v>
       </c>
       <c r="BC16" t="n">
         <v>28</v>
@@ -3626,17 +3626,17 @@
         <v>29</v>
       </c>
       <c r="BE16" t="n">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="BF16" t="n">
         <v>17</v>
       </c>
       <c r="BG16" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G17" t="n">
         <v>2.54</v>
       </c>
-      <c r="G17" t="n">
-        <v>2.58</v>
-      </c>
       <c r="H17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>3.3</v>
@@ -3688,37 +3688,37 @@
         <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
         <v>4.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
         <v>2.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X17" t="n">
         <v>11</v>
@@ -3730,16 +3730,16 @@
         <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC17" t="n">
         <v>7</v>
       </c>
       <c r="AD17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>40</v>
@@ -3763,7 +3763,7 @@
         <v>30</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM17" t="n">
         <v>120</v>
@@ -3772,7 +3772,7 @@
         <v>28</v>
       </c>
       <c r="AO17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP17" t="n">
         <v>10</v>
@@ -3793,25 +3793,25 @@
         <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
         <v>36</v>
       </c>
       <c r="AX17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA17" t="n">
         <v>48</v>
       </c>
       <c r="BB17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC17" t="n">
         <v>28</v>
@@ -3820,7 +3820,7 @@
         <v>42</v>
       </c>
       <c r="BE17" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF17" t="n">
         <v>25</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G18" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="H18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I18" t="n">
         <v>3.1</v>
       </c>
-      <c r="I18" t="n">
-        <v>3.15</v>
-      </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
         <v>1.38</v>
@@ -3894,7 +3894,7 @@
         <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R18" t="n">
         <v>1.45</v>
@@ -3906,16 +3906,16 @@
         <v>1.68</v>
       </c>
       <c r="U18" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="X18" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y18" t="n">
         <v>14</v>
@@ -3930,10 +3930,10 @@
         <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
         <v>34</v>
@@ -3951,7 +3951,7 @@
         <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK18" t="n">
         <v>24</v>
@@ -3963,13 +3963,13 @@
         <v>85</v>
       </c>
       <c r="AN18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>12.5</v>
@@ -3978,7 +3978,7 @@
         <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AT18" t="n">
         <v>10.5</v>
@@ -3996,7 +3996,7 @@
         <v>15</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>14</v>
@@ -4005,7 +4005,7 @@
         <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC18" t="n">
         <v>22</v>
@@ -4014,17 +4014,17 @@
         <v>30</v>
       </c>
       <c r="BE18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF18" t="n">
         <v>15.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G19" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H19" t="n">
         <v>2.76</v>
@@ -4067,7 +4067,7 @@
         <v>2.82</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
         <v>3.45</v>
@@ -4082,28 +4082,28 @@
         <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U19" t="n">
         <v>2.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W19" t="n">
         <v>1.52</v>
@@ -4178,7 +4178,7 @@
         <v>10</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
         <v>11.5</v>
@@ -4208,7 +4208,7 @@
         <v>42</v>
       </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF19" t="n">
         <v>29</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
         <v>1.33</v>
@@ -4282,7 +4282,7 @@
         <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R20" t="n">
         <v>1.36</v>
@@ -4294,7 +4294,7 @@
         <v>1.78</v>
       </c>
       <c r="U20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
         <v>1.67</v>
@@ -4321,7 +4321,7 @@
         <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE20" t="n">
         <v>40</v>
@@ -4330,7 +4330,7 @@
         <v>22</v>
       </c>
       <c r="AG20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>18</v>
@@ -4345,7 +4345,7 @@
         <v>38</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -4354,7 +4354,7 @@
         <v>36</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>12.5</v>
@@ -4369,13 +4369,13 @@
         <v>27</v>
       </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU20" t="n">
         <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW20" t="n">
         <v>23</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H21" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>3.3</v>
@@ -4473,28 +4473,28 @@
         <v>1.44</v>
       </c>
       <c r="P21" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
         <v>2.34</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X21" t="n">
         <v>11</v>
@@ -4503,7 +4503,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA21" t="n">
         <v>42</v>
@@ -4536,7 +4536,7 @@
         <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL21" t="n">
         <v>60</v>
@@ -4569,7 +4569,7 @@
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW21" t="n">
         <v>28</v>
@@ -4581,13 +4581,13 @@
         <v>12.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
         <v>44</v>
       </c>
       <c r="BB21" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BC21" t="n">
         <v>32</v>
@@ -4599,14 +4599,14 @@
         <v>85</v>
       </c>
       <c r="BF21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG21" t="n">
         <v>27</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H22" t="n">
         <v>4.1</v>
@@ -4661,34 +4661,34 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
         <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
         <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="X22" t="n">
         <v>11.5</v>
@@ -4703,13 +4703,13 @@
         <v>85</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC22" t="n">
         <v>7.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
         <v>55</v>
@@ -4790,17 +4790,17 @@
         <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="BF22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG22" t="n">
         <v>55</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4831,70 +4831,70 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="G23" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="J23" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>1.31</v>
       </c>
       <c r="P23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.94</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U23" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="V23" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB23" t="n">
         <v>19</v>
@@ -4903,7 +4903,7 @@
         <v>9.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>22</v>
@@ -4912,13 +4912,13 @@
         <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ23" t="n">
         <v>1000</v>
@@ -4936,43 +4936,43 @@
         <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AT23" t="n">
-        <v>12.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW23" t="n">
         <v>5.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.9</v>
+        <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB23" t="n">
         <v>6.2</v>
@@ -4990,11 +4990,11 @@
         <v>6</v>
       </c>
       <c r="BG23" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I24" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.49</v>
@@ -5049,13 +5049,13 @@
         <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O24" t="n">
         <v>1.42</v>
       </c>
       <c r="P24" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q24" t="n">
         <v>2.26</v>
@@ -5094,7 +5094,7 @@
         <v>14</v>
       </c>
       <c r="AC24" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
         <v>14</v>
@@ -5142,53 +5142,53 @@
         <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.3</v>
+        <v>19.5</v>
       </c>
       <c r="AX24" t="n">
         <v>4.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG24" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5219,49 +5219,49 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G25" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T25" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U25" t="n">
         <v>1.95</v>
@@ -5270,13 +5270,13 @@
         <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X25" t="n">
         <v>16.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z25" t="n">
         <v>48</v>
@@ -5285,7 +5285,7 @@
         <v>190</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC25" t="n">
         <v>10.5</v>
@@ -5297,22 +5297,22 @@
         <v>95</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG25" t="n">
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI25" t="n">
         <v>85</v>
       </c>
       <c r="AJ25" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL25" t="n">
         <v>40</v>
@@ -5321,7 +5321,7 @@
         <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AO25" t="n">
         <v>130</v>
@@ -5330,25 +5330,25 @@
         <v>12.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT25" t="n">
         <v>7.2</v>
       </c>
       <c r="AU25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW25" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>6.2</v>
       </c>
       <c r="AX25" t="n">
         <v>9.199999999999999</v>
@@ -5357,10 +5357,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BB25" t="n">
         <v>15.5</v>
@@ -5369,20 +5369,20 @@
         <v>15.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.8</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25" t="n">
         <v>9.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5413,28 +5413,28 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="G26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H26" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.29</v>
       </c>
       <c r="M26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N26" t="n">
         <v>5.9</v>
@@ -5443,16 +5443,16 @@
         <v>1.19</v>
       </c>
       <c r="P26" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R26" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S26" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T26" t="n">
         <v>1.65</v>
@@ -5461,122 +5461,122 @@
         <v>2.38</v>
       </c>
       <c r="V26" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.21</v>
       </c>
       <c r="X26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y26" t="n">
         <v>12.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AF26" t="n">
         <v>48</v>
       </c>
       <c r="AG26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AJ26" t="n">
         <v>120</v>
       </c>
       <c r="AK26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN26" t="n">
         <v>65</v>
       </c>
-      <c r="AL26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>60</v>
-      </c>
       <c r="AO26" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU26" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY26" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB26" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BC26" t="n">
         <v>50</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BE26" t="n">
         <v>27</v>
       </c>
       <c r="BF26" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BG26" t="n">
         <v>6.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5631,28 +5631,28 @@
         <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O27" t="n">
         <v>1.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R27" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T27" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U27" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V27" t="n">
         <v>1.28</v>
@@ -5673,10 +5673,10 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
         <v>20</v>
@@ -5709,68 +5709,68 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AQ27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT27" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AU27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AY27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>3.25</v>
       </c>
       <c r="H28" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I28" t="n">
         <v>3.1</v>
@@ -5837,16 +5837,16 @@
         <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S28" t="n">
         <v>6.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
         <v>1.48</v>
@@ -5909,16 +5909,16 @@
         <v>75</v>
       </c>
       <c r="AP28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
@@ -5927,44 +5927,44 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC28" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC28" t="n">
-        <v>9</v>
-      </c>
       <c r="BD28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="BG28" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
         <v>2.62</v>
       </c>
       <c r="I29" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J29" t="n">
         <v>3</v>
@@ -6028,7 +6028,7 @@
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="R29" t="n">
         <v>1.24</v>
@@ -6037,13 +6037,13 @@
         <v>4.8</v>
       </c>
       <c r="T29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.92</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.9</v>
-      </c>
       <c r="V29" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W29" t="n">
         <v>1.41</v>
@@ -6064,7 +6064,7 @@
         <v>10.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29" t="n">
         <v>13</v>
@@ -6112,7 +6112,7 @@
         <v>13.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT29" t="n">
         <v>9</v>
@@ -6124,7 +6124,7 @@
         <v>10.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX29" t="n">
         <v>17.5</v>
@@ -6133,32 +6133,32 @@
         <v>12</v>
       </c>
       <c r="AZ29" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="BA29" t="n">
         <v>40</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="BG29" t="n">
         <v>12</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>6.6</v>
       </c>
       <c r="H30" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I30" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="J30" t="n">
         <v>4.2</v>
@@ -6219,10 +6219,10 @@
         <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R30" t="n">
         <v>1.36</v>
@@ -6231,19 +6231,19 @@
         <v>3.6</v>
       </c>
       <c r="T30" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V30" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="W30" t="n">
         <v>1.17</v>
       </c>
       <c r="X30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y30" t="n">
         <v>7.8</v>
@@ -6258,28 +6258,28 @@
         <v>20</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AE30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG30" t="n">
         <v>25</v>
       </c>
       <c r="AH30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI30" t="n">
         <v>40</v>
       </c>
       <c r="AJ30" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AK30" t="n">
         <v>100</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>7</v>
@@ -6312,7 +6312,7 @@
         <v>17.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV30" t="n">
         <v>9.4</v>
@@ -6333,26 +6333,26 @@
         <v>34</v>
       </c>
       <c r="BB30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD30" t="n">
         <v>16.5</v>
       </c>
-      <c r="BC30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BE30" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="BF30" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG30" t="n">
         <v>9.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6383,64 +6383,64 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G31" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H31" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M31" t="n">
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="R31" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S31" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="T31" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="U31" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="V31" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W31" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X31" t="n">
         <v>60</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z31" t="n">
         <v>1000</v>
@@ -6449,13 +6449,13 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AC31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
@@ -6467,86 +6467,86 @@
         <v>12.5</v>
       </c>
       <c r="AH31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK31" t="n">
         <v>18</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>15</v>
       </c>
       <c r="AL31" t="n">
         <v>22</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AN31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AO31" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AV31" t="n">
         <v>6.6</v>
       </c>
       <c r="AW31" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="AX31" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB31" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="BD31" t="n">
         <v>6.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6586,13 +6586,13 @@
         <v>13</v>
       </c>
       <c r="I32" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K32" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>1.15</v>
@@ -6619,10 +6619,10 @@
         <v>1.59</v>
       </c>
       <c r="T32" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U32" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V32" t="n">
         <v>1.07</v>
@@ -6631,7 +6631,7 @@
         <v>5.1</v>
       </c>
       <c r="X32" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Y32" t="n">
         <v>90</v>
@@ -6643,19 +6643,19 @@
         <v>430</v>
       </c>
       <c r="AB32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC32" t="n">
         <v>24</v>
       </c>
       <c r="AD32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE32" t="n">
         <v>140</v>
       </c>
       <c r="AF32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG32" t="n">
         <v>13</v>
@@ -6679,16 +6679,16 @@
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AO32" t="n">
         <v>90</v>
       </c>
       <c r="AP32" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="AQ32" t="n">
-        <v>55</v>
+        <v>15.5</v>
       </c>
       <c r="AR32" t="n">
         <v>17</v>
@@ -6697,13 +6697,13 @@
         <v>18</v>
       </c>
       <c r="AT32" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AU32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV32" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AW32" t="n">
         <v>16.5</v>
@@ -6715,10 +6715,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BA32" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="BB32" t="n">
         <v>11.5</v>
@@ -6727,20 +6727,20 @@
         <v>11.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE32" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="BF32" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BG32" t="n">
         <v>60</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G33" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J33" t="n">
         <v>4.6</v>
       </c>
       <c r="K33" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L33" t="n">
         <v>1.25</v>
@@ -6795,34 +6795,34 @@
         <v>1.02</v>
       </c>
       <c r="N33" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="R33" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="S33" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6831,31 +6831,31 @@
         <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD33" t="n">
         <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI33" t="n">
         <v>1000</v>
@@ -6864,77 +6864,77 @@
         <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>75</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>44</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6965,25 +6965,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G34" t="n">
         <v>2.64</v>
       </c>
       <c r="H34" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I34" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J34" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K34" t="n">
         <v>4.3</v>
       </c>
       <c r="L34" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M34" t="n">
         <v>1.02</v>
@@ -7001,134 +7001,134 @@
         <v>1.41</v>
       </c>
       <c r="R34" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S34" t="n">
         <v>2.02</v>
       </c>
       <c r="T34" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="V34" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W34" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z34" t="n">
         <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF34" t="n">
         <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ34" t="n">
         <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G35" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H35" t="n">
         <v>2.22</v>
@@ -7177,34 +7177,34 @@
         <v>3.5</v>
       </c>
       <c r="L35" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N35" t="n">
         <v>3.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q35" t="n">
         <v>2.04</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T35" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U35" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V35" t="n">
         <v>1.8</v>
@@ -7213,19 +7213,19 @@
         <v>1.35</v>
       </c>
       <c r="X35" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y35" t="n">
         <v>9.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
         <v>27</v>
       </c>
       <c r="AB35" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC35" t="n">
         <v>7.8</v>
@@ -7234,13 +7234,13 @@
         <v>11</v>
       </c>
       <c r="AE35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF35" t="n">
         <v>25</v>
       </c>
       <c r="AG35" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH35" t="n">
         <v>17</v>
@@ -7261,16 +7261,16 @@
         <v>95</v>
       </c>
       <c r="AN35" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AO35" t="n">
         <v>17.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ35" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR35" t="n">
         <v>12.5</v>
@@ -7288,22 +7288,22 @@
         <v>10</v>
       </c>
       <c r="AW35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY35" t="n">
         <v>14</v>
       </c>
       <c r="AZ35" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA35" t="n">
         <v>34</v>
       </c>
       <c r="BB35" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BC35" t="n">
         <v>40</v>
@@ -7315,14 +7315,14 @@
         <v>80</v>
       </c>
       <c r="BF35" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BG35" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G36" t="n">
         <v>3.6</v>
       </c>
-      <c r="G36" t="n">
-        <v>3.65</v>
-      </c>
       <c r="H36" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J36" t="n">
         <v>3.05</v>
       </c>
       <c r="K36" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L36" t="n">
         <v>1.59</v>
@@ -7380,7 +7380,7 @@
         <v>2.7</v>
       </c>
       <c r="O36" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P36" t="n">
         <v>1.55</v>
@@ -7389,7 +7389,7 @@
         <v>2.74</v>
       </c>
       <c r="R36" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S36" t="n">
         <v>5.8</v>
@@ -7401,22 +7401,22 @@
         <v>1.81</v>
       </c>
       <c r="V36" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="W36" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X36" t="n">
         <v>8.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Z36" t="n">
         <v>14</v>
       </c>
       <c r="AA36" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB36" t="n">
         <v>9.800000000000001</v>
@@ -7440,10 +7440,10 @@
         <v>24</v>
       </c>
       <c r="AI36" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK36" t="n">
         <v>60</v>
@@ -7452,19 +7452,19 @@
         <v>85</v>
       </c>
       <c r="AM36" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN36" t="n">
         <v>95</v>
       </c>
       <c r="AO36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP36" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ36" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR36" t="n">
         <v>13</v>
@@ -7476,7 +7476,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV36" t="n">
         <v>11.5</v>
@@ -7494,19 +7494,19 @@
         <v>21</v>
       </c>
       <c r="BA36" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB36" t="n">
         <v>60</v>
       </c>
       <c r="BC36" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BD36" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE36" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BF36" t="n">
         <v>65</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7547,28 +7547,28 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G37" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H37" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J37" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K37" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N37" t="n">
         <v>2.98</v>
@@ -7577,140 +7577,140 @@
         <v>1.45</v>
       </c>
       <c r="P37" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T37" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U37" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V37" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W37" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X37" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z37" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH37" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AL37" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX37" t="n">
         <v>10</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AY37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC37" t="n">
         <v>21</v>
       </c>
-      <c r="AS37" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>20</v>
-      </c>
       <c r="BD37" t="n">
-        <v>5.3</v>
+        <v>42</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF37" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="G38" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H38" t="n">
         <v>1.04</v>
@@ -7753,7 +7753,7 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="K38" t="n">
         <v>950</v>
@@ -7765,13 +7765,13 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="O38" t="n">
         <v>1.23</v>
       </c>
       <c r="P38" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q38" t="n">
         <v>1.23</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7938,10 +7938,10 @@
         <v>3.85</v>
       </c>
       <c r="G39" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H39" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="I39" t="n">
         <v>1.89</v>
@@ -7950,7 +7950,7 @@
         <v>4.1</v>
       </c>
       <c r="K39" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L39" t="n">
         <v>1.21</v>
@@ -7959,7 +7959,7 @@
         <v>1.02</v>
       </c>
       <c r="N39" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="O39" t="n">
         <v>1.11</v>
@@ -7971,10 +7971,10 @@
         <v>1.36</v>
       </c>
       <c r="R39" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S39" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -8043,62 +8043,62 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G40" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H40" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I40" t="n">
         <v>5.7</v>
@@ -8144,155 +8144,155 @@
         <v>3.95</v>
       </c>
       <c r="K40" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L40" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M40" t="n">
         <v>1.06</v>
       </c>
       <c r="N40" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O40" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P40" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T40" t="n">
         <v>1.87</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.8</v>
-      </c>
       <c r="U40" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
         <v>1.22</v>
       </c>
       <c r="W40" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X40" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y40" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE40" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF40" t="n">
         <v>12.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH40" t="n">
         <v>23</v>
       </c>
       <c r="AI40" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ40" t="n">
         <v>21</v>
       </c>
       <c r="AK40" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AL40" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AP40" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AQ40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ40" t="n">
         <v>16.5</v>
       </c>
-      <c r="AR40" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>17</v>
-      </c>
       <c r="BA40" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB40" t="n">
         <v>16</v>
       </c>
       <c r="BC40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE40" t="n">
         <v>6</v>
       </c>
-      <c r="BE40" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BF40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG40" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G41" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I41" t="n">
         <v>6.2</v>
@@ -8338,7 +8338,7 @@
         <v>3.6</v>
       </c>
       <c r="K41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L41" t="n">
         <v>1.43</v>
@@ -8365,16 +8365,16 @@
         <v>3.7</v>
       </c>
       <c r="T41" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U41" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>1.2</v>
       </c>
       <c r="W41" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X41" t="n">
         <v>15.5</v>
@@ -8392,19 +8392,19 @@
         <v>9</v>
       </c>
       <c r="AC41" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD41" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE41" t="n">
         <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG41" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH41" t="n">
         <v>25</v>
@@ -8416,7 +8416,7 @@
         <v>23</v>
       </c>
       <c r="AK41" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL41" t="n">
         <v>1000</v>
@@ -8431,16 +8431,16 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AQ41" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="AR41" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT41" t="n">
         <v>6.6</v>
@@ -8449,44 +8449,44 @@
         <v>7.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX41" t="n">
         <v>8.6</v>
       </c>
       <c r="AY41" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AZ41" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC41" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF41" t="n">
         <v>9</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G42" t="n">
         <v>1.87</v>
       </c>
-      <c r="G42" t="n">
-        <v>1.9</v>
-      </c>
       <c r="H42" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J42" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K42" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L42" t="n">
         <v>1.44</v>
@@ -8544,55 +8544,55 @@
         <v>3.4</v>
       </c>
       <c r="O42" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P42" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q42" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W42" t="n">
         <v>2.14</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X42" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB42" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE42" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="n">
         <v>11</v>
@@ -8604,83 +8604,83 @@
         <v>1000</v>
       </c>
       <c r="AI42" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ42" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK42" t="n">
         <v>22</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM42" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AO42" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP42" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ42" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR42" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF42" t="n">
         <v>12.5</v>
       </c>
-      <c r="AT42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>13</v>
-      </c>
       <c r="BG42" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8717,40 +8717,40 @@
         <v>44</v>
       </c>
       <c r="H43" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="I43" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="J43" t="n">
-        <v>1.1</v>
+        <v>1.73</v>
       </c>
       <c r="K43" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O43" t="n">
         <v>1.3</v>
       </c>
       <c r="P43" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q43" t="n">
         <v>1.3</v>
       </c>
       <c r="R43" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S43" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -8759,10 +8759,10 @@
         <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8819,52 +8819,52 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
         <v>1.01</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="n">
         <v>3.55</v>
@@ -769,158 +769,158 @@
         <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
         <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.6</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.4</v>
+        <v>75</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.88</v>
+        <v>16.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="I3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
         <v>1.34</v>
@@ -975,40 +975,40 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
         <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3" t="n">
         <v>7.6</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="AB3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
         <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AH3" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
         <v>42</v>
@@ -1044,34 +1044,34 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AU3" t="n">
         <v>11.5</v>
@@ -1080,41 +1080,41 @@
         <v>9.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="AX3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB3" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
         <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -1148,52 +1148,52 @@
         <v>4.7</v>
       </c>
       <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J4" t="n">
         <v>5.1</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.2</v>
-      </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q4" t="n">
         <v>1.28</v>
       </c>
       <c r="R4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="S4" t="n">
         <v>1.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V4" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="W4" t="n">
         <v>1.25</v>
@@ -1202,10 +1202,10 @@
         <v>60</v>
       </c>
       <c r="Y4" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
         <v>24</v>
@@ -1217,19 +1217,19 @@
         <v>16.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>14.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI4" t="n">
         <v>18.5</v>
@@ -1238,13 +1238,13 @@
         <v>130</v>
       </c>
       <c r="AK4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN4" t="n">
         <v>20</v>
@@ -1253,10 +1253,10 @@
         <v>4.2</v>
       </c>
       <c r="AP4" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
         <v>17</v>
@@ -1271,7 +1271,7 @@
         <v>14</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>13.5</v>
@@ -1283,13 +1283,13 @@
         <v>21</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
         <v>16.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1304,11 +1304,11 @@
         <v>17.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -1339,64 +1339,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G5" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="n">
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1417,13 +1417,13 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1432,7 +1432,7 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1441,68 +1441,68 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
         <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
         <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G6" t="n">
         <v>2.02</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.08</v>
-      </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.51</v>
@@ -1566,31 +1566,31 @@
         <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T6" t="n">
         <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,22 +1599,22 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1623,10 +1623,10 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1647,56 +1647,56 @@
         <v>12</v>
       </c>
       <c r="AR6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS6" t="n">
-        <v>10</v>
-      </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AX6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD6" t="n">
         <v>10</v>
       </c>
-      <c r="AY6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>17</v>
-      </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="G7" t="n">
         <v>1.24</v>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.38</v>
@@ -1751,40 +1751,40 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
         <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1808,7 +1808,7 @@
         <v>6.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>8.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1835,31 +1835,31 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AR7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS7" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AT7" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="AV7" t="n">
         <v>8.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="AY7" t="n">
         <v>5.4</v>
@@ -1868,29 +1868,29 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="H8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="I8" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
         <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
         <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
         <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
         <v>15</v>
@@ -2014,7 +2014,7 @@
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2050,7 +2050,7 @@
         <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX8" t="n">
         <v>4.8</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -2121,19 +2121,19 @@
         <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J9" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M9" t="n">
         <v>1.19</v>
@@ -2148,7 +2148,7 @@
         <v>1.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.12</v>
@@ -2157,10 +2157,10 @@
         <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>2.28</v>
       </c>
       <c r="I10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2333,7 +2333,7 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -2345,19 +2345,19 @@
         <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S10" t="n">
         <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U10" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W10" t="n">
         <v>1.45</v>
@@ -2375,7 +2375,7 @@
         <v>32</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC10" t="n">
         <v>9.6</v>
@@ -2387,10 +2387,10 @@
         <v>21</v>
       </c>
       <c r="AF10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
         <v>14.5</v>
@@ -2417,7 +2417,7 @@
         <v>12</v>
       </c>
       <c r="AP10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ10" t="n">
         <v>13</v>
@@ -2432,7 +2432,7 @@
         <v>15.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV10" t="n">
         <v>10.5</v>
@@ -2444,19 +2444,19 @@
         <v>22</v>
       </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB10" t="n">
         <v>44</v>
       </c>
       <c r="BC10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD10" t="n">
         <v>29</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="G11" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
         <v>4.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T11" t="n">
         <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="X11" t="n">
         <v>22</v>
@@ -2566,7 +2566,7 @@
         <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB11" t="n">
         <v>12.5</v>
@@ -2578,22 +2578,22 @@
         <v>18</v>
       </c>
       <c r="AE11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ11" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK11" t="n">
         <v>16.5</v>
@@ -2602,10 +2602,10 @@
         <v>26</v>
       </c>
       <c r="AM11" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO11" t="n">
         <v>38</v>
@@ -2614,19 +2614,19 @@
         <v>21</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR11" t="n">
         <v>34</v>
       </c>
       <c r="AS11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AT11" t="n">
         <v>11</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
         <v>16.5</v>
@@ -2638,19 +2638,19 @@
         <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC11" t="n">
         <v>15</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>15.5</v>
       </c>
       <c r="BD11" t="n">
         <v>24</v>
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -2697,94 +2697,94 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="G12" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I12" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="J12" t="n">
         <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U12" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="V12" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AA12" t="n">
         <v>14.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF12" t="n">
         <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
         <v>1000</v>
@@ -2802,13 +2802,13 @@
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR12" t="n">
         <v>7.4</v>
@@ -2817,50 +2817,50 @@
         <v>10.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>19.5</v>
+        <v>5.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AY12" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AZ12" t="n">
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>30</v>
+        <v>6.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="G13" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="I13" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T13" t="n">
         <v>1.7</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Y13" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AA13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AF13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
         <v>21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.4</v>
+        <v>2.48</v>
       </c>
       <c r="AR13" t="n">
-        <v>10</v>
+        <v>2.78</v>
       </c>
       <c r="AS13" t="n">
-        <v>15</v>
+        <v>3.65</v>
       </c>
       <c r="AT13" t="n">
-        <v>19.5</v>
+        <v>2.56</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.800000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>14.5</v>
+        <v>2.68</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.2</v>
+        <v>2.74</v>
       </c>
       <c r="AY13" t="n">
-        <v>17.5</v>
+        <v>2.9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>2.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.6</v>
+        <v>2.54</v>
       </c>
       <c r="BB13" t="n">
-        <v>8</v>
+        <v>2.74</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.6</v>
+        <v>2.74</v>
       </c>
       <c r="BD13" t="n">
-        <v>21</v>
+        <v>2.74</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.4</v>
+        <v>2.74</v>
       </c>
       <c r="BF13" t="n">
-        <v>19</v>
+        <v>2.66</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>2.42</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I14" t="n">
         <v>2.34</v>
@@ -3100,7 +3100,7 @@
         <v>3.95</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>1.28</v>
@@ -3115,37 +3115,37 @@
         <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
         <v>1.54</v>
       </c>
       <c r="R14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U14" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
         <v>32</v>
@@ -3154,13 +3154,13 @@
         <v>21</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
         <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF14" t="n">
         <v>26</v>
@@ -3169,34 +3169,34 @@
         <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI14" t="n">
         <v>26</v>
       </c>
       <c r="AJ14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL14" t="n">
         <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP14" t="n">
         <v>25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>17</v>
@@ -3205,50 +3205,50 @@
         <v>28</v>
       </c>
       <c r="AT14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU14" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY14" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
         <v>42</v>
       </c>
       <c r="BC14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD14" t="n">
         <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BF14" t="n">
         <v>16.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.3</v>
@@ -3309,10 +3309,10 @@
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R15" t="n">
         <v>1.62</v>
@@ -3321,31 +3321,31 @@
         <v>2.52</v>
       </c>
       <c r="T15" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U15" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC15" t="n">
         <v>9.800000000000001</v>
@@ -3354,49 +3354,49 @@
         <v>16</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL15" t="n">
         <v>26</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>29</v>
       </c>
       <c r="AM15" t="n">
         <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO15" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AP15" t="n">
         <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
         <v>29</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="AT15" t="n">
         <v>12</v>
@@ -3405,10 +3405,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
@@ -3420,29 +3420,29 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
         <v>23</v>
       </c>
       <c r="BE15" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -3485,10 +3485,10 @@
         <v>2.12</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.26</v>
@@ -3503,16 +3503,16 @@
         <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R16" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T16" t="n">
         <v>1.49</v>
@@ -3521,7 +3521,7 @@
         <v>2.72</v>
       </c>
       <c r="V16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W16" t="n">
         <v>1.41</v>
@@ -3539,7 +3539,7 @@
         <v>27</v>
       </c>
       <c r="AB16" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AC16" t="n">
         <v>14</v>
@@ -3587,16 +3587,16 @@
         <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AU16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
@@ -3626,17 +3626,17 @@
         <v>29</v>
       </c>
       <c r="BE16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF16" t="n">
         <v>17</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -3673,22 +3673,22 @@
         <v>2.54</v>
       </c>
       <c r="H17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I17" t="n">
         <v>3.25</v>
       </c>
-      <c r="I17" t="n">
-        <v>3.3</v>
-      </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
         <v>3.35</v>
@@ -3700,7 +3700,7 @@
         <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R17" t="n">
         <v>1.29</v>
@@ -3709,13 +3709,13 @@
         <v>4.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
         <v>1.64</v>
@@ -3745,7 +3745,7 @@
         <v>40</v>
       </c>
       <c r="AF17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
@@ -3754,13 +3754,13 @@
         <v>18.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>36</v>
       </c>
       <c r="AK17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL17" t="n">
         <v>46</v>
@@ -3769,16 +3769,16 @@
         <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR17" t="n">
         <v>19.5</v>
@@ -3787,7 +3787,7 @@
         <v>50</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU17" t="n">
         <v>6.8</v>
@@ -3802,7 +3802,7 @@
         <v>14</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
         <v>17.5</v>
@@ -3811,7 +3811,7 @@
         <v>48</v>
       </c>
       <c r="BB17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC17" t="n">
         <v>28</v>
@@ -3826,11 +3826,11 @@
         <v>25</v>
       </c>
       <c r="BG17" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G18" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H18" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I18" t="n">
         <v>3.1</v>
@@ -3876,7 +3876,7 @@
         <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
         <v>1.38</v>
@@ -3885,10 +3885,10 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P18" t="n">
         <v>2.14</v>
@@ -3897,22 +3897,22 @@
         <v>1.86</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X18" t="n">
         <v>16.5</v>
@@ -3924,7 +3924,7 @@
         <v>22</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB18" t="n">
         <v>12</v>
@@ -3933,16 +3933,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
         <v>16</v>
@@ -3951,34 +3951,34 @@
         <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM18" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP18" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AT18" t="n">
         <v>10.5</v>
@@ -3990,13 +3990,13 @@
         <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
         <v>14</v>
@@ -4005,7 +4005,7 @@
         <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC18" t="n">
         <v>22</v>
@@ -4014,17 +4014,17 @@
         <v>30</v>
       </c>
       <c r="BE18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF18" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>2.9</v>
       </c>
       <c r="H19" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I19" t="n">
         <v>2.82</v>
@@ -4076,22 +4076,22 @@
         <v>1.46</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
         <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -4100,10 +4100,10 @@
         <v>1.85</v>
       </c>
       <c r="U19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
         <v>1.52</v>
@@ -4166,7 +4166,7 @@
         <v>11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR19" t="n">
         <v>16</v>
@@ -4178,10 +4178,10 @@
         <v>10</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW19" t="n">
         <v>29</v>
@@ -4202,23 +4202,23 @@
         <v>40</v>
       </c>
       <c r="BC19" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BD19" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BE19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF19" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BG19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H20" t="n">
         <v>2.42</v>
@@ -4261,7 +4261,7 @@
         <v>2.48</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
         <v>3.6</v>
@@ -4276,46 +4276,46 @@
         <v>3.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V20" t="n">
         <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y20" t="n">
         <v>10.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AB20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
@@ -4324,7 +4324,7 @@
         <v>11.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AF20" t="n">
         <v>22</v>
@@ -4336,7 +4336,7 @@
         <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
         <v>60</v>
@@ -4345,10 +4345,10 @@
         <v>38</v>
       </c>
       <c r="AL20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN20" t="n">
         <v>36</v>
@@ -4366,10 +4366,10 @@
         <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AT20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
         <v>7.2</v>
@@ -4387,22 +4387,22 @@
         <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD20" t="n">
         <v>40</v>
       </c>
       <c r="BE20" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BF20" t="n">
         <v>30</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -4443,61 +4443,61 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J21" t="n">
         <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M21" t="n">
         <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y21" t="n">
         <v>9.199999999999999</v>
@@ -4509,7 +4509,7 @@
         <v>42</v>
       </c>
       <c r="AB21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21" t="n">
         <v>7.2</v>
@@ -4518,10 +4518,10 @@
         <v>12.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>13.5</v>
@@ -4536,34 +4536,34 @@
         <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AL21" t="n">
         <v>60</v>
       </c>
       <c r="AM21" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN21" t="n">
         <v>44</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP21" t="n">
         <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
@@ -4572,7 +4572,7 @@
         <v>11.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AX21" t="n">
         <v>17.5</v>
@@ -4581,32 +4581,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB21" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF21" t="n">
         <v>40</v>
       </c>
-      <c r="BC21" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF21" t="n">
+      <c r="BG21" t="n">
         <v>30</v>
       </c>
-      <c r="BG21" t="n">
-        <v>27</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -4637,64 +4637,64 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G22" t="n">
         <v>2.18</v>
       </c>
-      <c r="G22" t="n">
-        <v>2.22</v>
-      </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
         <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X22" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
         <v>29</v>
@@ -4703,10 +4703,10 @@
         <v>85</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
         <v>16</v>
@@ -4715,70 +4715,70 @@
         <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO22" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP22" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW22" t="n">
         <v>48</v>
       </c>
       <c r="AX22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB22" t="n">
         <v>24</v>
@@ -4787,20 +4787,20 @@
         <v>22</v>
       </c>
       <c r="BD22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE22" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="BF22" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="G23" t="n">
         <v>4.9</v>
@@ -4840,40 +4840,40 @@
         <v>1.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="J23" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
         <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U23" t="n">
         <v>2.14</v>
@@ -4885,116 +4885,116 @@
         <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB23" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH23" t="n">
         <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP23" t="n">
         <v>13.5</v>
       </c>
-      <c r="AP23" t="n">
-        <v>6</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.3</v>
+        <v>18.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BB23" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="BD23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="BG23" t="n">
         <v>11.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -5025,40 +5025,40 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G24" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H24" t="n">
         <v>2.22</v>
       </c>
       <c r="I24" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
         <v>3.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
         <v>3.15</v>
       </c>
       <c r="O24" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P24" t="n">
         <v>1.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R24" t="n">
         <v>1.26</v>
@@ -5067,13 +5067,13 @@
         <v>4.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U24" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W24" t="n">
         <v>1.33</v>
@@ -5088,28 +5088,28 @@
         <v>16.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB24" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG24" t="n">
         <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -5130,65 +5130,65 @@
         <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AT24" t="n">
         <v>10.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV24" t="n">
         <v>10</v>
       </c>
       <c r="AW24" t="n">
-        <v>19.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BC24" t="n">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G25" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H25" t="n">
         <v>5.4</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>4.3</v>
@@ -5246,10 +5246,10 @@
         <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P25" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q25" t="n">
         <v>1.98</v>
@@ -5264,22 +5264,22 @@
         <v>1.9</v>
       </c>
       <c r="U25" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V25" t="n">
         <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X25" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="n">
         <v>18.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AA25" t="n">
         <v>190</v>
@@ -5288,22 +5288,22 @@
         <v>8.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD25" t="n">
         <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AF25" t="n">
         <v>10.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
         <v>85</v>
@@ -5312,10 +5312,10 @@
         <v>18.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
         <v>150</v>
@@ -5324,7 +5324,7 @@
         <v>11.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP25" t="n">
         <v>12.5</v>
@@ -5333,10 +5333,10 @@
         <v>15.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT25" t="n">
         <v>7.2</v>
@@ -5348,41 +5348,41 @@
         <v>18.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
         <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>27</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC25" t="n">
         <v>15.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF25" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>5.6</v>
       </c>
       <c r="G26" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H26" t="n">
         <v>1.64</v>
@@ -5434,31 +5434,31 @@
         <v>1.29</v>
       </c>
       <c r="M26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P26" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="R26" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="S26" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="T26" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U26" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
         <v>2.5</v>
@@ -5470,13 +5470,13 @@
         <v>25</v>
       </c>
       <c r="Y26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB26" t="n">
         <v>28</v>
@@ -5497,13 +5497,13 @@
         <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK26" t="n">
         <v>60</v>
@@ -5512,31 +5512,31 @@
         <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN26" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AO26" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AP26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ26" t="n">
         <v>11.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS26" t="n">
         <v>15.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AU26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
         <v>9.4</v>
@@ -5545,38 +5545,38 @@
         <v>14</v>
       </c>
       <c r="AX26" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY26" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA26" t="n">
         <v>23</v>
       </c>
       <c r="BB26" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BC26" t="n">
         <v>50</v>
       </c>
       <c r="BD26" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE26" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="BF26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G27" t="n">
         <v>1.91</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
         <v>4.6</v>
@@ -5640,13 +5640,13 @@
         <v>2.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R27" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S27" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
         <v>1.62</v>
@@ -5661,46 +5661,46 @@
         <v>2.08</v>
       </c>
       <c r="X27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y27" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Z27" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC27" t="n">
         <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG27" t="n">
         <v>12.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>1000</v>
@@ -5715,19 +5715,19 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AU27" t="n">
         <v>8.800000000000001</v>
@@ -5736,10 +5736,10 @@
         <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="AX27" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AY27" t="n">
         <v>9.199999999999999</v>
@@ -5748,29 +5748,29 @@
         <v>14</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BC27" t="n">
         <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -5804,10 +5804,10 @@
         <v>3.05</v>
       </c>
       <c r="G28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H28" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I28" t="n">
         <v>3.1</v>
@@ -5816,16 +5816,16 @@
         <v>2.8</v>
       </c>
       <c r="K28" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="L28" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M28" t="n">
         <v>1.17</v>
       </c>
       <c r="N28" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O28" t="n">
         <v>1.68</v>
@@ -5834,22 +5834,22 @@
         <v>1.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U28" t="n">
         <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W28" t="n">
         <v>1.45</v>
@@ -5858,13 +5858,13 @@
         <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="Z28" t="n">
         <v>20</v>
       </c>
       <c r="AA28" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB28" t="n">
         <v>8</v>
@@ -5873,52 +5873,52 @@
         <v>7</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE28" t="n">
         <v>55</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AH28" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI28" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK28" t="n">
         <v>65</v>
       </c>
-      <c r="AK28" t="n">
-        <v>55</v>
-      </c>
       <c r="AL28" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM28" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AN28" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AO28" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP28" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR28" t="n">
         <v>15.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
@@ -5930,41 +5930,41 @@
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB28" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BC28" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BE28" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G29" t="n">
         <v>3.4</v>
       </c>
       <c r="H29" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J29" t="n">
         <v>3</v>
@@ -6022,25 +6022,25 @@
         <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="R29" t="n">
         <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T29" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U29" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V29" t="n">
         <v>1.57</v>
@@ -6064,7 +6064,7 @@
         <v>10.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD29" t="n">
         <v>13</v>
@@ -6073,10 +6073,10 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH29" t="n">
         <v>1000</v>
@@ -6085,7 +6085,7 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="n">
         <v>1000</v>
@@ -6112,19 +6112,19 @@
         <v>13.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT29" t="n">
         <v>9</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
         <v>10.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AX29" t="n">
         <v>17.5</v>
@@ -6136,10 +6136,10 @@
         <v>9.6</v>
       </c>
       <c r="BA29" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC29" t="n">
         <v>36</v>
@@ -6148,17 +6148,17 @@
         <v>22</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29" t="n">
-        <v>17.5</v>
+        <v>42</v>
       </c>
       <c r="BG29" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>6.4</v>
       </c>
       <c r="G30" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="I30" t="n">
         <v>1.65</v>
@@ -6213,19 +6213,19 @@
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P30" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q30" t="n">
         <v>2.02</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S30" t="n">
         <v>3.6</v>
@@ -6249,25 +6249,25 @@
         <v>7.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AE30" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AG30" t="n">
         <v>25</v>
@@ -6276,31 +6276,31 @@
         <v>23</v>
       </c>
       <c r="AI30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ30" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AK30" t="n">
         <v>100</v>
       </c>
       <c r="AL30" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN30" t="n">
         <v>160</v>
       </c>
-      <c r="AN30" t="n">
-        <v>130</v>
-      </c>
       <c r="AO30" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP30" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR30" t="n">
         <v>8.4</v>
@@ -6309,7 +6309,7 @@
         <v>14</v>
       </c>
       <c r="AT30" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU30" t="n">
         <v>8.6</v>
@@ -6330,29 +6330,29 @@
         <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB30" t="n">
-        <v>17.5</v>
+        <v>90</v>
       </c>
       <c r="BC30" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="BD30" t="n">
-        <v>16.5</v>
+        <v>60</v>
       </c>
       <c r="BE30" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF30" t="n">
-        <v>16.5</v>
+        <v>100</v>
       </c>
       <c r="BG30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G31" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H31" t="n">
         <v>5</v>
@@ -6413,16 +6413,16 @@
         <v>1.1</v>
       </c>
       <c r="P31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q31" t="n">
         <v>1.31</v>
       </c>
       <c r="R31" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="T31" t="n">
         <v>1.44</v>
@@ -6434,13 +6434,13 @@
         <v>1.21</v>
       </c>
       <c r="W31" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X31" t="n">
         <v>60</v>
       </c>
       <c r="Y31" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
         <v>1000</v>
@@ -6449,10 +6449,10 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD31" t="n">
         <v>24</v>
@@ -6473,10 +6473,10 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL31" t="n">
         <v>22</v>
@@ -6491,25 +6491,25 @@
         <v>28</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ31" t="n">
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT31" t="n">
         <v>17.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW31" t="n">
         <v>40</v>
@@ -6521,10 +6521,10 @@
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BB31" t="n">
         <v>16.5</v>
@@ -6533,20 +6533,20 @@
         <v>12.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BF31" t="n">
         <v>3.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G32" t="n">
         <v>1.23</v>
       </c>
-      <c r="G32" t="n">
-        <v>1.24</v>
-      </c>
       <c r="H32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="J32" t="n">
         <v>8.4</v>
@@ -6616,61 +6616,61 @@
         <v>2.6</v>
       </c>
       <c r="S32" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T32" t="n">
         <v>1.62</v>
       </c>
       <c r="U32" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V32" t="n">
         <v>1.07</v>
       </c>
       <c r="W32" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="X32" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Y32" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Z32" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AA32" t="n">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="AB32" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AC32" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AD32" t="n">
         <v>55</v>
       </c>
       <c r="AE32" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF32" t="n">
         <v>15.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI32" t="n">
         <v>95</v>
       </c>
       <c r="AJ32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL32" t="n">
         <v>25</v>
@@ -6679,68 +6679,68 @@
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AO32" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP32" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AQ32" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR32" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AS32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW32" t="n">
         <v>18</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>21</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>38</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>16.5</v>
       </c>
       <c r="AX32" t="n">
         <v>13</v>
       </c>
       <c r="AY32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA32" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD32" t="n">
         <v>21</v>
       </c>
       <c r="BE32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BF32" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BG32" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>1.62</v>
       </c>
       <c r="G33" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H33" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I33" t="n">
         <v>5.6</v>
       </c>
       <c r="J33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L33" t="n">
         <v>1.25</v>
@@ -6795,19 +6795,19 @@
         <v>1.02</v>
       </c>
       <c r="N33" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P33" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="R33" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S33" t="n">
         <v>2.16</v>
@@ -6816,61 +6816,61 @@
         <v>1.56</v>
       </c>
       <c r="U33" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V33" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W33" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y33" t="n">
         <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD33" t="n">
         <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
         <v>14</v>
       </c>
       <c r="AG33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH33" t="n">
         <v>17.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM33" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
         <v>5.6</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ33" t="n">
         <v>25</v>
       </c>
-      <c r="AQ33" t="n">
-        <v>21</v>
-      </c>
       <c r="AR33" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AS33" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AT33" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AX33" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ33" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA33" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG33" t="n">
         <v>32</v>
       </c>
-      <c r="BB33" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>25</v>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -6965,91 +6965,91 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G34" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H34" t="n">
         <v>2.6</v>
       </c>
       <c r="I34" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="J34" t="n">
         <v>4.1</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M34" t="n">
         <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O34" t="n">
         <v>1.13</v>
       </c>
       <c r="P34" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q34" t="n">
         <v>1.41</v>
       </c>
       <c r="R34" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S34" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U34" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V34" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X34" t="n">
         <v>38</v>
       </c>
       <c r="Y34" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
         <v>23</v>
       </c>
-      <c r="Z34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>24</v>
-      </c>
       <c r="AC34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD34" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE34" t="n">
         <v>25</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH34" t="n">
         <v>14</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>14.5</v>
       </c>
       <c r="AI34" t="n">
         <v>27</v>
@@ -7061,7 +7061,7 @@
         <v>38</v>
       </c>
       <c r="AL34" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
@@ -7070,65 +7070,65 @@
         <v>10.5</v>
       </c>
       <c r="AO34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP34" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ34" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AR34" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AV34" t="n">
         <v>6</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="AX34" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="AY34" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="AZ34" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BA34" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BB34" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BD34" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BE34" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BG34" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="F35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G35" t="n">
         <v>3.8</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3.85</v>
       </c>
       <c r="H35" t="n">
         <v>2.22</v>
@@ -7171,10 +7171,10 @@
         <v>2.24</v>
       </c>
       <c r="J35" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L35" t="n">
         <v>1.44</v>
@@ -7186,7 +7186,7 @@
         <v>3.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P35" t="n">
         <v>1.94</v>
@@ -7198,28 +7198,28 @@
         <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T35" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U35" t="n">
         <v>2.18</v>
       </c>
       <c r="V35" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W35" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y35" t="n">
         <v>9.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA35" t="n">
         <v>27</v>
@@ -7228,7 +7228,7 @@
         <v>13.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD35" t="n">
         <v>11</v>
@@ -7267,7 +7267,7 @@
         <v>17.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ35" t="n">
         <v>9</v>
@@ -7276,10 +7276,10 @@
         <v>12.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT35" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU35" t="n">
         <v>7.4</v>
@@ -7303,7 +7303,7 @@
         <v>34</v>
       </c>
       <c r="BB35" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BC35" t="n">
         <v>40</v>
@@ -7318,11 +7318,11 @@
         <v>46</v>
       </c>
       <c r="BG35" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -7353,19 +7353,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G36" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H36" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I36" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="J36" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
         <v>3.1</v>
@@ -7374,10 +7374,10 @@
         <v>1.59</v>
       </c>
       <c r="M36" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N36" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O36" t="n">
         <v>1.57</v>
@@ -7386,7 +7386,7 @@
         <v>1.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R36" t="n">
         <v>1.19</v>
@@ -7401,25 +7401,25 @@
         <v>1.81</v>
       </c>
       <c r="V36" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W36" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X36" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y36" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC36" t="n">
         <v>7</v>
@@ -7431,7 +7431,7 @@
         <v>38</v>
       </c>
       <c r="AF36" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG36" t="n">
         <v>15.5</v>
@@ -7440,7 +7440,7 @@
         <v>24</v>
       </c>
       <c r="AI36" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ36" t="n">
         <v>70</v>
@@ -7449,7 +7449,7 @@
         <v>60</v>
       </c>
       <c r="AL36" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="n">
         <v>190</v>
@@ -7458,7 +7458,7 @@
         <v>95</v>
       </c>
       <c r="AO36" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP36" t="n">
         <v>7.6</v>
@@ -7473,7 +7473,7 @@
         <v>32</v>
       </c>
       <c r="AT36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU36" t="n">
         <v>6.4</v>
@@ -7485,7 +7485,7 @@
         <v>32</v>
       </c>
       <c r="AX36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY36" t="n">
         <v>14</v>
@@ -7506,17 +7506,17 @@
         <v>65</v>
       </c>
       <c r="BE36" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF36" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="BG36" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -7547,25 +7547,25 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="G37" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="H37" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I37" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L37" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M37" t="n">
         <v>1.11</v>
@@ -7574,143 +7574,143 @@
         <v>2.98</v>
       </c>
       <c r="O37" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P37" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R37" t="n">
         <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T37" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U37" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W37" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="X37" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y37" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB37" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF37" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG37" t="n">
         <v>12</v>
       </c>
       <c r="AH37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW37" t="n">
         <v>21</v>
       </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AX37" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BC37" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD37" t="n">
         <v>21</v>
       </c>
-      <c r="BD37" t="n">
-        <v>42</v>
-      </c>
       <c r="BE37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF37" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="BG37" t="n">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K38" t="n">
         <v>950</v>
@@ -7765,28 +7765,28 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>2.04</v>
+        <v>1.1</v>
       </c>
       <c r="O38" t="n">
         <v>1.23</v>
       </c>
       <c r="P38" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="R38" t="n">
         <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V38" t="n">
         <v>1.02</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -7944,10 +7944,10 @@
         <v>1.79</v>
       </c>
       <c r="I39" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
         <v>5.1</v>
@@ -7959,7 +7959,7 @@
         <v>1.02</v>
       </c>
       <c r="N39" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="O39" t="n">
         <v>1.11</v>
@@ -7971,19 +7971,19 @@
         <v>1.36</v>
       </c>
       <c r="R39" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="S39" t="n">
         <v>1.91</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="U39" t="n">
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W39" t="n">
         <v>1.28</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -8129,40 +8129,40 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G40" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H40" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I40" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J40" t="n">
         <v>3.95</v>
       </c>
       <c r="K40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L40" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M40" t="n">
         <v>1.06</v>
       </c>
       <c r="N40" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O40" t="n">
         <v>1.32</v>
       </c>
       <c r="P40" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
         <v>1.37</v>
@@ -8171,128 +8171,128 @@
         <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V40" t="n">
         <v>1.22</v>
       </c>
       <c r="W40" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X40" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y40" t="n">
         <v>18</v>
       </c>
-      <c r="Y40" t="n">
-        <v>20</v>
-      </c>
       <c r="Z40" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD40" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE40" t="n">
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG40" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH40" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI40" t="n">
         <v>85</v>
       </c>
       <c r="AJ40" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK40" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM40" t="n">
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP40" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AR40" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AS40" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="AT40" t="n">
         <v>7.4</v>
       </c>
       <c r="AU40" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV40" t="n">
         <v>18</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="AX40" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY40" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.8</v>
+        <v>34</v>
       </c>
       <c r="BB40" t="n">
         <v>16</v>
       </c>
       <c r="BC40" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.3</v>
+        <v>30</v>
       </c>
       <c r="BE40" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="BF40" t="n">
         <v>10</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -8326,19 +8326,19 @@
         <v>1.75</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I41" t="n">
         <v>6.2</v>
       </c>
       <c r="J41" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K41" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L41" t="n">
         <v>1.43</v>
@@ -8350,7 +8350,7 @@
         <v>3.55</v>
       </c>
       <c r="O41" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P41" t="n">
         <v>1.86</v>
@@ -8374,7 +8374,7 @@
         <v>1.2</v>
       </c>
       <c r="W41" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X41" t="n">
         <v>15.5</v>
@@ -8425,22 +8425,22 @@
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ41" t="n">
         <v>14</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS41" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT41" t="n">
         <v>6.6</v>
@@ -8458,35 +8458,35 @@
         <v>8.6</v>
       </c>
       <c r="AY41" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AZ41" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC41" t="n">
         <v>5.2</v>
       </c>
-      <c r="BA41" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD41" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE41" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF41" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="BG41" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G42" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H42" t="n">
         <v>5</v>
@@ -8547,34 +8547,34 @@
         <v>1.37</v>
       </c>
       <c r="P42" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="U42" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V42" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W42" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X42" t="n">
         <v>12.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z42" t="n">
         <v>38</v>
@@ -8583,7 +8583,7 @@
         <v>140</v>
       </c>
       <c r="AB42" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC42" t="n">
         <v>8.199999999999999</v>
@@ -8598,10 +8598,10 @@
         <v>11</v>
       </c>
       <c r="AG42" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI42" t="n">
         <v>90</v>
@@ -8613,74 +8613,74 @@
         <v>22</v>
       </c>
       <c r="AL42" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AO42" t="n">
         <v>100</v>
       </c>
       <c r="AP42" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AS42" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT42" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU42" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV42" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX42" t="n">
         <v>9.4</v>
       </c>
-      <c r="AW42" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX42" t="n">
+      <c r="AY42" t="n">
         <v>9</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AZ42" t="n">
         <v>18</v>
       </c>
       <c r="BA42" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>17.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC42" t="n">
         <v>19.5</v>
       </c>
       <c r="BD42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE42" t="n">
         <v>12</v>
       </c>
-      <c r="BE42" t="n">
-        <v>11</v>
-      </c>
       <c r="BF42" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG42" t="n">
         <v>12.5</v>
       </c>
-      <c r="BG42" t="n">
-        <v>12</v>
-      </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="G43" t="n">
-        <v>44</v>
+        <v>3.85</v>
       </c>
       <c r="H43" t="n">
         <v>1.09</v>
@@ -8723,7 +8723,7 @@
         <v>44</v>
       </c>
       <c r="J43" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="K43" t="n">
         <v>32</v>
@@ -8747,10 +8747,10 @@
         <v>1.3</v>
       </c>
       <c r="R43" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S43" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -8759,7 +8759,7 @@
         <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
         <v>1.55</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-23 05:10:25</t>
+          <t>2026-04-23 07:32:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-23.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>1.86</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>2.66</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>760</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>810</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AR2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AS2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>2.98</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>3.95</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>2.84</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>1.41</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>2.44</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>3.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>3.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>1.41</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>3.15</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>3.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>3.35</v>
       </c>
       <c r="BG2" t="n">
-        <v>16.5</v>
+        <v>3.35</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
+        <v>38</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE3" t="n">
         <v>13</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>550</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>280</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>220</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>220</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>320</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AX3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AY3" t="n">
-        <v>15.5</v>
+        <v>46</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="BA3" t="n">
         <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="BE3" t="n">
-        <v>120</v>
+        <v>17.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -1145,100 +1145,100 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G4" t="n">
         <v>4.7</v>
       </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
       <c r="H4" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="J4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K4" t="n">
         <v>5.1</v>
       </c>
-      <c r="K4" t="n">
-        <v>5.4</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="P4" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="R4" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="U4" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
         <v>60</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB4" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH4" t="n">
         <v>14.5</v>
       </c>
-      <c r="AF4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>15</v>
-      </c>
       <c r="AI4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AK4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
@@ -1247,68 +1247,68 @@
         <v>42</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
         <v>20</v>
       </c>
       <c r="AT4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BC4" t="n">
         <v>38</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF4" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -1339,109 +1339,109 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y5" t="n">
         <v>21</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD5" t="n">
         <v>22</v>
       </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1450,13 +1450,13 @@
         <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT5" t="n">
         <v>7.8</v>
@@ -1465,44 +1465,44 @@
         <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.6</v>
+        <v>85</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G6" t="n">
         <v>2.02</v>
@@ -1542,55 +1542,55 @@
         <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>1.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T6" t="n">
         <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,13 +1599,13 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1617,16 +1617,16 @@
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1650,16 +1650,16 @@
         <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="AW6" t="n">
         <v>10.5</v>
@@ -1671,32 +1671,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>9.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
       </c>
       <c r="BE6" t="n">
-        <v>11.5</v>
+        <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
         <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="G7" t="n">
         <v>1.24</v>
       </c>
       <c r="H7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J7" t="n">
         <v>6.6</v>
@@ -1751,7 +1751,7 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>1.31</v>
@@ -1760,7 +1760,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
         <v>1.39</v>
@@ -1772,7 +1772,7 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V7" t="n">
         <v>1.04</v>
@@ -1781,7 +1781,7 @@
         <v>5.2</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y7" t="n">
         <v>1000</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,37 +1838,37 @@
         <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
         <v>15</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB7" t="n">
         <v>7</v>
@@ -1877,20 +1877,20 @@
         <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="G8" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="H8" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="I8" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
         <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
         <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY8" t="n">
         <v>15</v>
       </c>
-      <c r="Y8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AZ8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG8" t="n">
         <v>15.5</v>
       </c>
-      <c r="AA8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I9" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="K9" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="L9" t="n">
         <v>1.76</v>
       </c>
       <c r="M9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="N9" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O9" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="P9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -2309,73 +2309,73 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T10" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="U10" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V10" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X10" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA10" t="n">
         <v>32</v>
       </c>
       <c r="AB10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9.6</v>
@@ -2405,22 +2405,22 @@
         <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
         <v>55</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
         <v>16</v>
@@ -2429,7 +2429,7 @@
         <v>27</v>
       </c>
       <c r="AT10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU10" t="n">
         <v>8.800000000000001</v>
@@ -2447,10 +2447,10 @@
         <v>12.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB10" t="n">
         <v>44</v>
@@ -2459,20 +2459,20 @@
         <v>26</v>
       </c>
       <c r="BD10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE10" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="BF10" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BG10" t="n">
         <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -2527,16 +2527,16 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
         <v>1.61</v>
@@ -2545,128 +2545,128 @@
         <v>2.58</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>23</v>
       </c>
-      <c r="Z11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AK11" t="n">
         <v>18</v>
       </c>
-      <c r="AE11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AL11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN11" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP11" t="n">
         <v>21</v>
       </c>
       <c r="AQ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB11" t="n">
         <v>20</v>
       </c>
-      <c r="AR11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="BC11" t="n">
         <v>16.5</v>
       </c>
-      <c r="AW11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>15</v>
-      </c>
       <c r="BD11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE11" t="n">
         <v>55</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -2709,10 +2709,10 @@
         <v>1.53</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.36</v>
@@ -2721,58 +2721,58 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T12" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
         <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD12" t="n">
         <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
         <v>1000</v>
@@ -2781,7 +2781,7 @@
         <v>34</v>
       </c>
       <c r="AH12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2805,22 +2805,22 @@
         <v>7.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS12" t="n">
         <v>10.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.9</v>
+        <v>22</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV12" t="n">
         <v>8.800000000000001</v>
@@ -2829,38 +2829,38 @@
         <v>13.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AY12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG12" t="n">
         <v>6.2</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="I13" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>1.33</v>
@@ -2915,146 +2915,146 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V13" t="n">
         <v>2.74</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2.44</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI13" t="n">
         <v>28</v>
       </c>
-      <c r="Y13" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>44</v>
-      </c>
       <c r="AJ13" t="n">
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM13" t="n">
         <v>95</v>
       </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AP13" t="n">
         <v>21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.48</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.78</v>
+        <v>9.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.65</v>
+        <v>13.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.56</v>
+        <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.68</v>
+        <v>13.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.74</v>
+        <v>46</v>
       </c>
       <c r="AY13" t="n">
-        <v>2.9</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.54</v>
+        <v>25</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.74</v>
+        <v>13</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.74</v>
+        <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.74</v>
+        <v>15.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.74</v>
+        <v>16</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.66</v>
+        <v>15</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.42</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -3115,31 +3115,31 @@
         <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V14" t="n">
         <v>1.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Y14" t="n">
         <v>17</v>
@@ -3154,16 +3154,16 @@
         <v>21</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>21</v>
       </c>
       <c r="AF14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG14" t="n">
         <v>14</v>
@@ -3175,7 +3175,7 @@
         <v>26</v>
       </c>
       <c r="AJ14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK14" t="n">
         <v>29</v>
@@ -3187,16 +3187,16 @@
         <v>48</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
         <v>25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR14" t="n">
         <v>17</v>
@@ -3205,7 +3205,7 @@
         <v>28</v>
       </c>
       <c r="AT14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AU14" t="n">
         <v>8.6</v>
@@ -3214,13 +3214,13 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX14" t="n">
         <v>24</v>
       </c>
       <c r="AY14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>12</v>
@@ -3229,26 +3229,26 @@
         <v>23</v>
       </c>
       <c r="BB14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BC14" t="n">
         <v>26</v>
       </c>
       <c r="BD14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="BF14" t="n">
         <v>16.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G15" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>3.85</v>
@@ -3294,61 +3294,61 @@
         <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.6</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.62</v>
-      </c>
       <c r="S15" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U15" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V15" t="n">
         <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y15" t="n">
         <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AB15" t="n">
         <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD15" t="n">
         <v>16</v>
@@ -3369,22 +3369,22 @@
         <v>42</v>
       </c>
       <c r="AJ15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM15" t="n">
         <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP15" t="n">
         <v>20</v>
@@ -3393,10 +3393,10 @@
         <v>18</v>
       </c>
       <c r="AR15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS15" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="AT15" t="n">
         <v>12</v>
@@ -3417,32 +3417,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="BB15" t="n">
         <v>20</v>
       </c>
       <c r="BC15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG15" t="n">
         <v>15.5</v>
       </c>
-      <c r="BD15" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>25</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="J16" t="n">
         <v>4.3</v>
@@ -3491,152 +3491,152 @@
         <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
         <v>6.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="R16" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="S16" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="U16" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="W16" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AB16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF16" t="n">
         <v>28</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AG16" t="n">
         <v>14</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>15.5</v>
       </c>
       <c r="AH16" t="n">
         <v>14.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ16" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK16" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
         <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AO16" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AR16" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AY16" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA16" t="n">
         <v>21</v>
       </c>
       <c r="BB16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BC16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BD16" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BE16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF16" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>3.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
@@ -3688,7 +3688,7 @@
         <v>1.52</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
         <v>3.35</v>
@@ -3700,7 +3700,7 @@
         <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R17" t="n">
         <v>1.29</v>
@@ -3709,16 +3709,16 @@
         <v>4.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U17" t="n">
         <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X17" t="n">
         <v>11</v>
@@ -3730,13 +3730,13 @@
         <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD17" t="n">
         <v>14</v>
@@ -3769,7 +3769,7 @@
         <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO17" t="n">
         <v>46</v>
@@ -3787,13 +3787,13 @@
         <v>50</v>
       </c>
       <c r="AT17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW17" t="n">
         <v>36</v>
@@ -3802,25 +3802,25 @@
         <v>14</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
         <v>48</v>
       </c>
       <c r="BB17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD17" t="n">
         <v>42</v>
       </c>
       <c r="BE17" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BF17" t="n">
         <v>25</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="G18" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="J18" t="n">
         <v>3.65</v>
@@ -3879,55 +3879,55 @@
         <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.28</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="X18" t="n">
         <v>16.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>48</v>
+        <v>970</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
         <v>8.199999999999999</v>
@@ -3936,25 +3936,25 @@
         <v>13</v>
       </c>
       <c r="AE18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
         <v>36</v>
@@ -3963,68 +3963,68 @@
         <v>75</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ18" t="n">
         <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AT18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU18" t="n">
         <v>7.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY18" t="n">
         <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE18" t="n">
         <v>60</v>
       </c>
       <c r="BF18" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BG18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="G19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H19" t="n">
         <v>2.9</v>
       </c>
-      <c r="H19" t="n">
-        <v>2.74</v>
-      </c>
       <c r="I19" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB19" t="n">
         <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ19" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AK19" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM19" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN19" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
         <v>30</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AX19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY19" t="n">
         <v>11</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
         <v>40</v>
       </c>
       <c r="BB19" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BC19" t="n">
         <v>27</v>
       </c>
       <c r="BD19" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BF19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -4252,70 +4252,70 @@
         <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
         <v>2.42</v>
       </c>
       <c r="I20" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
         <v>2.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U20" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
@@ -4324,28 +4324,28 @@
         <v>11.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
         <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AJ20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK20" t="n">
         <v>38</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM20" t="n">
         <v>95</v>
@@ -4354,31 +4354,31 @@
         <v>36</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ20" t="n">
         <v>9.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS20" t="n">
         <v>30</v>
       </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX20" t="n">
         <v>20</v>
@@ -4387,32 +4387,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC20" t="n">
         <v>34</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>23</v>
       </c>
       <c r="BD20" t="n">
         <v>40</v>
       </c>
       <c r="BE20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF20" t="n">
         <v>30</v>
       </c>
       <c r="BG20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G21" t="n">
         <v>3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I21" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.35</v>
       </c>
       <c r="L21" t="n">
         <v>1.52</v>
@@ -4470,7 +4470,7 @@
         <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P21" t="n">
         <v>1.7</v>
@@ -4485,7 +4485,7 @@
         <v>4.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U21" t="n">
         <v>1.97</v>
@@ -4494,13 +4494,13 @@
         <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X21" t="n">
         <v>10.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
         <v>16</v>
@@ -4509,16 +4509,16 @@
         <v>42</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC21" t="n">
         <v>7.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
         <v>19</v>
@@ -4551,7 +4551,7 @@
         <v>34</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ21" t="n">
         <v>8.6</v>
@@ -4560,7 +4560,7 @@
         <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AT21" t="n">
         <v>9.199999999999999</v>
@@ -4569,28 +4569,28 @@
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AX21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
         <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BB21" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BC21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD21" t="n">
         <v>42</v>
@@ -4599,14 +4599,14 @@
         <v>42</v>
       </c>
       <c r="BF21" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BG21" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I22" t="n">
         <v>4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.2</v>
       </c>
       <c r="J22" t="n">
         <v>3.35</v>
@@ -4655,64 +4655,64 @@
         <v>3.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.7</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.8</v>
-      </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
         <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y22" t="n">
         <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA22" t="n">
         <v>85</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC22" t="n">
         <v>7.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF22" t="n">
         <v>13</v>
@@ -4721,7 +4721,7 @@
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>60</v>
@@ -4733,13 +4733,13 @@
         <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM22" t="n">
         <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO22" t="n">
         <v>55</v>
@@ -4787,20 +4787,20 @@
         <v>22</v>
       </c>
       <c r="BD22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE22" t="n">
         <v>80</v>
       </c>
       <c r="BF22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -4837,40 +4837,40 @@
         <v>4.9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="I23" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="J23" t="n">
         <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
         <v>1.78</v>
@@ -4882,79 +4882,79 @@
         <v>2.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="n">
         <v>22</v>
       </c>
       <c r="AB23" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AC23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
         <v>10.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AF23" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AG23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="n">
         <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL23" t="n">
         <v>110</v>
       </c>
-      <c r="AK23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>70</v>
-      </c>
       <c r="AM23" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP23" t="n">
         <v>14</v>
       </c>
-      <c r="AP23" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV23" t="n">
         <v>9.199999999999999</v>
@@ -4969,32 +4969,32 @@
         <v>16</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="BD23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE23" t="n">
         <v>12.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-23 07:32:14</t>
+          <t>2026-04-23 09:57:50</t>
         </is>
       </c>
     </row>
@@ -5034,73 +5034,73 @@
         <v>2.22</v>
       </c>
       <c r="I24" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J24" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R24" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="U24" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
         <v>16.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB24" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
         <v>11.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF24" t="n">
         <v>32</v>
@@ -5109,7 +5109,7 @@
         <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -5130,65 +5130,65 @@
         <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ24" t="n">
         <v>7.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX24" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.8